--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,31 +501,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4708251488426893</v>
+        <v>0.4934769756689703</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3525902406428866</v>
+        <v>0.338895164192504</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5604249603850782</v>
+        <v>0.4212471361590849</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.360455686320745</v>
+        <v>1.460851653841713</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3">
@@ -538,28 +538,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1977298325883842</v>
+        <v>0.1566035309348527</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.21967395183435</v>
+        <v>0.2249426078247836</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1669575651624964</v>
+        <v>0.143955827412041</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.358137159144218</v>
+        <v>1.472804594688848</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1326400346779815</v>
+        <v>0.1635813081454697</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2075387471542296</v>
+        <v>0.2073766001947369</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06779629672406792</v>
+        <v>0.09376222928743319</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.326793301119276</v>
+        <v>1.418653016452894</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09961293536075137</v>
+        <v>0.07655031662667959</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1788751068561756</v>
+        <v>0.1652371240146799</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03375795125024297</v>
+        <v>0.02010834142406274</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8380195870454115</v>
+        <v>0.8672166885734174</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.08510906192926335</v>
+        <v>0.09093983284067626</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01198016051298536</v>
+        <v>0.009249262636788309</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02543098655731628</v>
+        <v>0.02654435833171037</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7481099372148119</v>
+        <v>0.8339964500456545</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="7">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002174497713142228</v>
+        <v>0.0006623874105793368</v>
       </c>
       <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01082545318724312</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.01584562269079249</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.0001342453518592856</v>
+        <v>0.0007410061135764123</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7894921326934701</v>
+        <v>0.9731716775514923</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00132709769091784</v>
+        <v>0.001030879111032006</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001635452808147984</v>
+        <v>0.01823310073242509</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006042120375294502</v>
+        <v>0.001191792659991719</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07176842362683944</v>
+        <v>0.3412892129988085</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001059193415642016</v>
+        <v>0.0007530530725082443</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002810805503528566</v>
+        <v>0.001077156610443113</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>2.198813528203614e-05</v>
+        <v>0.0001611350279293711</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1555645995356798</v>
+        <v>0.744186914584263</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001072879674425107</v>
+        <v>0.0004999010613522326</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001268168286095804</v>
+        <v>0.001123066054036514</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>5.077956548692475e-05</v>
+        <v>0.0001458349710713014</v>
       </c>
       <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2413980955877375</v>
+      </c>
+      <c r="J10" t="n">
         <v>14</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.1419004963272781</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0007291527243273023</v>
+        <v>0.0002950139211836122</v>
       </c>
       <c r="D11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001892574032144988</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0001873242169758371</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2779894243050682</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="n">
         <v>14</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0007961398502900826</v>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0005963259770771278</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.13042557705251</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" t="n">
-        <v>10.75</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0008095213653611792</v>
+        <v>0.0005889879807100593</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001002426555430714</v>
+        <v>0.001081133185744966</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0003985635151521838</v>
+        <v>5.026650528268117e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>0.10619039574375</v>
+        <v>0.2431577677377081</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0009760565256204592</v>
+        <v>0.0002973423066116075</v>
       </c>
       <c r="D13" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.00137428593249932</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0001529619352196754</v>
+      </c>
+      <c r="H13" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.002409913179546283</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-1.801691110409065e-05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>18</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.1646103851497331</v>
+        <v>0.2680127065233666</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0005253332440265347</v>
+        <v>0.0002944702810060399</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000531447116479929</v>
+        <v>0.001608220600207737</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002375519504744461</v>
+        <v>7.325294506478341e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08824839594920286</v>
+        <v>0.843235841284093</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005915998417233243</v>
+        <v>0.0005581832467282384</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0002240749991915604</v>
+        <v>0.0005753573624328989</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003236184086395921</v>
+        <v>0.0003026497551013252</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06272479552172694</v>
+        <v>0.2031832835351097</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>15.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0002593251221110288</v>
+        <v>0.0007682207633995115</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0007379080710492715</v>
+        <v>0.0009936734567571033</v>
       </c>
       <c r="F16" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0001005435566609036</v>
+      </c>
+      <c r="H16" t="n">
         <v>13</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0001559438263676438</v>
-      </c>
-      <c r="H16" t="n">
-        <v>11</v>
-      </c>
       <c r="I16" t="n">
-        <v>0.02095338443789396</v>
+        <v>0.141599339793979</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001107769456230276</v>
+        <v>0.002886182563130571</v>
       </c>
       <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.002679453698458627</v>
+      </c>
+      <c r="F17" t="n">
         <v>8</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.0003511295588861592</v>
-      </c>
-      <c r="F17" t="n">
-        <v>17</v>
-      </c>
       <c r="G17" t="n">
-        <v>-0.0001913266231740818</v>
+        <v>-0.0002476561263153543</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04869265431341319</v>
+        <v>0.9968591896377172</v>
       </c>
       <c r="J17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>16.75</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005404184944181518</v>
+        <v>0.00064037491702989</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000364971021233304</v>
+        <v>0.0007341646200798267</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>4.120020042464034e-05</v>
+        <v>1.475127075224458e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05790657997375037</v>
+        <v>0.2231802573544841</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>16.75</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006378213642902811</v>
+        <v>0.0004090822092578022</v>
       </c>
       <c r="D19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0005938799435931378</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.511672052393781e-05</v>
+      </c>
+      <c r="H19" t="n">
         <v>15</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.0002221615907832199</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
+        <v>0.1587709816647886</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26</v>
+      </c>
+      <c r="K19" t="n">
         <v>21</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-8.618697228195416e-05</v>
-      </c>
-      <c r="H19" t="n">
-        <v>21</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.1134615809563653</v>
-      </c>
-      <c r="J19" t="n">
-        <v>11</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0006054554098934552</v>
+        <v>0.001185263719407358</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0003415333819301951</v>
+        <v>0.0009920751080023354</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.723195384256362e-05</v>
+        <v>5.29586757816225e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07143248123717916</v>
+        <v>0.07951115201995407</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005198599874589906</v>
+        <v>0.0004182502430682502</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0003681320382587627</v>
+        <v>0.0003960475015691421</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>5.367976371118965e-05</v>
+        <v>6.2408608076292e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01129667129768874</v>
+        <v>0.1499236532073862</v>
       </c>
       <c r="J21" t="n">
+        <v>27</v>
+      </c>
+      <c r="K21" t="n">
         <v>22</v>
-      </c>
-      <c r="K21" t="n">
-        <v>17.5</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0008807873083301238</v>
+        <v>0.0004071574005070125</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0002827151004070339</v>
+        <v>0.0003041679440847097</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0001706313620291389</v>
+        <v>5.855107534625814e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0277615951376573</v>
+        <v>0.1493719011629593</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>18.25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0002475080465596292</v>
+        <v>0.0004266799322393587</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0001382569695774216</v>
+        <v>0.0002886609689897829</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.446678705078867e-05</v>
+        <v>2.228985867063216e-05</v>
       </c>
       <c r="H23" t="n">
+        <v>27</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1957830607978728</v>
+      </c>
+      <c r="J23" t="n">
         <v>20</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.0645543823776662</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16</v>
-      </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,1145 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7.894344728654669e-05</v>
+      </c>
+      <c r="D24" t="n">
+        <v>46</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0007960865176047714</v>
+      </c>
+      <c r="F24" t="n">
+        <v>18</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.824206781837368e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>26</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2364750138504186</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" t="n">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0003900859873871865</v>
+      </c>
+      <c r="D25" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.000294270837652906</v>
+      </c>
+      <c r="F25" t="n">
+        <v>31</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.532496698884559e-05</v>
+      </c>
+      <c r="H25" t="n">
+        <v>19</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09677789336238218</v>
+      </c>
+      <c r="J25" t="n">
+        <v>40</v>
+      </c>
+      <c r="K25" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5.630606897554129e-05</v>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.00076598115109719</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.159328692732388e-05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>28</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2357135238578496</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0003292534638235924</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0006001673178206944</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-9.79245142200158e-05</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1786956032887064</v>
+      </c>
+      <c r="J27" t="n">
+        <v>22</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0003909137986629653</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0002329365121236286</v>
+      </c>
+      <c r="F28" t="n">
+        <v>39</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.147234116810504e-05</v>
+      </c>
+      <c r="H28" t="n">
+        <v>29</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1461564347318935</v>
+      </c>
+      <c r="J28" t="n">
+        <v>29</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002946421161636714</v>
+      </c>
+      <c r="D29" t="n">
+        <v>28</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0003749091419610152</v>
+      </c>
+      <c r="F29" t="n">
+        <v>26</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.957636883188508e-05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09333954918326937</v>
+      </c>
+      <c r="J29" t="n">
+        <v>42</v>
+      </c>
+      <c r="K29" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0002521542320226248</v>
+      </c>
+      <c r="D30" t="n">
+        <v>33</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0001840748891843003</v>
+      </c>
+      <c r="F30" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.841594983122313e-05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1348959181405722</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0002751771056297094</v>
+      </c>
+      <c r="D31" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0002780510057352769</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.644465675406329e-05</v>
+      </c>
+      <c r="H31" t="n">
+        <v>22</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1055202396413497</v>
+      </c>
+      <c r="J31" t="n">
+        <v>37</v>
+      </c>
+      <c r="K31" t="n">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7.107003209822167e-05</v>
+      </c>
+      <c r="D32" t="n">
+        <v>48</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001537153584875766</v>
+      </c>
+      <c r="F32" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-6.048627357146952e-06</v>
+      </c>
+      <c r="H32" t="n">
+        <v>42</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1707544587680432</v>
+      </c>
+      <c r="J32" t="n">
+        <v>23</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0005474636811603711</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.000298682041584456</v>
+      </c>
+      <c r="F33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-2.586766987557887e-05</v>
+      </c>
+      <c r="H33" t="n">
+        <v>46</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1221102006732759</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0004976066404976792</v>
+      </c>
+      <c r="D34" t="n">
+        <v>17</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0002558941964679858</v>
+      </c>
+      <c r="F34" t="n">
+        <v>34</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.0001888985741649085</v>
+      </c>
+      <c r="H34" t="n">
+        <v>52</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1652770224911846</v>
+      </c>
+      <c r="J34" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" t="n">
+        <v>31.75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0003830628266531956</v>
+      </c>
+      <c r="D35" t="n">
+        <v>24</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.000180298276363558</v>
+      </c>
+      <c r="F35" t="n">
+        <v>44</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-5.421508224578986e-06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>40</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1925205334070608</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21</v>
+      </c>
+      <c r="K35" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0002398687408691055</v>
+      </c>
+      <c r="D36" t="n">
+        <v>36</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0002430422942303231</v>
+      </c>
+      <c r="F36" t="n">
+        <v>37</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1.727999246934342e-05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>45</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.206042605746664</v>
+      </c>
+      <c r="J36" t="n">
+        <v>18</v>
+      </c>
+      <c r="K36" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0002912269097378063</v>
+      </c>
+      <c r="D37" t="n">
+        <v>30</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0003470098968722277</v>
+      </c>
+      <c r="F37" t="n">
+        <v>27</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-7.835917637153412e-05</v>
+      </c>
+      <c r="H37" t="n">
+        <v>49</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1426675686584642</v>
+      </c>
+      <c r="J37" t="n">
+        <v>31</v>
+      </c>
+      <c r="K37" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0002579590734871167</v>
+      </c>
+      <c r="D38" t="n">
+        <v>32</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0002504882483320145</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.810816755548396e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.06525408048085124</v>
+      </c>
+      <c r="J38" t="n">
+        <v>46</v>
+      </c>
+      <c r="K38" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0002491653832428795</v>
+      </c>
+      <c r="D39" t="n">
+        <v>34</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0003060744594260856</v>
+      </c>
+      <c r="F39" t="n">
+        <v>28</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-1.351283128953051e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>43</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1391609698191743</v>
+      </c>
+      <c r="J39" t="n">
+        <v>33</v>
+      </c>
+      <c r="K39" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8.728350352817404e-05</v>
+      </c>
+      <c r="D40" t="n">
+        <v>45</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000626076574427717</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21</v>
+      </c>
+      <c r="G40" t="n">
+        <v>9.50334715297263e-06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>33</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.020601990187056</v>
+      </c>
+      <c r="J40" t="n">
+        <v>50</v>
+      </c>
+      <c r="K40" t="n">
+        <v>37.25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0002343322341740696</v>
+      </c>
+      <c r="D41" t="n">
+        <v>38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.000196870791204119</v>
+      </c>
+      <c r="F41" t="n">
+        <v>41</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-6.179572673862266e-05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>47</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1618468036499907</v>
+      </c>
+      <c r="J41" t="n">
+        <v>25</v>
+      </c>
+      <c r="K41" t="n">
+        <v>37.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0001644768478988834</v>
+      </c>
+      <c r="D42" t="n">
+        <v>43</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.000242006138068137</v>
+      </c>
+      <c r="F42" t="n">
+        <v>38</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.02461454677494e-05</v>
+      </c>
+      <c r="H42" t="n">
+        <v>24</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.05715079294994618</v>
+      </c>
+      <c r="J42" t="n">
+        <v>47</v>
+      </c>
+      <c r="K42" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0002377479275142439</v>
+      </c>
+      <c r="D43" t="n">
+        <v>37</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0002116225599470462</v>
+      </c>
+      <c r="F43" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-7.464296639827505e-05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>48</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1456793987127565</v>
+      </c>
+      <c r="J43" t="n">
+        <v>30</v>
+      </c>
+      <c r="K43" t="n">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.000198203740831712</v>
+      </c>
+      <c r="D44" t="n">
+        <v>42</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0001813860060519051</v>
+      </c>
+      <c r="F44" t="n">
+        <v>43</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.436338466875853e-05</v>
+      </c>
+      <c r="H44" t="n">
+        <v>31</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.09813417184463846</v>
+      </c>
+      <c r="J44" t="n">
+        <v>39</v>
+      </c>
+      <c r="K44" t="n">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0002341166204347321</v>
+      </c>
+      <c r="D45" t="n">
+        <v>39</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0001631995498436024</v>
+      </c>
+      <c r="F45" t="n">
+        <v>46</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.452768611387434e-06</v>
+      </c>
+      <c r="H45" t="n">
+        <v>35</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1019458773657425</v>
+      </c>
+      <c r="J45" t="n">
+        <v>38</v>
+      </c>
+      <c r="K45" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0002452326659973242</v>
+      </c>
+      <c r="D46" t="n">
+        <v>35</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0002512080601245316</v>
+      </c>
+      <c r="F46" t="n">
+        <v>35</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-1.598813033291124e-05</v>
+      </c>
+      <c r="H46" t="n">
+        <v>44</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.07554720522443992</v>
+      </c>
+      <c r="J46" t="n">
+        <v>45</v>
+      </c>
+      <c r="K46" t="n">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0001462709729975095</v>
+      </c>
+      <c r="D47" t="n">
+        <v>44</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0001043026151371769</v>
+      </c>
+      <c r="F47" t="n">
+        <v>49</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8.436790474319888e-06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>34</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.09430905966686209</v>
+      </c>
+      <c r="J47" t="n">
+        <v>41</v>
+      </c>
+      <c r="K47" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0002130685956627212</v>
+      </c>
+      <c r="D48" t="n">
+        <v>40</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.747146222328386e-05</v>
+      </c>
+      <c r="F48" t="n">
+        <v>50</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-7.143576778112503e-07</v>
+      </c>
+      <c r="H48" t="n">
+        <v>38</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.08603500859574087</v>
+      </c>
+      <c r="J48" t="n">
+        <v>43</v>
+      </c>
+      <c r="K48" t="n">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6.694215915596535e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>49</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0001708630312780224</v>
+      </c>
+      <c r="F49" t="n">
+        <v>45</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.35237771476282e-05</v>
+      </c>
+      <c r="H49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.03890270057521183</v>
+      </c>
+      <c r="J49" t="n">
+        <v>48</v>
+      </c>
+      <c r="K49" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0002008403108520613</v>
+      </c>
+      <c r="D50" t="n">
+        <v>41</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0001256065543468434</v>
+      </c>
+      <c r="F50" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.0001082205470914421</v>
+      </c>
+      <c r="H50" t="n">
+        <v>51</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1111892772634375</v>
+      </c>
+      <c r="J50" t="n">
+        <v>36</v>
+      </c>
+      <c r="K50" t="n">
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>7.284823813362488e-05</v>
+      </c>
+      <c r="D51" t="n">
+        <v>47</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0001227173258486162</v>
+      </c>
+      <c r="F51" t="n">
+        <v>48</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-5.838369691546496e-06</v>
+      </c>
+      <c r="H51" t="n">
+        <v>41</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.03499447622261265</v>
+      </c>
+      <c r="J51" t="n">
+        <v>49</v>
+      </c>
+      <c r="K51" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4.855094616615176e-06</v>
+      </c>
+      <c r="D52" t="n">
+        <v>53</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5.445202767085317e-05</v>
+      </c>
+      <c r="F52" t="n">
+        <v>51</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6.953063436454521e-07</v>
+      </c>
+      <c r="H52" t="n">
+        <v>37</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.01374888500033489</v>
+      </c>
+      <c r="J52" t="n">
+        <v>51</v>
+      </c>
+      <c r="K52" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7.250526481278343e-06</v>
+      </c>
+      <c r="D53" t="n">
+        <v>52</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.475558383849283e-05</v>
+      </c>
+      <c r="F53" t="n">
+        <v>53</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9.784998548756363e-07</v>
+      </c>
+      <c r="H53" t="n">
+        <v>36</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>52</v>
+      </c>
+      <c r="K53" t="n">
+        <v>48.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1.870921645239433e-05</v>
-      </c>
-      <c r="D24" t="n">
-        <v>23</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.093427774408886e-05</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4.955794874228481e-06</v>
-      </c>
-      <c r="H24" t="n">
-        <v>17</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="C54" t="n">
+        <v>8.236697623228188e-06</v>
+      </c>
+      <c r="D54" t="n">
+        <v>51</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.911154645240304e-05</v>
+      </c>
+      <c r="F54" t="n">
+        <v>52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-1.668896820428145e-06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>39</v>
+      </c>
+      <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>23</v>
-      </c>
-      <c r="K24" t="n">
-        <v>21.5</v>
+      <c r="J54" t="n">
+        <v>52</v>
+      </c>
+      <c r="K54" t="n">
+        <v>48.5</v>
       </c>
     </row>
   </sheetData>
@@ -1423,31 +2533,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4708251488426893</v>
+        <v>0.4934769756689703</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3525902406428866</v>
+        <v>0.338895164192504</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5604249603850782</v>
+        <v>0.4212471361590849</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.360455686320745</v>
+        <v>1.460851653841713</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3">
@@ -1460,28 +2570,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1977298325883842</v>
+        <v>0.1566035309348527</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.21967395183435</v>
+        <v>0.2249426078247836</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1669575651624964</v>
+        <v>0.143955827412041</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.358137159144218</v>
+        <v>1.472804594688848</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -1497,31 +2607,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1326400346779815</v>
+        <v>0.1635813081454697</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2075387471542296</v>
+        <v>0.2073766001947369</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06779629672406792</v>
+        <v>0.09376222928743319</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.326793301119276</v>
+        <v>1.418653016452894</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -1534,31 +2644,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09961293536075137</v>
+        <v>0.07655031662667959</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1788751068561756</v>
+        <v>0.1652371240146799</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03375795125024297</v>
+        <v>0.02010834142406274</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8380195870454115</v>
+        <v>0.8672166885734174</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1571,31 +2681,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.08510906192926335</v>
+        <v>0.09093983284067626</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01198016051298536</v>
+        <v>0.009249262636788309</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02543098655731628</v>
+        <v>0.02654435833171037</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7481099372148119</v>
+        <v>0.8339964500456545</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="7">
@@ -1608,31 +2718,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002174497713142228</v>
+        <v>0.0006623874105793368</v>
       </c>
       <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01082545318724312</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.01584562269079249</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.0001342453518592856</v>
+        <v>0.0007410061135764123</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7894921326934701</v>
+        <v>0.9731716775514923</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="8">
@@ -1641,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00132709769091784</v>
+        <v>0.001030879111032006</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001635452808147984</v>
+        <v>0.01823310073242509</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006042120375294502</v>
+        <v>0.001191792659991719</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07176842362683944</v>
+        <v>0.3412892129988085</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="9">
@@ -1678,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001059193415642016</v>
+        <v>0.0007530530725082443</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002810805503528566</v>
+        <v>0.001077156610443113</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>2.198813528203614e-05</v>
+        <v>0.0001611350279293711</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1555645995356798</v>
+        <v>0.744186914584263</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1715,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001072879674425107</v>
+        <v>0.0004999010613522326</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001268168286095804</v>
+        <v>0.001123066054036514</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>5.077956548692475e-05</v>
+        <v>0.0001458349710713014</v>
       </c>
       <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2413980955877375</v>
+      </c>
+      <c r="J10" t="n">
         <v>14</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.1419004963272781</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="11">
@@ -1752,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0007291527243273023</v>
+        <v>0.0002950139211836122</v>
       </c>
       <c r="D11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001892574032144988</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0001873242169758371</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2779894243050682</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="n">
         <v>14</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0007961398502900826</v>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0005963259770771278</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.13042557705251</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" t="n">
-        <v>10.75</v>
       </c>
     </row>
     <row r="12">
@@ -1789,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0008095213653611792</v>
+        <v>0.0005889879807100593</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001002426555430714</v>
+        <v>0.001081133185744966</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0003985635151521838</v>
+        <v>5.026650528268117e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>0.10619039574375</v>
+        <v>0.2431577677377081</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13">
@@ -1826,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0009760565256204592</v>
+        <v>0.0002973423066116075</v>
       </c>
       <c r="D13" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.00137428593249932</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0001529619352196754</v>
+      </c>
+      <c r="H13" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.002409913179546283</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-1.801691110409065e-05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>18</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.1646103851497331</v>
+        <v>0.2680127065233666</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="14">
@@ -1863,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0005253332440265347</v>
+        <v>0.0002944702810060399</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000531447116479929</v>
+        <v>0.001608220600207737</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002375519504744461</v>
+        <v>7.325294506478341e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08824839594920286</v>
+        <v>0.843235841284093</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="15">
@@ -1900,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005915998417233243</v>
+        <v>0.0005581832467282384</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0002240749991915604</v>
+        <v>0.0005753573624328989</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003236184086395921</v>
+        <v>0.0003026497551013252</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06272479552172694</v>
+        <v>0.2031832835351097</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>15.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="16">
@@ -1937,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0002593251221110288</v>
+        <v>0.0007682207633995115</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0007379080710492715</v>
+        <v>0.0009936734567571033</v>
       </c>
       <c r="F16" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0001005435566609036</v>
+      </c>
+      <c r="H16" t="n">
         <v>13</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.0001559438263676438</v>
-      </c>
-      <c r="H16" t="n">
-        <v>11</v>
-      </c>
       <c r="I16" t="n">
-        <v>0.02095338443789396</v>
+        <v>0.141599339793979</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="17">
@@ -1974,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001107769456230276</v>
+        <v>0.002886182563130571</v>
       </c>
       <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.002679453698458627</v>
+      </c>
+      <c r="F17" t="n">
         <v>8</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.0003511295588861592</v>
-      </c>
-      <c r="F17" t="n">
-        <v>17</v>
-      </c>
       <c r="G17" t="n">
-        <v>-0.0001913266231740818</v>
+        <v>-0.0002476561263153543</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04869265431341319</v>
+        <v>0.9968591896377172</v>
       </c>
       <c r="J17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>16.75</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="18">
@@ -2011,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005404184944181518</v>
+        <v>0.00064037491702989</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000364971021233304</v>
+        <v>0.0007341646200798267</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>4.120020042464034e-05</v>
+        <v>1.475127075224458e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05790657997375037</v>
+        <v>0.2231802573544841</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>16.75</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="19">
@@ -2048,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006378213642902811</v>
+        <v>0.0004090822092578022</v>
       </c>
       <c r="D19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0005938799435931378</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.511672052393781e-05</v>
+      </c>
+      <c r="H19" t="n">
         <v>15</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.0002221615907832199</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
+        <v>0.1587709816647886</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26</v>
+      </c>
+      <c r="K19" t="n">
         <v>21</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-8.618697228195416e-05</v>
-      </c>
-      <c r="H19" t="n">
-        <v>21</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.1134615809563653</v>
-      </c>
-      <c r="J19" t="n">
-        <v>11</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -2085,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0006054554098934552</v>
+        <v>0.001185263719407358</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0003415333819301951</v>
+        <v>0.0009920751080023354</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.723195384256362e-05</v>
+        <v>5.29586757816225e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07143248123717916</v>
+        <v>0.07951115201995407</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2122,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005198599874589906</v>
+        <v>0.0004182502430682502</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0003681320382587627</v>
+        <v>0.0003960475015691421</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>5.367976371118965e-05</v>
+        <v>6.2408608076292e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01129667129768874</v>
+        <v>0.1499236532073862</v>
       </c>
       <c r="J21" t="n">
+        <v>27</v>
+      </c>
+      <c r="K21" t="n">
         <v>22</v>
-      </c>
-      <c r="K21" t="n">
-        <v>17.5</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4708251488426893</v>
+        <v>0.4934769756689703</v>
       </c>
     </row>
     <row r="3">
@@ -2203,11 +3313,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1977298325883842</v>
+        <v>0.1635813081454697</v>
       </c>
     </row>
     <row r="4">
@@ -2216,11 +3326,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1326400346779815</v>
+        <v>0.1566035309348527</v>
       </c>
     </row>
     <row r="5">
@@ -2229,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09961293536075137</v>
+        <v>0.09093983284067626</v>
       </c>
     </row>
     <row r="6">
@@ -2242,11 +3352,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.08510906192926335</v>
+        <v>0.07655031662667959</v>
       </c>
     </row>
     <row r="7">
@@ -2255,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002174497713142228</v>
+        <v>0.002886182563130571</v>
       </c>
     </row>
     <row r="8">
@@ -2268,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00132709769091784</v>
+        <v>0.001185263719407358</v>
       </c>
     </row>
     <row r="9">
@@ -2281,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001107769456230276</v>
+        <v>0.001030879111032006</v>
       </c>
     </row>
     <row r="10">
@@ -2294,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001072879674425107</v>
+        <v>0.0007682207633995115</v>
       </c>
     </row>
     <row r="11">
@@ -2307,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001059193415642016</v>
+        <v>0.0007530530725082443</v>
       </c>
     </row>
     <row r="12">
@@ -2320,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0009760565256204592</v>
+        <v>0.0006623874105793368</v>
       </c>
     </row>
     <row r="13">
@@ -2333,11 +3443,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0008807873083301238</v>
+        <v>0.00064037491702989</v>
       </c>
     </row>
     <row r="14">
@@ -2346,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0008095213653611792</v>
+        <v>0.0005889879807100593</v>
       </c>
     </row>
     <row r="15">
@@ -2363,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0007291527243273023</v>
+        <v>0.0005581832467282384</v>
       </c>
     </row>
     <row r="16">
@@ -2372,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0006378213642902811</v>
+        <v>0.0005474636811603711</v>
       </c>
     </row>
     <row r="17">
@@ -2385,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0006054554098934552</v>
+        <v>0.0004999010613522326</v>
       </c>
     </row>
     <row r="18">
@@ -2398,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005915998417233243</v>
+        <v>0.0004976066404976792</v>
       </c>
     </row>
     <row r="19">
@@ -2411,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0005404184944181518</v>
+        <v>0.0004266799322393587</v>
       </c>
     </row>
     <row r="20">
@@ -2428,7 +3538,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005253332440265347</v>
+        <v>0.0004182502430682502</v>
       </c>
     </row>
     <row r="21">
@@ -2437,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005198599874589906</v>
+        <v>0.0004090822092578022</v>
       </c>
     </row>
     <row r="22">
@@ -2450,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002593251221110288</v>
+        <v>0.0004071574005070125</v>
       </c>
     </row>
     <row r="23">
@@ -2463,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0002475080465596292</v>
+        <v>0.0003909137986629653</v>
       </c>
     </row>
     <row r="24">
@@ -2476,11 +3586,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0003900859873871865</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0003830628266531956</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0003292534638235924</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0002973423066116075</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0002950139211836122</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002946421161636714</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>report_date_month</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0002944702810060399</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0002912269097378063</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0002751771056297094</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0002579590734871167</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0002521542320226248</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0002491653832428795</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0002452326659973242</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0002398687408691055</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0002377479275142439</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0002343322341740696</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0002341166204347321</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0002130685956627212</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0002008403108520613</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.000198203740831712</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0001644768478988834</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0001462709729975095</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8.728350352817404e-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7.894344728654669e-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7.284823813362488e-05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7.107003209822167e-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>6.694215915596535e-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5.630606897554129e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1.870921645239433e-05</v>
+      <c r="C52" t="n">
+        <v>8.236697623228188e-06</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7.250526481278343e-06</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4.855094616615176e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3525902406428866</v>
+        <v>0.338895164192504</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.21967395183435</v>
+        <v>0.2249426078247836</v>
       </c>
     </row>
     <row r="4">
@@ -2550,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2075387471542296</v>
+        <v>0.2073766001947369</v>
       </c>
     </row>
     <row r="5">
@@ -2563,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1788751068561756</v>
+        <v>0.1652371240146799</v>
       </c>
     </row>
     <row r="6">
@@ -2572,11 +4072,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01584562269079249</v>
+        <v>0.01823310073242509</v>
       </c>
     </row>
     <row r="7">
@@ -2585,11 +4085,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01198016051298536</v>
+        <v>0.01082545318724312</v>
       </c>
     </row>
     <row r="8">
@@ -2598,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002810805503528566</v>
+        <v>0.009249262636788309</v>
       </c>
     </row>
     <row r="9">
@@ -2611,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002409913179546283</v>
+        <v>0.002679453698458627</v>
       </c>
     </row>
     <row r="10">
@@ -2624,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001635452808147984</v>
+        <v>0.001892574032144988</v>
       </c>
     </row>
     <row r="11">
@@ -2637,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001268168286095804</v>
+        <v>0.001608220600207737</v>
       </c>
     </row>
     <row r="12">
@@ -2650,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001002426555430714</v>
+        <v>0.001537153584875766</v>
       </c>
     </row>
     <row r="13">
@@ -2663,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0007961398502900826</v>
+        <v>0.00137428593249932</v>
       </c>
     </row>
     <row r="14">
@@ -2676,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0007379080710492715</v>
+        <v>0.001123066054036514</v>
       </c>
     </row>
     <row r="15">
@@ -2689,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.000531447116479929</v>
+        <v>0.001081133185744966</v>
       </c>
     </row>
     <row r="16">
@@ -2702,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003681320382587627</v>
+        <v>0.001077156610443113</v>
       </c>
     </row>
     <row r="17">
@@ -2715,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.000364971021233304</v>
+        <v>0.0009936734567571033</v>
       </c>
     </row>
     <row r="18">
@@ -2728,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003511295588861592</v>
+        <v>0.0009920751080023354</v>
       </c>
     </row>
     <row r="19">
@@ -2741,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003415333819301951</v>
+        <v>0.0007960865176047714</v>
       </c>
     </row>
     <row r="20">
@@ -2754,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002827151004070339</v>
+        <v>0.00076598115109719</v>
       </c>
     </row>
     <row r="21">
@@ -2767,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002240749991915604</v>
+        <v>0.0007341646200798267</v>
       </c>
     </row>
     <row r="22">
@@ -2780,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002221615907832199</v>
+        <v>0.000626076574427717</v>
       </c>
     </row>
     <row r="23">
@@ -2793,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001382569695774216</v>
+        <v>0.0006001673178206944</v>
       </c>
     </row>
     <row r="24">
@@ -2806,11 +4306,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0005938799435931378</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0005753573624328989</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0003960475015691421</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0003749091419610152</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0003470098968722277</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0003060744594260856</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0003041679440847097</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.000298682041584456</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.000294270837652906</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0002886609689897829</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0002780510057352769</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0002558941964679858</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0002512080601245316</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0002504882483320145</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0002430422942303231</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.000242006138068137</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0002329365121236286</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0002116225599470462</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.000196870791204119</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0001840748891843003</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0001813860060519051</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.000180298276363558</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0001708630312780224</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0001631995498436024</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0001256065543468434</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0001227173258486162</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0001043026151371769</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>9.747146222328386e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5.445202767085317e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1.093427774408886e-05</v>
+      <c r="C53" t="n">
+        <v>1.911154645240304e-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1.475558383849283e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5604249603850782</v>
+        <v>0.4212471361590849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04772986140377863</v>
+        <v>0.03611059365480117</v>
       </c>
     </row>
     <row r="3">
@@ -2875,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1669575651624964</v>
+        <v>0.143955827412041</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009237240631347877</v>
+        <v>0.00776635928047572</v>
       </c>
     </row>
     <row r="4">
@@ -2891,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06779629672406792</v>
+        <v>0.09376222928743319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005996595180127939</v>
+        <v>0.006483763428301178</v>
       </c>
     </row>
     <row r="5">
@@ -2903,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03375795125024297</v>
+        <v>0.02654435833171037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005406416590357536</v>
+        <v>0.003979485304965496</v>
       </c>
     </row>
     <row r="6">
@@ -2919,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02543098655731628</v>
+        <v>0.02010834142406274</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005154255250643878</v>
+        <v>0.003118027567508813</v>
       </c>
     </row>
     <row r="7">
@@ -2935,14 +4825,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0006042120375294502</v>
+        <v>0.001191792659991719</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001102555748752804</v>
+        <v>0.0001049422604976716</v>
       </c>
     </row>
     <row r="8">
@@ -2951,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0005963259770771278</v>
+        <v>0.0007410061135764123</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001201658748133092</v>
+        <v>7.788303636944813e-06</v>
       </c>
     </row>
     <row r="9">
@@ -2967,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003985635151521838</v>
+        <v>0.0003026497551013252</v>
       </c>
       <c r="D9" t="n">
-        <v>2.889618976466559e-05</v>
+        <v>0.0001093109383231229</v>
       </c>
     </row>
     <row r="10">
@@ -2983,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003236184086395921</v>
+        <v>0.0001873242169758371</v>
       </c>
       <c r="D10" t="n">
-        <v>8.684888994434149e-05</v>
+        <v>7.092128871524662e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2999,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002375519504744461</v>
+        <v>0.0001611350279293711</v>
       </c>
       <c r="D11" t="n">
-        <v>6.283214555208655e-05</v>
+        <v>6.31931139378999e-05</v>
       </c>
     </row>
     <row r="12">
@@ -3015,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0001559438263676438</v>
+        <v>0.0001529619352196754</v>
       </c>
       <c r="D12" t="n">
-        <v>1.814008088881033e-06</v>
+        <v>5.464644704515163e-05</v>
       </c>
     </row>
     <row r="13">
@@ -3031,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0001342453518592856</v>
+        <v>0.0001458349710713014</v>
       </c>
       <c r="D13" t="n">
-        <v>3.126076790755493e-05</v>
+        <v>0.000105652772163094</v>
       </c>
     </row>
     <row r="14">
@@ -3047,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.367976371118965e-05</v>
+        <v>0.0001005435566609036</v>
       </c>
       <c r="D14" t="n">
-        <v>4.274752296764561e-05</v>
+        <v>6.082226906787488e-05</v>
       </c>
     </row>
     <row r="15">
@@ -3063,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.077956548692475e-05</v>
+        <v>7.841594983122313e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001634264633254022</v>
+        <v>2.844185382379873e-05</v>
       </c>
     </row>
     <row r="16">
@@ -3079,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.120020042464034e-05</v>
+        <v>7.511672052393781e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>3.963166759123221e-05</v>
+        <v>1.992765721384532e-05</v>
       </c>
     </row>
     <row r="17">
@@ -3095,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.198813528203614e-05</v>
+        <v>7.325294506478341e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000171647532545811</v>
+        <v>6.149274280191493e-05</v>
       </c>
     </row>
     <row r="18">
@@ -3111,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.955794874228481e-06</v>
+        <v>6.2408608076292e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>6.463239379482615e-06</v>
+        <v>7.281152153062255e-05</v>
       </c>
     </row>
     <row r="19">
@@ -3127,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1.801691110409065e-05</v>
+        <v>5.855107534625814e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001434876243129392</v>
+        <v>5.592748114504596e-05</v>
       </c>
     </row>
     <row r="20">
@@ -3143,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-4.723195384256362e-05</v>
+        <v>5.532496698884559e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>4.466707825552737e-05</v>
+        <v>4.316451186385658e-05</v>
       </c>
     </row>
     <row r="21">
@@ -3159,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-5.446678705078867e-05</v>
+        <v>5.29586757816225e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>5.805203382046315e-05</v>
+        <v>0.0005930640440956977</v>
       </c>
     </row>
     <row r="22">
@@ -3175,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-8.618697228195416e-05</v>
+        <v>5.026650528268117e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001151530622824328</v>
+        <v>4.572340696402321e-05</v>
       </c>
     </row>
     <row r="23">
@@ -3191,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.0001706313620291389</v>
+        <v>4.644465675406329e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001906125269513778</v>
+        <v>1.984606585794413e-05</v>
       </c>
     </row>
     <row r="24">
@@ -3207,14 +5097,494 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3.810816755548396e-05</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.882957767401136e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3.02461454677494e-05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.802101514072507e-05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.957636883188508e-05</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.785480192300289e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2.824206781837368e-05</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.944608570741844e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2.228985867063216e-05</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9.070145746241402e-05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2.159328692732388e-05</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.561987688781347e-06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2.147234116810504e-05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.956073450676586e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.475127075224458e-05</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.73488135266934e-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.436338466875853e-05</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.513180728829008e-05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1.35237771476282e-05</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.052067573590642e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9.50334715297263e-06</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.835026794076016e-07</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8.436790474319888e-06</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.30315678312168e-05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.452768611387434e-06</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.243214661470544e-05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>9.784998548756363e-07</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.020906816829307e-06</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>6.953063436454521e-07</v>
+      </c>
+      <c r="D38" t="n">
+        <v>9.064763378063593e-07</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-7.143576778112503e-07</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.740368019901645e-05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.668896820428145e-06</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.27982035655436e-06</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-5.421508224578986e-06</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0001564618999997516</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-5.838369691546496e-06</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.341584854204905e-05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-6.048627357146952e-06</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.416139702143126e-05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.351283128953051e-05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3.5683470121688e-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.598813033291124e-05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.032776263617263e-05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.727999246934342e-05</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3.19167283085617e-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>sulphited_brix</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>-0.0001913266231740818</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0001649371137188589</v>
+      <c r="C47" t="n">
+        <v>-2.586766987557887e-05</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.0001254392689678129</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-6.179572673862266e-05</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.645697135789296e-05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-7.464296639827505e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.940309874948056e-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-7.835917637153412e-05</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.012127406410508e-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-9.79245142200158e-05</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6.109844966970093e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0001082205470914421</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7.194541074355793e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0001888985741649085</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.0003757906730581535</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>work_day</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0002476561263153543</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0005951006808222924</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3254,11 +5624,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.360455686320745</v>
+        <v>1.472804594688848</v>
       </c>
     </row>
     <row r="3">
@@ -3267,11 +5637,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.358137159144218</v>
+        <v>1.460851653841713</v>
       </c>
     </row>
     <row r="4">
@@ -3284,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.326793301119276</v>
+        <v>1.418653016452894</v>
       </c>
     </row>
     <row r="5">
@@ -3293,11 +5663,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8380195870454115</v>
+        <v>0.9968591896377172</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +5680,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7894921326934701</v>
+        <v>0.9731716775514923</v>
       </c>
     </row>
     <row r="7">
@@ -3319,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7481099372148119</v>
+        <v>0.8672166885734174</v>
       </c>
     </row>
     <row r="8">
@@ -3332,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1646103851497331</v>
+        <v>0.843235841284093</v>
       </c>
     </row>
     <row r="9">
@@ -3345,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1555645995356798</v>
+        <v>0.8339964500456545</v>
       </c>
     </row>
     <row r="10">
@@ -3358,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1419004963272781</v>
+        <v>0.744186914584263</v>
       </c>
     </row>
     <row r="11">
@@ -3371,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.13042557705251</v>
+        <v>0.3412892129988085</v>
       </c>
     </row>
     <row r="12">
@@ -3384,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1134615809563653</v>
+        <v>0.2779894243050682</v>
       </c>
     </row>
     <row r="13">
@@ -3397,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.10619039574375</v>
+        <v>0.2680127065233666</v>
       </c>
     </row>
     <row r="14">
@@ -3410,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.08824839594920286</v>
+        <v>0.2431577677377081</v>
       </c>
     </row>
     <row r="15">
@@ -3423,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.07176842362683944</v>
+        <v>0.2413980955877375</v>
       </c>
     </row>
     <row r="16">
@@ -3436,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.07143248123717916</v>
+        <v>0.2364750138504186</v>
       </c>
     </row>
     <row r="17">
@@ -3449,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0645543823776662</v>
+        <v>0.2357135238578496</v>
       </c>
     </row>
     <row r="18">
@@ -3462,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.06272479552172694</v>
+        <v>0.2231802573544841</v>
       </c>
     </row>
     <row r="19">
@@ -3475,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.05790657997375037</v>
+        <v>0.206042605746664</v>
       </c>
     </row>
     <row r="20">
@@ -3488,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.04869265431341319</v>
+        <v>0.2031832835351097</v>
       </c>
     </row>
     <row r="21">
@@ -3501,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0277615951376573</v>
+        <v>0.1957830607978728</v>
       </c>
     </row>
     <row r="22">
@@ -3514,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02095338443789396</v>
+        <v>0.1925205334070608</v>
       </c>
     </row>
     <row r="23">
@@ -3527,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01129667129768874</v>
+        <v>0.1786956032887064</v>
       </c>
     </row>
     <row r="24">
@@ -3540,10 +5910,400 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1707544587680432</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1652770224911846</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1618468036499907</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1587709816647886</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1499236532073862</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1493719011629593</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1461564347318935</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1456793987127565</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1426675686584642</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.141599339793979</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1391609698191743</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1348959181405722</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1221102006732759</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1111892772634375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1055202396413497</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1019458773657425</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.09813417184463846</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.09677789336238218</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.09430905966686209</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.09333954918326937</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.08603500859574087</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.07951115201995407</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.07554720522443992</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.06525408048085124</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.05715079294994618</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.03890270057521183</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.03499447622261265</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.020601990187056</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.01374888500033489</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,17 +6355,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:43:56 UTC</t>
+          <t>2026-06-11 05:03:37 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4212471361590849</v>
+        <v>0.4212471361590847</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02010834142406274</v>
+        <v>0.02010834142406271</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02654435833171037</v>
+        <v>0.02654435833171039</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007410061135764123</v>
+        <v>0.0007410061135762784</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001191792659991719</v>
+        <v>0.001191792659991686</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>5.026650528268117e-05</v>
+        <v>5.026650528265897e-05</v>
       </c>
       <c r="H12" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001529619352196754</v>
+        <v>0.0001529619352196865</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -994,7 +994,7 @@
         <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003026497551013252</v>
+        <v>0.0003026497551013363</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -1031,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001005435566609036</v>
+        <v>0.0001005435566608925</v>
       </c>
       <c r="H16" t="n">
         <v>13</v>
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0002476561263153543</v>
+        <v>-0.0002476561263153654</v>
       </c>
       <c r="H17" t="n">
         <v>53</v>
@@ -1105,7 +1105,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>1.475127075224458e-05</v>
+        <v>1.475127075225568e-05</v>
       </c>
       <c r="H18" t="n">
         <v>30</v>
@@ -1142,7 +1142,7 @@
         <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>7.511672052393781e-05</v>
+        <v>7.51167205239267e-05</v>
       </c>
       <c r="H19" t="n">
         <v>15</v>
@@ -1179,7 +1179,7 @@
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>5.29586757816225e-05</v>
+        <v>5.29586757816336e-05</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>5.855107534625814e-05</v>
+        <v>5.855107534626924e-05</v>
       </c>
       <c r="H22" t="n">
         <v>18</v>
@@ -1290,7 +1290,7 @@
         <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>2.228985867063216e-05</v>
+        <v>2.228985867064326e-05</v>
       </c>
       <c r="H23" t="n">
         <v>27</v>
@@ -1327,7 +1327,7 @@
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>2.824206781837368e-05</v>
+        <v>2.824206781839589e-05</v>
       </c>
       <c r="H24" t="n">
         <v>26</v>
@@ -1364,7 +1364,7 @@
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>5.532496698884559e-05</v>
+        <v>5.532496698883449e-05</v>
       </c>
       <c r="H25" t="n">
         <v>19</v>
@@ -1475,7 +1475,7 @@
         <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>2.147234116810504e-05</v>
+        <v>2.147234116807173e-05</v>
       </c>
       <c r="H28" t="n">
         <v>29</v>
@@ -1549,7 +1549,7 @@
         <v>42</v>
       </c>
       <c r="G30" t="n">
-        <v>7.841594983122313e-05</v>
+        <v>7.841594983123423e-05</v>
       </c>
       <c r="H30" t="n">
         <v>14</v>
@@ -1586,7 +1586,7 @@
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>4.644465675406329e-05</v>
+        <v>4.644465675408549e-05</v>
       </c>
       <c r="H31" t="n">
         <v>22</v>
@@ -1623,7 +1623,7 @@
         <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>-6.048627357146952e-06</v>
+        <v>-6.04862735713585e-06</v>
       </c>
       <c r="H32" t="n">
         <v>42</v>
@@ -1697,7 +1697,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0001888985741649085</v>
+        <v>-0.0001888985741648974</v>
       </c>
       <c r="H34" t="n">
         <v>52</v>
@@ -1734,7 +1734,7 @@
         <v>44</v>
       </c>
       <c r="G35" t="n">
-        <v>-5.421508224578986e-06</v>
+        <v>-5.421508224590088e-06</v>
       </c>
       <c r="H35" t="n">
         <v>40</v>
@@ -1808,7 +1808,7 @@
         <v>27</v>
       </c>
       <c r="G37" t="n">
-        <v>-7.835917637153412e-05</v>
+        <v>-7.835917637154522e-05</v>
       </c>
       <c r="H37" t="n">
         <v>49</v>
@@ -1882,7 +1882,7 @@
         <v>28</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.351283128953051e-05</v>
+        <v>-1.351283128954162e-05</v>
       </c>
       <c r="H39" t="n">
         <v>43</v>
@@ -1919,7 +1919,7 @@
         <v>21</v>
       </c>
       <c r="G40" t="n">
-        <v>9.50334715297263e-06</v>
+        <v>9.503347152983731e-06</v>
       </c>
       <c r="H40" t="n">
         <v>33</v>
@@ -1956,7 +1956,7 @@
         <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>-6.179572673862266e-05</v>
+        <v>-6.179572673861155e-05</v>
       </c>
       <c r="H41" t="n">
         <v>47</v>
@@ -2030,7 +2030,7 @@
         <v>40</v>
       </c>
       <c r="G43" t="n">
-        <v>-7.464296639827505e-05</v>
+        <v>-7.464296639825285e-05</v>
       </c>
       <c r="H43" t="n">
         <v>48</v>
@@ -2067,7 +2067,7 @@
         <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>1.436338466875853e-05</v>
+        <v>1.436338466879183e-05</v>
       </c>
       <c r="H44" t="n">
         <v>31</v>
@@ -2104,7 +2104,7 @@
         <v>46</v>
       </c>
       <c r="G45" t="n">
-        <v>1.452768611387434e-06</v>
+        <v>1.452768611420741e-06</v>
       </c>
       <c r="H45" t="n">
         <v>35</v>
@@ -2141,7 +2141,7 @@
         <v>35</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.598813033291124e-05</v>
+        <v>-1.598813033288904e-05</v>
       </c>
       <c r="H46" t="n">
         <v>44</v>
@@ -2289,7 +2289,7 @@
         <v>47</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.0001082205470914421</v>
+        <v>-0.0001082205470914088</v>
       </c>
       <c r="H50" t="n">
         <v>51</v>
@@ -2326,7 +2326,7 @@
         <v>48</v>
       </c>
       <c r="G51" t="n">
-        <v>-5.838369691546496e-06</v>
+        <v>-5.838369691557599e-06</v>
       </c>
       <c r="H51" t="n">
         <v>41</v>
@@ -2363,7 +2363,7 @@
         <v>51</v>
       </c>
       <c r="G52" t="n">
-        <v>6.953063436454521e-07</v>
+        <v>6.953063436565543e-07</v>
       </c>
       <c r="H52" t="n">
         <v>37</v>
@@ -2400,7 +2400,7 @@
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>9.784998548756363e-07</v>
+        <v>9.784998548312275e-07</v>
       </c>
       <c r="H53" t="n">
         <v>36</v>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4212471361590849</v>
+        <v>0.4212471361590847</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02010834142406274</v>
+        <v>0.02010834142406271</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02654435833171037</v>
+        <v>0.02654435833171039</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007410061135764123</v>
+        <v>0.0007410061135762784</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2767,7 +2767,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001191792659991719</v>
+        <v>0.001191792659991686</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -2915,7 +2915,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>5.026650528268117e-05</v>
+        <v>5.026650528265897e-05</v>
       </c>
       <c r="H12" t="n">
         <v>21</v>
@@ -2952,7 +2952,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001529619352196754</v>
+        <v>0.0001529619352196865</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -3026,7 +3026,7 @@
         <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003026497551013252</v>
+        <v>0.0003026497551013363</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -3063,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001005435566609036</v>
+        <v>0.0001005435566608925</v>
       </c>
       <c r="H16" t="n">
         <v>13</v>
@@ -3100,7 +3100,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0002476561263153543</v>
+        <v>-0.0002476561263153654</v>
       </c>
       <c r="H17" t="n">
         <v>53</v>
@@ -3137,7 +3137,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>1.475127075224458e-05</v>
+        <v>1.475127075225568e-05</v>
       </c>
       <c r="H18" t="n">
         <v>30</v>
@@ -3174,7 +3174,7 @@
         <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>7.511672052393781e-05</v>
+        <v>7.51167205239267e-05</v>
       </c>
       <c r="H19" t="n">
         <v>15</v>
@@ -3211,7 +3211,7 @@
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>5.29586757816225e-05</v>
+        <v>5.29586757816336e-05</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4212471361590849</v>
+        <v>0.4212471361590847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03611059365480117</v>
+        <v>0.03611059365480114</v>
       </c>
     </row>
     <row r="3">
@@ -4768,7 +4768,7 @@
         <v>0.143955827412041</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00776635928047572</v>
+        <v>0.007766359280475725</v>
       </c>
     </row>
     <row r="4">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02654435833171037</v>
+        <v>0.02654435833171039</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003979485304965496</v>
+        <v>0.003979485304965487</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02010834142406274</v>
+        <v>0.02010834142406271</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003118027567508813</v>
+        <v>0.003118027567508811</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001191792659991719</v>
+        <v>0.001191792659991686</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001049422604976716</v>
+        <v>0.0001049422604976825</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0007410061135764123</v>
+        <v>0.0007410061135762784</v>
       </c>
       <c r="D8" t="n">
-        <v>7.788303636944813e-06</v>
+        <v>7.78830363693586e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003026497551013252</v>
+        <v>0.0003026497551013363</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001093109383231229</v>
+        <v>0.0001093109383231348</v>
       </c>
     </row>
     <row r="10">
@@ -4880,7 +4880,7 @@
         <v>0.0001873242169758371</v>
       </c>
       <c r="D10" t="n">
-        <v>7.092128871524662e-05</v>
+        <v>7.092128871523098e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4896,7 +4896,7 @@
         <v>0.0001611350279293711</v>
       </c>
       <c r="D11" t="n">
-        <v>6.31931139378999e-05</v>
+        <v>6.319311393788344e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0001529619352196754</v>
+        <v>0.0001529619352196865</v>
       </c>
       <c r="D12" t="n">
-        <v>5.464644704515163e-05</v>
+        <v>5.464644704515823e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0001005435566609036</v>
+        <v>0.0001005435566608925</v>
       </c>
       <c r="D14" t="n">
-        <v>6.082226906787488e-05</v>
+        <v>6.082226906787357e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.841594983122313e-05</v>
+        <v>7.841594983123423e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>2.844185382379873e-05</v>
+        <v>2.844185382380329e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.511672052393781e-05</v>
+        <v>7.51167205239267e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>1.992765721384532e-05</v>
+        <v>1.992765721385495e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4992,7 +4992,7 @@
         <v>7.325294506478341e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>6.149274280191493e-05</v>
+        <v>6.149274280194455e-05</v>
       </c>
     </row>
     <row r="18">
@@ -5008,7 +5008,7 @@
         <v>6.2408608076292e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>7.281152153062255e-05</v>
+        <v>7.281152153062162e-05</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.855107534625814e-05</v>
+        <v>5.855107534626924e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>5.592748114504596e-05</v>
+        <v>5.592748114504927e-05</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.532496698884559e-05</v>
+        <v>5.532496698883449e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>4.316451186385658e-05</v>
+        <v>4.316451186386958e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.29586757816225e-05</v>
+        <v>5.29586757816336e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0005930640440956977</v>
+        <v>0.0005930640440957069</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.026650528268117e-05</v>
+        <v>5.026650528265897e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>4.572340696402321e-05</v>
+        <v>4.572340696400091e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.644465675406329e-05</v>
+        <v>4.644465675408549e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>1.984606585794413e-05</v>
+        <v>1.984606585794202e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5104,7 +5104,7 @@
         <v>3.810816755548396e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>2.882957767401136e-05</v>
+        <v>2.882957767400429e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5120,7 +5120,7 @@
         <v>3.02461454677494e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.802101514072507e-05</v>
+        <v>1.80210151407425e-05</v>
       </c>
     </row>
     <row r="26">
@@ -5136,7 +5136,7 @@
         <v>2.957636883188508e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>2.785480192300289e-05</v>
+        <v>2.78548019230335e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.824206781837368e-05</v>
+        <v>2.824206781839589e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.944608570741844e-05</v>
+        <v>1.944608570740266e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.228985867063216e-05</v>
+        <v>2.228985867064326e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>9.070145746241402e-05</v>
+        <v>9.070145746245526e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5184,7 +5184,7 @@
         <v>2.159328692732388e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>6.561987688781347e-06</v>
+        <v>6.561987688814561e-06</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.147234116810504e-05</v>
+        <v>2.147234116807173e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>3.956073450676586e-05</v>
+        <v>3.956073450679267e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.475127075224458e-05</v>
+        <v>1.475127075225568e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>3.73488135266934e-05</v>
+        <v>3.734881352668717e-05</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.436338466875853e-05</v>
+        <v>1.436338466879183e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>3.513180728829008e-05</v>
+        <v>3.513180728832451e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9.50334715297263e-06</v>
+        <v>9.503347152983731e-06</v>
       </c>
       <c r="D34" t="n">
-        <v>5.835026794076016e-07</v>
+        <v>5.835026794025116e-07</v>
       </c>
     </row>
     <row r="35">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.452768611387434e-06</v>
+        <v>1.452768611420741e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>1.243214661470544e-05</v>
+        <v>1.243214661469633e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9.784998548756363e-07</v>
+        <v>9.784998548312275e-07</v>
       </c>
       <c r="D37" t="n">
-        <v>1.020906816829307e-06</v>
+        <v>1.020906816827111e-06</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6.953063436454521e-07</v>
+        <v>6.953063436565543e-07</v>
       </c>
       <c r="D38" t="n">
-        <v>9.064763378063593e-07</v>
+        <v>9.064763378067245e-07</v>
       </c>
     </row>
     <row r="39">
@@ -5344,7 +5344,7 @@
         <v>-7.143576778112503e-07</v>
       </c>
       <c r="D39" t="n">
-        <v>4.740368019901645e-05</v>
+        <v>4.740368019902112e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5360,7 +5360,7 @@
         <v>-1.668896820428145e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>3.27982035655436e-06</v>
+        <v>3.279820356534446e-06</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-5.421508224578986e-06</v>
+        <v>-5.421508224590088e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001564618999997516</v>
+        <v>0.0001564618999997506</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.838369691546496e-06</v>
+        <v>-5.838369691557599e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.341584854204905e-05</v>
+        <v>1.34158485420633e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-6.048627357146952e-06</v>
+        <v>-6.04862735713585e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>2.416139702143126e-05</v>
+        <v>2.41613970214327e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.351283128953051e-05</v>
+        <v>-1.351283128954162e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>3.5683470121688e-05</v>
+        <v>3.568347012171998e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1.598813033291124e-05</v>
+        <v>-1.598813033288904e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>4.032776263617263e-05</v>
+        <v>4.032776263619629e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-6.179572673862266e-05</v>
+        <v>-6.179572673861155e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>4.645697135789296e-05</v>
+        <v>4.645697135787311e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-7.464296639827505e-05</v>
+        <v>-7.464296639825285e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>3.940309874948056e-05</v>
+        <v>3.940309874948654e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-7.835917637153412e-05</v>
+        <v>-7.835917637154522e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>3.012127406410508e-05</v>
+        <v>3.012127406408834e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001082205470914421</v>
+        <v>-0.0001082205470914088</v>
       </c>
       <c r="D52" t="n">
-        <v>7.194541074355793e-05</v>
+        <v>7.194541074356519e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001888985741649085</v>
+        <v>-0.0001888985741648974</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0003757906730581535</v>
+        <v>0.0003757906730581602</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0002476561263153543</v>
+        <v>-0.0002476561263153654</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0005951006808222924</v>
+        <v>0.0005951006808222858</v>
       </c>
     </row>
   </sheetData>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:03:37 UTC</t>
+          <t>2026-06-11 07:45:41 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4934769756689703</v>
+        <v>0.4977888743490059</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.338895164192504</v>
+        <v>0.3555639308574666</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4212471361590847</v>
+        <v>0.4275278758199269</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.460851653841713</v>
+        <v>1.212438164413909</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -538,31 +538,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1566035309348527</v>
+        <v>0.1705570914101155</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2249426078247836</v>
+        <v>0.2190170715818167</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.143955827412041</v>
+        <v>0.1547372651050634</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.472804594688848</v>
+        <v>1.231562346339471</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1635813081454697</v>
+        <v>0.1493154822576961</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2073766001947369</v>
+        <v>0.1945990500210734</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09376222928743319</v>
+        <v>0.08337686689426374</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.418653016452894</v>
+        <v>1.071602712577556</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07655031662667959</v>
+        <v>0.09109327576136467</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1652371240146799</v>
+        <v>0.1704639022676688</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02010834142406271</v>
+        <v>0.02625494934165764</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8672166885734174</v>
+        <v>0.6647508870541099</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.09093983284067626</v>
+        <v>0.07266127677126222</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009249262636788309</v>
+        <v>0.009783522296471749</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02654435833171039</v>
+        <v>0.01662492513450207</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8339964500456545</v>
+        <v>0.550538439464701</v>
       </c>
       <c r="J6" t="n">
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0006623874105793368</v>
+        <v>0.0007103842065014464</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01082545318724312</v>
+        <v>0.01008863850085699</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007410061135762784</v>
+        <v>0.0009065309642399915</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9731716775514923</v>
+        <v>0.6663908335330178</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -723,25 +723,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001030879111032006</v>
+        <v>0.001106154337122481</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01823310073242509</v>
+        <v>0.01507350619875696</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001191792659991686</v>
+        <v>0.001183796798163073</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3412892129988085</v>
+        <v>0.3335482345837661</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -760,31 +760,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0007530530725082443</v>
+        <v>0.0006782722832782091</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001077156610443113</v>
+        <v>0.00107945562607117</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001611350279293711</v>
+        <v>0.0001071084214119389</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.744186914584263</v>
+        <v>0.4648439152564756</v>
       </c>
       <c r="J9" t="n">
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="10">
@@ -797,31 +797,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0004999010613522326</v>
+        <v>0.0004998411828986698</v>
       </c>
       <c r="D10" t="n">
         <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001123066054036514</v>
+        <v>0.001375017038606483</v>
       </c>
       <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.000151267789462084</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2547847995899231</v>
+      </c>
+      <c r="J10" t="n">
         <v>13</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0001458349710713014</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2413980955877375</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>13.75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002950139211836122</v>
+        <v>0.0003127567702813812</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001892574032144988</v>
+        <v>0.001910325373208544</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001873242169758371</v>
+        <v>0.0001997195509044092</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2779894243050682</v>
+        <v>0.2587939072850545</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="12">
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0005889879807100593</v>
+        <v>0.0005909537916020339</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001081133185744966</v>
+        <v>0.001058674853744491</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>5.026650528265897e-05</v>
+        <v>6.458258715732467e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2431577677377081</v>
+        <v>0.2408108237229087</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>15.25</v>
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0002973423066116075</v>
+        <v>0.0005375576450263882</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00137428593249932</v>
+        <v>0.0004710658840022318</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001529619352196865</v>
+        <v>0.0003713926271153301</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2680127065233666</v>
+        <v>0.2102993797330091</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="14">
@@ -945,31 +945,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0002944702810060399</v>
+        <v>0.0002653077650617428</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001608220600207737</v>
+        <v>0.001670788762225316</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>7.325294506478341e-05</v>
+        <v>0.0001214139411114035</v>
       </c>
       <c r="H14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.843235841284093</v>
+        <v>0.5913076670343078</v>
       </c>
       <c r="J14" t="n">
         <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -978,32 +978,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005581832467282384</v>
+        <v>0.0002802875274942336</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005753573624328989</v>
+        <v>0.001330236486653077</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003026497551013363</v>
+        <v>0.0001716239216839277</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2031832835351097</v>
+        <v>0.2552694439026277</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K15" t="n">
         <v>16.25</v>
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0007682207633995115</v>
+        <v>0.002701697807286757</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0009936734567571033</v>
+        <v>0.002646968175849742</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001005435566608925</v>
+        <v>-7.159233054340186e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I16" t="n">
-        <v>0.141599339793979</v>
+        <v>0.8068634900832006</v>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -1052,32 +1052,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002886182563130571</v>
+        <v>0.0007793803402373105</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002679453698458627</v>
+        <v>0.001065731735818191</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0002476561263153654</v>
+        <v>8.792114628443093e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9968591896377172</v>
+        <v>0.1142378946588831</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
         <v>17.75</v>
@@ -1093,31 +1093,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00064037491702989</v>
+        <v>0.0005057072382968386</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0007341646200798267</v>
+        <v>0.001182958538978182</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>1.475127075225568e-05</v>
+        <v>-5.105894637469355e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2231802573544841</v>
+        <v>0.2429740107274019</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>19.75</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="19">
@@ -1130,31 +1130,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004090822092578022</v>
+        <v>0.0004523097060686619</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0005938799435931378</v>
+        <v>0.0007324938894881081</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>7.51167205239267e-05</v>
+        <v>0.0001321039942656199</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1587709816647886</v>
+        <v>0.1077071466686097</v>
       </c>
       <c r="J19" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>21</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001185263719407358</v>
+        <v>0.0004078805259264197</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0009920751080023354</v>
+        <v>0.0004516600996286941</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>5.29586757816336e-05</v>
+        <v>8.593794349395222e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07951115201995407</v>
+        <v>0.1301270971527879</v>
       </c>
       <c r="J20" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004182502430682502</v>
+        <v>0.000403395323502312</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0003960475015691421</v>
+        <v>0.0004206830033535337</v>
       </c>
       <c r="F21" t="n">
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2408608076292e-05</v>
+        <v>4.073934206418883e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1499236532073862</v>
+        <v>0.1471659955571996</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004071574005070125</v>
+        <v>0.0003690440611496681</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0003041679440847097</v>
+        <v>0.0002893802531270894</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>5.855107534626924e-05</v>
+        <v>2.731557529442874e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1493719011629593</v>
+        <v>0.1957813546346203</v>
       </c>
       <c r="J22" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>24</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004266799322393587</v>
+        <v>0.0004043506940899511</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002886609689897829</v>
+        <v>0.0002980767494984981</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>2.228985867064326e-05</v>
+        <v>1.7556905478322e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1957830607978728</v>
+        <v>0.14754127066016</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" t="n">
-        <v>24.25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.894344728654669e-05</v>
+        <v>0.001208727117400267</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0007960865176047714</v>
+        <v>0.0008763349563827641</v>
       </c>
       <c r="F24" t="n">
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>2.824206781839589e-05</v>
+        <v>-4.703411712991823e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2364750138504186</v>
+        <v>0.08944913025642398</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>26.25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="25">
@@ -1352,31 +1352,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003900859873871865</v>
+        <v>0.0003215492859344674</v>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000294270837652906</v>
+        <v>0.0003054777829877038</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>5.532496698883449e-05</v>
+        <v>4.255398592509785e-05</v>
       </c>
       <c r="H25" t="n">
         <v>19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09677789336238218</v>
+        <v>0.1107850262028252</v>
       </c>
       <c r="J25" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>28.25</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.630606897554129e-05</v>
+        <v>0.0003165551200612789</v>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00076598115109719</v>
+        <v>0.0002417902342040286</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>2.159328692732388e-05</v>
+        <v>4.174844017821311e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2357135238578496</v>
+        <v>0.1471304004695173</v>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>28.25</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003292534638235924</v>
+        <v>7.397080698261438e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0006001673178206944</v>
+        <v>0.0008689963662404777</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>-9.79245142200158e-05</v>
+        <v>2.521327939198903e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1786956032887064</v>
+        <v>0.1902758747175912</v>
       </c>
       <c r="J27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>29.75</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003909137986629653</v>
+        <v>7.690559978830481e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0002329365121236286</v>
+        <v>0.0007659739879395197</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>2.147234116807173e-05</v>
+        <v>1.612708750226011e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1461564347318935</v>
+        <v>0.1711370859094126</v>
       </c>
       <c r="J28" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>29.75</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002946421161636714</v>
+        <v>0.0002604295756068635</v>
       </c>
       <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0002712595222667998</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.641385675950738e-05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1299078641209057</v>
+      </c>
+      <c r="J29" t="n">
         <v>28</v>
       </c>
-      <c r="E29" t="n">
-        <v>0.0003749091419610152</v>
-      </c>
-      <c r="F29" t="n">
-        <v>26</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.957636883188508e-05</v>
-      </c>
-      <c r="H29" t="n">
-        <v>25</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09333954918326937</v>
-      </c>
-      <c r="J29" t="n">
-        <v>42</v>
-      </c>
       <c r="K29" t="n">
-        <v>30.25</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002521542320226248</v>
+        <v>0.0003420062886621227</v>
       </c>
       <c r="D30" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0001840748891843003</v>
+        <v>0.0001883828094131394</v>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
-        <v>7.841594983123423e-05</v>
+        <v>4.903678078282958e-06</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1348959181405722</v>
+        <v>0.1479960569991445</v>
       </c>
       <c r="J30" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="K30" t="n">
-        <v>30.75</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002751771056297094</v>
+        <v>0.0003048981208460142</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0002780510057352769</v>
+        <v>0.0003543421399181286</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G31" t="n">
-        <v>4.644465675408549e-05</v>
+        <v>-3.951582136071386e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1055202396413497</v>
+        <v>0.2134376731829786</v>
       </c>
       <c r="J31" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K31" t="n">
-        <v>30.75</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.107003209822167e-05</v>
+        <v>0.0005657610149501117</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001537153584875766</v>
+        <v>0.0002582400865463695</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>-6.04862735713585e-06</v>
+        <v>-2.314953044951773e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1707544587680432</v>
+        <v>0.09673555695449876</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K32" t="n">
-        <v>31</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0005474636811603711</v>
+        <v>0.0003213782488106037</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000298682041584456</v>
+        <v>0.0002432338739456334</v>
       </c>
       <c r="F33" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>-2.586766987557887e-05</v>
+        <v>-8.670828243894091e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1221102006732759</v>
+        <v>0.1958019766982275</v>
       </c>
       <c r="J33" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0004976066404976792</v>
+        <v>6.505301077455776e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0002558941964679858</v>
+        <v>0.001399623245753354</v>
       </c>
       <c r="F34" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0001888985741648974</v>
+        <v>-6.05583248360908e-06</v>
       </c>
       <c r="H34" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1652770224911846</v>
+        <v>0.1214339320950062</v>
       </c>
       <c r="J34" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K34" t="n">
-        <v>31.75</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0003830628266531956</v>
+        <v>0.0002654677369844531</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000180298276363558</v>
+        <v>0.0003021859458919988</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G35" t="n">
-        <v>-5.421508224590088e-06</v>
+        <v>6.263717936794144e-06</v>
       </c>
       <c r="H35" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1925205334070608</v>
+        <v>0.087624953920451</v>
       </c>
       <c r="J35" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="K35" t="n">
-        <v>32.25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -1759,31 +1759,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0002398687408691055</v>
+        <v>0.0002341925729293735</v>
       </c>
       <c r="D36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0002430422942303231</v>
+        <v>0.0002022542739255145</v>
       </c>
       <c r="F36" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.727999246934342e-05</v>
+        <v>-9.162387754613199e-07</v>
       </c>
       <c r="H36" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="I36" t="n">
-        <v>0.206042605746664</v>
+        <v>0.16122192641236</v>
       </c>
       <c r="J36" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>34</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002912269097378063</v>
+        <v>0.0002751731629187985</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0003470098968722277</v>
+        <v>0.0003326441258727966</v>
       </c>
       <c r="F37" t="n">
         <v>27</v>
       </c>
       <c r="G37" t="n">
-        <v>-7.835917637154522e-05</v>
+        <v>-3.15504134551281e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1426675686584642</v>
+        <v>0.1029656032469943</v>
       </c>
       <c r="J37" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K37" t="n">
-        <v>34.25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0002579590734871167</v>
+        <v>0.0003221144683825916</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0002504882483320145</v>
+        <v>0.0002404243134378276</v>
       </c>
       <c r="F38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G38" t="n">
-        <v>3.810816755548396e-05</v>
+        <v>-2.92481468815442e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06525408048085124</v>
+        <v>0.1026725904342158</v>
       </c>
       <c r="J38" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="K38" t="n">
-        <v>34.25</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0002491653832428795</v>
+        <v>8.876224140878438e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0003060744594260856</v>
+        <v>0.0004722700057947649</v>
       </c>
       <c r="F39" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.351283128954162e-05</v>
+        <v>3.495879729875639e-06</v>
       </c>
       <c r="H39" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1391609698191743</v>
+        <v>0.03428089609839091</v>
       </c>
       <c r="J39" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K39" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8.728350352817404e-05</v>
+        <v>0.0004632163977099433</v>
       </c>
       <c r="D40" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000626076574427717</v>
+        <v>0.0002240733036846782</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>9.503347152983731e-06</v>
+        <v>-0.0002221778104696814</v>
       </c>
       <c r="H40" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I40" t="n">
-        <v>0.020601990187056</v>
+        <v>0.1062313428240609</v>
       </c>
       <c r="J40" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K40" t="n">
-        <v>37.25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002343322341740696</v>
+        <v>0.0002681110978138219</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>0.000196870791204119</v>
+        <v>0.0002907647771068084</v>
       </c>
       <c r="F41" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G41" t="n">
-        <v>-6.179572673861155e-05</v>
+        <v>-2.240409385209086e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1618468036499907</v>
+        <v>0.03341579694077312</v>
       </c>
       <c r="J41" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K41" t="n">
-        <v>37.75</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0001644768478988834</v>
+        <v>0.0002448766988373972</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>0.000242006138068137</v>
+        <v>0.0002077091998718574</v>
       </c>
       <c r="F42" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>3.02461454677494e-05</v>
+        <v>-3.738914359018297e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="I42" t="n">
-        <v>0.05715079294994618</v>
+        <v>0.1220322635174351</v>
       </c>
       <c r="J42" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0002377479275142439</v>
+        <v>0.0002095847207526698</v>
       </c>
       <c r="D43" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0002116225599470462</v>
+        <v>0.0001555529762327496</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G43" t="n">
-        <v>-7.464296639825285e-05</v>
+        <v>3.40641085841975e-06</v>
       </c>
       <c r="H43" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1456793987127565</v>
+        <v>0.08510757614392039</v>
       </c>
       <c r="J43" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K43" t="n">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.000198203740831712</v>
+        <v>0.0002553428017997986</v>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001813860060519051</v>
+        <v>0.0002092501790068323</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G44" t="n">
-        <v>1.436338466879183e-05</v>
+        <v>-2.014887607815208e-06</v>
       </c>
       <c r="H44" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09813417184463846</v>
+        <v>0.02686938527320182</v>
       </c>
       <c r="J44" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>38.75</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="45">
@@ -2092,31 +2092,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0002341166204347321</v>
+        <v>0.0001901943927653888</v>
       </c>
       <c r="D45" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001631995498436024</v>
+        <v>0.0001580952325513216</v>
       </c>
       <c r="F45" t="n">
+        <v>44</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-3.208803637063662e-05</v>
+      </c>
+      <c r="H45" t="n">
         <v>46</v>
       </c>
-      <c r="G45" t="n">
-        <v>1.452768611420741e-06</v>
-      </c>
-      <c r="H45" t="n">
-        <v>35</v>
-      </c>
       <c r="I45" t="n">
-        <v>0.1019458773657425</v>
+        <v>0.1131622911198775</v>
       </c>
       <c r="J45" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K45" t="n">
-        <v>39.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
@@ -2125,35 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0002452326659973242</v>
+        <v>0.0001366122827683942</v>
       </c>
       <c r="D46" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0002512080601245316</v>
+        <v>9.854451162539894e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.598813033288904e-05</v>
+        <v>6.540573459712373e-06</v>
       </c>
       <c r="H46" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07554720522443992</v>
+        <v>0.07784304879969328</v>
       </c>
       <c r="J46" t="n">
         <v>45</v>
       </c>
       <c r="K46" t="n">
-        <v>39.75</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="47">
@@ -2162,29 +2162,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0001462709729975095</v>
+        <v>0.0002205826903911296</v>
       </c>
       <c r="D47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0001043026151371769</v>
+        <v>0.000222129825404503</v>
       </c>
       <c r="F47" t="n">
+        <v>39</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-5.748719285413318e-05</v>
+      </c>
+      <c r="H47" t="n">
         <v>49</v>
       </c>
-      <c r="G47" t="n">
-        <v>8.436790474319888e-06</v>
-      </c>
-      <c r="H47" t="n">
-        <v>34</v>
-      </c>
       <c r="I47" t="n">
-        <v>0.09430905966686209</v>
+        <v>0.08788530601202416</v>
       </c>
       <c r="J47" t="n">
         <v>41</v>
@@ -2199,35 +2199,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0002130685956627212</v>
+        <v>7.506688267847946e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E48" t="n">
-        <v>9.747146222328386e-05</v>
+        <v>0.0001034278042927943</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G48" t="n">
-        <v>-7.143576778112503e-07</v>
+        <v>1.916612153399777e-05</v>
       </c>
       <c r="H48" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.08603500859574087</v>
+        <v>0.02907315417629119</v>
       </c>
       <c r="J48" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K48" t="n">
-        <v>42.75</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
@@ -2236,32 +2236,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.694215915596535e-05</v>
+        <v>0.0001974076638096041</v>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0001708630312780224</v>
+        <v>0.0001254575048111429</v>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G49" t="n">
-        <v>1.35237771476282e-05</v>
+        <v>-0.0001153350793199892</v>
       </c>
       <c r="H49" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I49" t="n">
-        <v>0.03890270057521183</v>
+        <v>0.1065366655791227</v>
       </c>
       <c r="J49" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
         <v>43.5</v>
@@ -2273,35 +2273,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0002008403108520613</v>
+        <v>6.965077812365236e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0001256065543468434</v>
+        <v>0.0001115110041910677</v>
       </c>
       <c r="F50" t="n">
         <v>47</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.0001082205470914088</v>
+        <v>2.333098037632375e-06</v>
       </c>
       <c r="H50" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1111892772634375</v>
+        <v>0.06408156581287239</v>
       </c>
       <c r="J50" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K50" t="n">
-        <v>43.75</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="51">
@@ -2310,35 +2310,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.284823813362488e-05</v>
+        <v>0.0001796341241109861</v>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0001227173258486162</v>
+        <v>0.0001013191853664384</v>
       </c>
       <c r="F51" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-5.838369691557599e-06</v>
+        <v>-6.182965407941499e-06</v>
       </c>
       <c r="H51" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I51" t="n">
-        <v>0.03499447622261265</v>
+        <v>0.08188351724165344</v>
       </c>
       <c r="J51" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K51" t="n">
-        <v>46.25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
@@ -2351,31 +2351,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4.855094616615176e-06</v>
+        <v>5.432341154503717e-06</v>
       </c>
       <c r="D52" t="n">
         <v>53</v>
       </c>
       <c r="E52" t="n">
-        <v>5.445202767085317e-05</v>
+        <v>5.725891521908949e-05</v>
       </c>
       <c r="F52" t="n">
         <v>51</v>
       </c>
       <c r="G52" t="n">
-        <v>6.953063436565543e-07</v>
+        <v>7.726373676852915e-07</v>
       </c>
       <c r="H52" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.01374888500033489</v>
+        <v>0.005891922780134173</v>
       </c>
       <c r="J52" t="n">
         <v>51</v>
       </c>
       <c r="K52" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
@@ -2388,22 +2388,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7.250526481278343e-06</v>
+        <v>1.136232410642219e-05</v>
       </c>
       <c r="D53" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E53" t="n">
-        <v>1.475558383849283e-05</v>
+        <v>1.890476486443773e-05</v>
       </c>
       <c r="F53" t="n">
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>9.784998548312275e-07</v>
+        <v>1.102212534354052e-07</v>
       </c>
       <c r="H53" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>52</v>
       </c>
       <c r="K53" t="n">
-        <v>48.25</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="54">
@@ -2425,22 +2425,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.236697623228188e-06</v>
+        <v>8.698675467773773e-06</v>
       </c>
       <c r="D54" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E54" t="n">
-        <v>1.911154645240304e-05</v>
+        <v>1.942895088559494e-05</v>
       </c>
       <c r="F54" t="n">
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.668896820428145e-06</v>
+        <v>-6.67839771288925e-06</v>
       </c>
       <c r="H54" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>52</v>
       </c>
       <c r="K54" t="n">
-        <v>48.5</v>
+        <v>49.25</v>
       </c>
     </row>
   </sheetData>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4934769756689703</v>
+        <v>0.4977888743490059</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.338895164192504</v>
+        <v>0.3555639308574666</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4212471361590847</v>
+        <v>0.4275278758199269</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.460851653841713</v>
+        <v>1.212438164413909</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -2570,31 +2570,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1566035309348527</v>
+        <v>0.1705570914101155</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2249426078247836</v>
+        <v>0.2190170715818167</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.143955827412041</v>
+        <v>0.1547372651050634</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.472804594688848</v>
+        <v>1.231562346339471</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2607,31 +2607,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1635813081454697</v>
+        <v>0.1493154822576961</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2073766001947369</v>
+        <v>0.1945990500210734</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09376222928743319</v>
+        <v>0.08337686689426374</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.418653016452894</v>
+        <v>1.071602712577556</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2644,31 +2644,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07655031662667959</v>
+        <v>0.09109327576136467</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1652371240146799</v>
+        <v>0.1704639022676688</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02010834142406271</v>
+        <v>0.02625494934165764</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8672166885734174</v>
+        <v>0.6647508870541099</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -2681,31 +2681,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.09093983284067626</v>
+        <v>0.07266127677126222</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009249262636788309</v>
+        <v>0.009783522296471749</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02654435833171039</v>
+        <v>0.01662492513450207</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8339964500456545</v>
+        <v>0.550538439464701</v>
       </c>
       <c r="J6" t="n">
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -2718,31 +2718,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0006623874105793368</v>
+        <v>0.0007103842065014464</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01082545318724312</v>
+        <v>0.01008863850085699</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007410061135762784</v>
+        <v>0.0009065309642399915</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9731716775514923</v>
+        <v>0.6663908335330178</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2755,25 +2755,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001030879111032006</v>
+        <v>0.001106154337122481</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01823310073242509</v>
+        <v>0.01507350619875696</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001191792659991686</v>
+        <v>0.001183796798163073</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3412892129988085</v>
+        <v>0.3335482345837661</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0007530530725082443</v>
+        <v>0.0006782722832782091</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001077156610443113</v>
+        <v>0.00107945562607117</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001611350279293711</v>
+        <v>0.0001071084214119389</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.744186914584263</v>
+        <v>0.4648439152564756</v>
       </c>
       <c r="J9" t="n">
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="10">
@@ -2829,31 +2829,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0004999010613522326</v>
+        <v>0.0004998411828986698</v>
       </c>
       <c r="D10" t="n">
         <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001123066054036514</v>
+        <v>0.001375017038606483</v>
       </c>
       <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.000151267789462084</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2547847995899231</v>
+      </c>
+      <c r="J10" t="n">
         <v>13</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0001458349710713014</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2413980955877375</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>13.75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002950139211836122</v>
+        <v>0.0003127567702813812</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001892574032144988</v>
+        <v>0.001910325373208544</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001873242169758371</v>
+        <v>0.0001997195509044092</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2779894243050682</v>
+        <v>0.2587939072850545</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="12">
@@ -2903,28 +2903,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0005889879807100593</v>
+        <v>0.0005909537916020339</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001081133185744966</v>
+        <v>0.001058674853744491</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>5.026650528265897e-05</v>
+        <v>6.458258715732467e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2431577677377081</v>
+        <v>0.2408108237229087</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>15.25</v>
@@ -2936,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0002973423066116075</v>
+        <v>0.0005375576450263882</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00137428593249932</v>
+        <v>0.0004710658840022318</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001529619352196865</v>
+        <v>0.0003713926271153301</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2680127065233666</v>
+        <v>0.2102993797330091</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="14">
@@ -2977,31 +2977,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0002944702810060399</v>
+        <v>0.0002653077650617428</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001608220600207737</v>
+        <v>0.001670788762225316</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>7.325294506478341e-05</v>
+        <v>0.0001214139411114035</v>
       </c>
       <c r="H14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.843235841284093</v>
+        <v>0.5913076670343078</v>
       </c>
       <c r="J14" t="n">
         <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005581832467282384</v>
+        <v>0.0002802875274942336</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005753573624328989</v>
+        <v>0.001330236486653077</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003026497551013363</v>
+        <v>0.0001716239216839277</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2031832835351097</v>
+        <v>0.2552694439026277</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K15" t="n">
         <v>16.25</v>
@@ -3047,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0007682207633995115</v>
+        <v>0.002701697807286757</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0009936734567571033</v>
+        <v>0.002646968175849742</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001005435566608925</v>
+        <v>-7.159233054340186e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I16" t="n">
-        <v>0.141599339793979</v>
+        <v>0.8068634900832006</v>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -3084,32 +3084,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002886182563130571</v>
+        <v>0.0007793803402373105</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002679453698458627</v>
+        <v>0.001065731735818191</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0002476561263153654</v>
+        <v>8.792114628443093e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9968591896377172</v>
+        <v>0.1142378946588831</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
         <v>17.75</v>
@@ -3125,31 +3125,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00064037491702989</v>
+        <v>0.0005057072382968386</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0007341646200798267</v>
+        <v>0.001182958538978182</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>1.475127075225568e-05</v>
+        <v>-5.105894637469355e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2231802573544841</v>
+        <v>0.2429740107274019</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>19.75</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="19">
@@ -3162,31 +3162,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004090822092578022</v>
+        <v>0.0004523097060686619</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0005938799435931378</v>
+        <v>0.0007324938894881081</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>7.51167205239267e-05</v>
+        <v>0.0001321039942656199</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1587709816647886</v>
+        <v>0.1077071466686097</v>
       </c>
       <c r="J19" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>21</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001185263719407358</v>
+        <v>0.0004078805259264197</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0009920751080023354</v>
+        <v>0.0004516600996286941</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>5.29586757816336e-05</v>
+        <v>8.593794349395222e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07951115201995407</v>
+        <v>0.1301270971527879</v>
       </c>
       <c r="J20" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004182502430682502</v>
+        <v>0.000403395323502312</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0003960475015691421</v>
+        <v>0.0004206830033535337</v>
       </c>
       <c r="F21" t="n">
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2408608076292e-05</v>
+        <v>4.073934206418883e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1499236532073862</v>
+        <v>0.1471659955571996</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4934769756689703</v>
+        <v>0.4977888743490059</v>
       </c>
     </row>
     <row r="3">
@@ -3313,11 +3313,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1635813081454697</v>
+        <v>0.1705570914101155</v>
       </c>
     </row>
     <row r="4">
@@ -3326,11 +3326,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1566035309348527</v>
+        <v>0.1493154822576961</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09093983284067626</v>
+        <v>0.09109327576136467</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3352,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.07655031662667959</v>
+        <v>0.07266127677126222</v>
       </c>
     </row>
     <row r="7">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002886182563130571</v>
+        <v>0.002701697807286757</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001185263719407358</v>
+        <v>0.001208727117400267</v>
       </c>
     </row>
     <row r="9">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001030879111032006</v>
+        <v>0.001106154337122481</v>
       </c>
     </row>
     <row r="10">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0007682207633995115</v>
+        <v>0.0007793803402373105</v>
       </c>
     </row>
     <row r="11">
@@ -3417,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0007530530725082443</v>
+        <v>0.0007103842065014464</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0006623874105793368</v>
+        <v>0.0006782722832782091</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00064037491702989</v>
+        <v>0.0005909537916020339</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0005889879807100593</v>
+        <v>0.0005657610149501117</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005581832467282384</v>
+        <v>0.0005375576450263882</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005474636811603711</v>
+        <v>0.0005057072382968386</v>
       </c>
     </row>
     <row r="17">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0004999010613522326</v>
+        <v>0.0004998411828986698</v>
       </c>
     </row>
     <row r="18">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0004976066404976792</v>
+        <v>0.0004632163977099433</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004266799322393587</v>
+        <v>0.0004523097060686619</v>
       </c>
     </row>
     <row r="20">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004182502430682502</v>
+        <v>0.0004078805259264197</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004090822092578022</v>
+        <v>0.0004043506940899511</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004071574005070125</v>
+        <v>0.000403395323502312</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003909137986629653</v>
+        <v>0.0003690440611496681</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003900859873871865</v>
+        <v>0.0003420062886621227</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003830628266531956</v>
+        <v>0.0003221144683825916</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3612,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003292534638235924</v>
+        <v>0.0003215492859344674</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3625,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002973423066116075</v>
+        <v>0.0003213782488106037</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002950139211836122</v>
+        <v>0.0003165551200612789</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002946421161636714</v>
+        <v>0.0003127567702813812</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3664,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002944702810060399</v>
+        <v>0.0003048981208460142</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3677,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002912269097378063</v>
+        <v>0.0002802875274942336</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002751771056297094</v>
+        <v>0.0002751731629187985</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002579590734871167</v>
+        <v>0.0002681110978138219</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3716,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0002521542320226248</v>
+        <v>0.0002654677369844531</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3729,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0002491653832428795</v>
+        <v>0.0002653077650617428</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0002452326659973242</v>
+        <v>0.0002604295756068635</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002398687408691055</v>
+        <v>0.0002553428017997986</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0002377479275142439</v>
+        <v>0.0002448766988373972</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0002343322341740696</v>
+        <v>0.0002341925729293735</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3794,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0002341166204347321</v>
+        <v>0.0002205826903911296</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3807,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002130685956627212</v>
+        <v>0.0002095847207526698</v>
       </c>
     </row>
     <row r="42">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0002008403108520613</v>
+        <v>0.0001974076638096041</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3833,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.000198203740831712</v>
+        <v>0.0001901943927653888</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0001644768478988834</v>
+        <v>0.0001796341241109861</v>
       </c>
     </row>
     <row r="45">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0001462709729975095</v>
+        <v>0.0001366122827683942</v>
       </c>
     </row>
     <row r="46">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.728350352817404e-05</v>
+        <v>8.876224140878438e-05</v>
       </c>
     </row>
     <row r="47">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7.894344728654669e-05</v>
+        <v>7.690559978830481e-05</v>
       </c>
     </row>
     <row r="48">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7.284823813362488e-05</v>
+        <v>7.506688267847946e-05</v>
       </c>
     </row>
     <row r="49">
@@ -3911,11 +3911,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7.107003209822167e-05</v>
+        <v>7.397080698261438e-05</v>
       </c>
     </row>
     <row r="50">
@@ -3924,11 +3924,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6.694215915596535e-05</v>
+        <v>6.965077812365236e-05</v>
       </c>
     </row>
     <row r="51">
@@ -3937,11 +3937,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.630606897554129e-05</v>
+        <v>6.505301077455776e-05</v>
       </c>
     </row>
     <row r="52">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.236697623228188e-06</v>
+        <v>1.136232410642219e-05</v>
       </c>
     </row>
     <row r="53">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7.250526481278343e-06</v>
+        <v>8.698675467773773e-06</v>
       </c>
     </row>
     <row r="54">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.855094616615176e-06</v>
+        <v>5.432341154503717e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.338895164192504</v>
+        <v>0.3555639308574666</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2249426078247836</v>
+        <v>0.2190170715818167</v>
       </c>
     </row>
     <row r="4">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2073766001947369</v>
+        <v>0.1945990500210734</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1652371240146799</v>
+        <v>0.1704639022676688</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01823310073242509</v>
+        <v>0.01507350619875696</v>
       </c>
     </row>
     <row r="7">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01082545318724312</v>
+        <v>0.01008863850085699</v>
       </c>
     </row>
     <row r="8">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009249262636788309</v>
+        <v>0.009783522296471749</v>
       </c>
     </row>
     <row r="9">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002679453698458627</v>
+        <v>0.002646968175849742</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001892574032144988</v>
+        <v>0.001910325373208544</v>
       </c>
     </row>
     <row r="11">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001608220600207737</v>
+        <v>0.001670788762225316</v>
       </c>
     </row>
     <row r="12">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001537153584875766</v>
+        <v>0.001399623245753354</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00137428593249932</v>
+        <v>0.001375017038606483</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001123066054036514</v>
+        <v>0.001330236486653077</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001081133185744966</v>
+        <v>0.001182958538978182</v>
       </c>
     </row>
     <row r="16">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001077156610443113</v>
+        <v>0.00107945562607117</v>
       </c>
     </row>
     <row r="17">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0009936734567571033</v>
+        <v>0.001065731735818191</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009920751080023354</v>
+        <v>0.001058674853744491</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0007960865176047714</v>
+        <v>0.0008763349563827641</v>
       </c>
     </row>
     <row r="20">
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00076598115109719</v>
+        <v>0.0008689963662404777</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0007341646200798267</v>
+        <v>0.0007659739879395197</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.000626076574427717</v>
+        <v>0.0007324938894881081</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0006001673178206944</v>
+        <v>0.0004722700057947649</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0005938799435931378</v>
+        <v>0.0004710658840022318</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0005753573624328989</v>
+        <v>0.0004516600996286941</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003960475015691421</v>
+        <v>0.0004206830033535337</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003749091419610152</v>
+        <v>0.0003543421399181286</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003470098968722277</v>
+        <v>0.0003326441258727966</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0003060744594260856</v>
+        <v>0.0003054777829877038</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003041679440847097</v>
+        <v>0.0003021859458919988</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.000298682041584456</v>
+        <v>0.0002980767494984981</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000294270837652906</v>
+        <v>0.0002907647771068084</v>
       </c>
     </row>
     <row r="33">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002886609689897829</v>
+        <v>0.0002893802531270894</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0002780510057352769</v>
+        <v>0.0002712595222667998</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0002558941964679858</v>
+        <v>0.0002582400865463695</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0002512080601245316</v>
+        <v>0.0002432338739456334</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002504882483320145</v>
+        <v>0.0002417902342040286</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0002430422942303231</v>
+        <v>0.0002404243134378276</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4501,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.000242006138068137</v>
+        <v>0.0002240733036846782</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4514,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0002329365121236286</v>
+        <v>0.000222129825404503</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4527,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002116225599470462</v>
+        <v>0.0002092501790068323</v>
       </c>
     </row>
     <row r="42">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.000196870791204119</v>
+        <v>0.0002077091998718574</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0001840748891843003</v>
+        <v>0.0002022542739255145</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4566,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0001813860060519051</v>
+        <v>0.0001883828094131394</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.000180298276363558</v>
+        <v>0.0001580952325513216</v>
       </c>
     </row>
     <row r="46">
@@ -4592,11 +4592,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0001708630312780224</v>
+        <v>0.0001555529762327496</v>
       </c>
     </row>
     <row r="47">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0001631995498436024</v>
+        <v>0.0001254575048111429</v>
       </c>
     </row>
     <row r="48">
@@ -4618,11 +4618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0001256065543468434</v>
+        <v>0.0001115110041910677</v>
       </c>
     </row>
     <row r="49">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0001227173258486162</v>
+        <v>0.0001034278042927943</v>
       </c>
     </row>
     <row r="50">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0001043026151371769</v>
+        <v>0.0001013191853664384</v>
       </c>
     </row>
     <row r="51">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9.747146222328386e-05</v>
+        <v>9.854451162539894e-05</v>
       </c>
     </row>
     <row r="52">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.445202767085317e-05</v>
+        <v>5.725891521908949e-05</v>
       </c>
     </row>
     <row r="53">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.911154645240304e-05</v>
+        <v>1.942895088559494e-05</v>
       </c>
     </row>
     <row r="54">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.475558383849283e-05</v>
+        <v>1.890476486443773e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4212471361590847</v>
+        <v>0.4275278758199269</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03611059365480114</v>
+        <v>0.03550831053475043</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.143955827412041</v>
+        <v>0.1547372651050634</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007766359280475725</v>
+        <v>0.007585522874415529</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09376222928743319</v>
+        <v>0.08337686689426374</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006483763428301178</v>
+        <v>0.006168871607691502</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02654435833171039</v>
+        <v>0.02625494934165764</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003979485304965487</v>
+        <v>0.003888841631173515</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02010834142406271</v>
+        <v>0.01662492513450207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003118027567508811</v>
+        <v>0.002830197896181445</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001191792659991686</v>
+        <v>0.001183796798163073</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001049422604976825</v>
+        <v>9.264444868287794e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0007410061135762784</v>
+        <v>0.0009065309642399915</v>
       </c>
       <c r="D8" t="n">
-        <v>7.78830363693586e-06</v>
+        <v>8.551896153054946e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003026497551013363</v>
+        <v>0.0003713926271153301</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001093109383231348</v>
+        <v>0.0001100944661529354</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001873242169758371</v>
+        <v>0.0001997195509044092</v>
       </c>
       <c r="D10" t="n">
-        <v>7.092128871523098e-05</v>
+        <v>6.949015172659392e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0001611350279293711</v>
+        <v>0.0001716239216839277</v>
       </c>
       <c r="D11" t="n">
-        <v>6.319311393788344e-05</v>
+        <v>6.954159173446452e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0001529619352196865</v>
+        <v>0.000151267789462084</v>
       </c>
       <c r="D12" t="n">
-        <v>5.464644704515823e-05</v>
+        <v>6.712967861880868e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0001458349710713014</v>
+        <v>0.0001321039942656199</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000105652772163094</v>
+        <v>2.584794060076915e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0001005435566608925</v>
+        <v>0.0001214139411114035</v>
       </c>
       <c r="D14" t="n">
-        <v>6.082226906787357e-05</v>
+        <v>4.654010032356979e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.841594983123423e-05</v>
+        <v>0.0001071084214119389</v>
       </c>
       <c r="D15" t="n">
-        <v>2.844185382380329e-05</v>
+        <v>8.690073980559234e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.51167205239267e-05</v>
+        <v>8.792114628443093e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>1.992765721385495e-05</v>
+        <v>5.947570701509682e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.325294506478341e-05</v>
+        <v>8.593794349395222e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>6.149274280194455e-05</v>
+        <v>5.649686260959632e-05</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.2408608076292e-05</v>
+        <v>6.458258715732467e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>7.281152153062162e-05</v>
+        <v>5.005957946790429e-05</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.855107534626924e-05</v>
+        <v>5.641385675950738e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>5.592748114504927e-05</v>
+        <v>2.228212941223416e-05</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.532496698883449e-05</v>
+        <v>4.255398592509785e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>4.316451186386958e-05</v>
+        <v>3.306726163051698e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.29586757816336e-05</v>
+        <v>4.174844017821311e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0005930640440957069</v>
+        <v>6.216704953096202e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.026650528265897e-05</v>
+        <v>4.073934206418883e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>4.572340696400091e-05</v>
+        <v>3.180255036780966e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.644465675408549e-05</v>
+        <v>2.731557529442874e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>1.984606585794202e-05</v>
+        <v>7.713035803174252e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.810816755548396e-05</v>
+        <v>2.521327939198903e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>2.882957767400429e-05</v>
+        <v>1.167913747057947e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.02461454677494e-05</v>
+        <v>1.916612153399777e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.80210151407425e-05</v>
+        <v>1.702656900939287e-05</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.957636883188508e-05</v>
+        <v>1.7556905478322e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>2.78548019230335e-05</v>
+        <v>4.201143414976832e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.824206781839589e-05</v>
+        <v>1.612708750226011e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.944608570740266e-05</v>
+        <v>1.383780085513268e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.228985867064326e-05</v>
+        <v>6.540573459712373e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>9.070145746245526e-05</v>
+        <v>1.210792919676313e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.159328692732388e-05</v>
+        <v>6.263717936794144e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>6.561987688814561e-06</v>
+        <v>2.661511124307446e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.147234116807173e-05</v>
+        <v>4.903678078282958e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>3.956073450679267e-05</v>
+        <v>0.0001315005443876463</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.475127075225568e-05</v>
+        <v>3.495879729875639e-06</v>
       </c>
       <c r="D31" t="n">
-        <v>3.734881352668717e-05</v>
+        <v>5.816398148777523e-07</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.436338466879183e-05</v>
+        <v>3.40641085841975e-06</v>
       </c>
       <c r="D32" t="n">
-        <v>3.513180728832451e-05</v>
+        <v>6.861140601515437e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.35237771476282e-05</v>
+        <v>2.333098037632375e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>1.052067573590642e-05</v>
+        <v>1.344812316134969e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9.503347152983731e-06</v>
+        <v>7.726373676852915e-07</v>
       </c>
       <c r="D34" t="n">
-        <v>5.835026794025116e-07</v>
+        <v>6.249980597893795e-07</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8.436790474319888e-06</v>
+        <v>1.102212534354052e-07</v>
       </c>
       <c r="D35" t="n">
-        <v>1.30315678312168e-05</v>
+        <v>1.252178067890837e-07</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.452768611420741e-06</v>
+        <v>-9.162387754613199e-07</v>
       </c>
       <c r="D36" t="n">
-        <v>1.243214661469633e-05</v>
+        <v>4.830560856431495e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9.784998548312275e-07</v>
+        <v>-2.014887607815208e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>1.020906816827111e-06</v>
+        <v>1.324658498492881e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6.953063436565543e-07</v>
+        <v>-4.703411712991823e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>9.064763378067245e-07</v>
+        <v>0.0005463410241920008</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-7.143576778112503e-07</v>
+        <v>-5.105894637469355e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>4.740368019902112e-05</v>
+        <v>3.495626077877415e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-1.668896820428145e-06</v>
+        <v>-6.05583248360908e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>3.279820356534446e-06</v>
+        <v>1.460938618062169e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-5.421508224590088e-06</v>
+        <v>-6.182965407941499e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001564618999997506</v>
+        <v>3.076844158505298e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.838369691557599e-06</v>
+        <v>-6.67839771288925e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.34158485420633e-05</v>
+        <v>9.07070924700926e-06</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-6.04862735713585e-06</v>
+        <v>-2.240409385209086e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>2.41613970214327e-05</v>
+        <v>3.110442438468803e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.351283128954162e-05</v>
+        <v>-2.314953044951773e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>3.568347012171998e-05</v>
+        <v>0.00012310960812805</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1.598813033288904e-05</v>
+        <v>-2.92481468815442e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>4.032776263619629e-05</v>
+        <v>4.659280836759468e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1.727999246934342e-05</v>
+        <v>-3.15504134551281e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>3.19167283085617e-05</v>
+        <v>2.435233876713221e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2.586766987557887e-05</v>
+        <v>-3.208803637063662e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0001254392689678129</v>
+        <v>1.553855684654054e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-6.179572673861155e-05</v>
+        <v>-3.738914359018297e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>4.645697135787311e-05</v>
+        <v>5.200121220848164e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-7.464296639825285e-05</v>
+        <v>-3.951582136071386e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>3.940309874948654e-05</v>
+        <v>3.375271597848838e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-7.835917637154522e-05</v>
+        <v>-5.748719285413318e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>3.012127406408834e-05</v>
+        <v>3.706251298449458e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-9.79245142200158e-05</v>
+        <v>-7.159233054340186e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>6.109844966970093e-05</v>
+        <v>0.0006041521753791865</v>
       </c>
     </row>
     <row r="52">
@@ -5545,14 +5545,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001082205470914088</v>
+        <v>-8.670828243894091e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>7.194541074356519e-05</v>
+        <v>4.386469448239552e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001888985741648974</v>
+        <v>-0.0001153350793199892</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0003757906730581602</v>
+        <v>6.87529426097149e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5577,14 +5577,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0002476561263153654</v>
+        <v>-0.0002221778104696814</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0005951006808222858</v>
+        <v>0.0003531514623099235</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.472804594688848</v>
+        <v>1.231562346339471</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.460851653841713</v>
+        <v>1.212438164413909</v>
       </c>
     </row>
     <row r="4">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.418653016452894</v>
+        <v>1.071602712577556</v>
       </c>
     </row>
     <row r="5">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9968591896377172</v>
+        <v>0.8068634900832006</v>
       </c>
     </row>
     <row r="6">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9731716775514923</v>
+        <v>0.6663908335330178</v>
       </c>
     </row>
     <row r="7">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8672166885734174</v>
+        <v>0.6647508870541099</v>
       </c>
     </row>
     <row r="8">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.843235841284093</v>
+        <v>0.5913076670343078</v>
       </c>
     </row>
     <row r="9">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8339964500456545</v>
+        <v>0.550538439464701</v>
       </c>
     </row>
     <row r="10">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.744186914584263</v>
+        <v>0.4648439152564756</v>
       </c>
     </row>
     <row r="11">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3412892129988085</v>
+        <v>0.3335482345837661</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2779894243050682</v>
+        <v>0.2587939072850545</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2680127065233666</v>
+        <v>0.2552694439026277</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2431577677377081</v>
+        <v>0.2547847995899231</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2413980955877375</v>
+        <v>0.2429740107274019</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2364750138504186</v>
+        <v>0.2408108237229087</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2357135238578496</v>
+        <v>0.2134376731829786</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.2231802573544841</v>
+        <v>0.2102993797330091</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.206042605746664</v>
+        <v>0.1958019766982275</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2031832835351097</v>
+        <v>0.1957813546346203</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1957830607978728</v>
+        <v>0.1902758747175912</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1925205334070608</v>
+        <v>0.1711370859094126</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1786956032887064</v>
+        <v>0.16122192641236</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1707544587680432</v>
+        <v>0.1479960569991445</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5923,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1652770224911846</v>
+        <v>0.14754127066016</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1618468036499907</v>
+        <v>0.1471659955571996</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5949,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1587709816647886</v>
+        <v>0.1471304004695173</v>
       </c>
     </row>
     <row r="28">
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1499236532073862</v>
+        <v>0.1301270971527879</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1493719011629593</v>
+        <v>0.1299078641209057</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1461564347318935</v>
+        <v>0.1220322635174351</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1456793987127565</v>
+        <v>0.1214339320950062</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1426675686584642</v>
+        <v>0.1142378946588831</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.141599339793979</v>
+        <v>0.1131622911198775</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +6040,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1391609698191743</v>
+        <v>0.1107850262028252</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +6053,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1348959181405722</v>
+        <v>0.1077071466686097</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1221102006732759</v>
+        <v>0.1065366655791227</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +6079,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1111892772634375</v>
+        <v>0.1062313428240609</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +6092,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1055202396413497</v>
+        <v>0.1029656032469943</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1019458773657425</v>
+        <v>0.1026725904342158</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.09813417184463846</v>
+        <v>0.09673555695449876</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.09677789336238218</v>
+        <v>0.08944913025642398</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +6144,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.09430905966686209</v>
+        <v>0.08788530601202416</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +6157,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.09333954918326937</v>
+        <v>0.087624953920451</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.08603500859574087</v>
+        <v>0.08510757614392039</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.07951115201995407</v>
+        <v>0.08188351724165344</v>
       </c>
     </row>
     <row r="46">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.07554720522443992</v>
+        <v>0.07784304879969328</v>
       </c>
     </row>
     <row r="47">
@@ -6209,11 +6209,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.06525408048085124</v>
+        <v>0.06408156581287239</v>
       </c>
     </row>
     <row r="48">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.05715079294994618</v>
+        <v>0.03428089609839091</v>
       </c>
     </row>
     <row r="49">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.03890270057521183</v>
+        <v>0.03341579694077312</v>
       </c>
     </row>
     <row r="50">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.03499447622261265</v>
+        <v>0.02907315417629119</v>
       </c>
     </row>
     <row r="51">
@@ -6261,11 +6261,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.020601990187056</v>
+        <v>0.02686938527320182</v>
       </c>
     </row>
     <row r="52">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.01374888500033489</v>
+        <v>0.005891922780134173</v>
       </c>
     </row>
     <row r="53">
@@ -6318,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,15 +6334,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>training_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>permutation_rows_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_variables_ranked</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoded_feature_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preprocessing_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_at_utc</t>
         </is>
@@ -6358,14 +6373,25 @@
         <v>788</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E2" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="n">
-        <v>446</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 07:45:41 UTC</t>
+      <c r="F2" t="n">
+        <v>414</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fit_on_training_split_only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:54:30 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4275278758199269</v>
+        <v>0.4275278758199268</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547372651050634</v>
+        <v>0.1547372651050635</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02625494934165764</v>
+        <v>0.02625494934165765</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01662492513450207</v>
+        <v>0.01662492513450205</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009065309642399915</v>
+        <v>0.0009065309642396138</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001183796798163073</v>
+        <v>0.001183796798163061</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -809,7 +809,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000151267789462084</v>
+        <v>0.0001512677894620507</v>
       </c>
       <c r="H10" t="n">
         <v>11</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001997195509044092</v>
+        <v>0.0001997195509044203</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>6.458258715732467e-05</v>
+        <v>6.458258715731357e-05</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -920,7 +920,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003713926271153301</v>
+        <v>0.0003713926271153745</v>
       </c>
       <c r="H13" t="n">
         <v>8</v>
@@ -994,7 +994,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001716239216839277</v>
+        <v>0.0001716239216839166</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.159233054340186e-05</v>
+        <v>-7.159233054339076e-05</v>
       </c>
       <c r="H16" t="n">
         <v>50</v>
@@ -1068,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>8.792114628443093e-05</v>
+        <v>8.792114628441983e-05</v>
       </c>
       <c r="H17" t="n">
         <v>15</v>
@@ -1105,7 +1105,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.105894637469355e-06</v>
+        <v>-5.10589463744715e-06</v>
       </c>
       <c r="H18" t="n">
         <v>38</v>
@@ -1142,7 +1142,7 @@
         <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001321039942656199</v>
+        <v>0.000132103994265631</v>
       </c>
       <c r="H19" t="n">
         <v>12</v>
@@ -1216,7 +1216,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>4.073934206418883e-05</v>
+        <v>4.073934206416663e-05</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>2.731557529442874e-05</v>
+        <v>2.731557529441764e-05</v>
       </c>
       <c r="H22" t="n">
         <v>22</v>
@@ -1290,7 +1290,7 @@
         <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7556905478322e-05</v>
+        <v>1.75569054783109e-05</v>
       </c>
       <c r="H23" t="n">
         <v>25</v>
@@ -1327,7 +1327,7 @@
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.703411712991823e-06</v>
+        <v>-4.703411713002925e-06</v>
       </c>
       <c r="H24" t="n">
         <v>37</v>
@@ -1364,7 +1364,7 @@
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>4.255398592509785e-05</v>
+        <v>4.255398592508675e-05</v>
       </c>
       <c r="H25" t="n">
         <v>19</v>
@@ -1401,7 +1401,7 @@
         <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>4.174844017821311e-05</v>
+        <v>4.174844017820201e-05</v>
       </c>
       <c r="H26" t="n">
         <v>20</v>
@@ -1438,7 +1438,7 @@
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>2.521327939198903e-05</v>
+        <v>2.521327939195572e-05</v>
       </c>
       <c r="H27" t="n">
         <v>23</v>
@@ -1475,7 +1475,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>1.612708750226011e-05</v>
+        <v>1.612708750228231e-05</v>
       </c>
       <c r="H28" t="n">
         <v>26</v>
@@ -1512,7 +1512,7 @@
         <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>5.641385675950738e-05</v>
+        <v>5.641385675948518e-05</v>
       </c>
       <c r="H29" t="n">
         <v>18</v>
@@ -1586,7 +1586,7 @@
         <v>26</v>
       </c>
       <c r="G31" t="n">
-        <v>-3.951582136071386e-05</v>
+        <v>-3.951582136070275e-05</v>
       </c>
       <c r="H31" t="n">
         <v>48</v>
@@ -1660,7 +1660,7 @@
         <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>-8.670828243894091e-05</v>
+        <v>-8.67082824389187e-05</v>
       </c>
       <c r="H33" t="n">
         <v>51</v>
@@ -1734,7 +1734,7 @@
         <v>29</v>
       </c>
       <c r="G35" t="n">
-        <v>6.263717936794144e-06</v>
+        <v>6.263717936783042e-06</v>
       </c>
       <c r="H35" t="n">
         <v>28</v>
@@ -1771,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="G36" t="n">
-        <v>-9.162387754613199e-07</v>
+        <v>-9.162387754724222e-07</v>
       </c>
       <c r="H36" t="n">
         <v>35</v>
@@ -1882,7 +1882,7 @@
         <v>22</v>
       </c>
       <c r="G39" t="n">
-        <v>3.495879729875639e-06</v>
+        <v>3.495879729864537e-06</v>
       </c>
       <c r="H39" t="n">
         <v>30</v>
@@ -1919,7 +1919,7 @@
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0002221778104696814</v>
+        <v>-0.0002221778104696925</v>
       </c>
       <c r="H40" t="n">
         <v>53</v>
@@ -1993,7 +1993,7 @@
         <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.738914359018297e-05</v>
+        <v>-3.738914359020517e-05</v>
       </c>
       <c r="H42" t="n">
         <v>47</v>
@@ -2030,7 +2030,7 @@
         <v>45</v>
       </c>
       <c r="G43" t="n">
-        <v>3.40641085841975e-06</v>
+        <v>3.406410858430853e-06</v>
       </c>
       <c r="H43" t="n">
         <v>31</v>
@@ -2104,7 +2104,7 @@
         <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>-3.208803637063662e-05</v>
+        <v>-3.208803637064772e-05</v>
       </c>
       <c r="H45" t="n">
         <v>46</v>
@@ -2141,7 +2141,7 @@
         <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>6.540573459712373e-06</v>
+        <v>6.540573459734578e-06</v>
       </c>
       <c r="H46" t="n">
         <v>27</v>
@@ -2178,7 +2178,7 @@
         <v>39</v>
       </c>
       <c r="G47" t="n">
-        <v>-5.748719285413318e-05</v>
+        <v>-5.748719285409986e-05</v>
       </c>
       <c r="H47" t="n">
         <v>49</v>
@@ -2215,7 +2215,7 @@
         <v>48</v>
       </c>
       <c r="G48" t="n">
-        <v>1.916612153399777e-05</v>
+        <v>1.916612153397557e-05</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -2289,7 +2289,7 @@
         <v>47</v>
       </c>
       <c r="G50" t="n">
-        <v>2.333098037632375e-06</v>
+        <v>2.33309803761017e-06</v>
       </c>
       <c r="H50" t="n">
         <v>32</v>
@@ -2326,7 +2326,7 @@
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-6.182965407941499e-06</v>
+        <v>-6.182965407930397e-06</v>
       </c>
       <c r="H51" t="n">
         <v>40</v>
@@ -2363,7 +2363,7 @@
         <v>51</v>
       </c>
       <c r="G52" t="n">
-        <v>7.726373676852915e-07</v>
+        <v>7.726373676963938e-07</v>
       </c>
       <c r="H52" t="n">
         <v>33</v>
@@ -2400,7 +2400,7 @@
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>1.102212534354052e-07</v>
+        <v>1.10221253424303e-07</v>
       </c>
       <c r="H53" t="n">
         <v>34</v>
@@ -2437,7 +2437,7 @@
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>-6.67839771288925e-06</v>
+        <v>-6.678397712900352e-06</v>
       </c>
       <c r="H54" t="n">
         <v>41</v>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4275278758199269</v>
+        <v>0.4275278758199268</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547372651050634</v>
+        <v>0.1547372651050635</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02625494934165764</v>
+        <v>0.02625494934165765</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01662492513450207</v>
+        <v>0.01662492513450205</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009065309642399915</v>
+        <v>0.0009065309642396138</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2767,7 +2767,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001183796798163073</v>
+        <v>0.001183796798163061</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000151267789462084</v>
+        <v>0.0001512677894620507</v>
       </c>
       <c r="H10" t="n">
         <v>11</v>
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001997195509044092</v>
+        <v>0.0001997195509044203</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -2915,7 +2915,7 @@
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>6.458258715732467e-05</v>
+        <v>6.458258715731357e-05</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -2952,7 +2952,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003713926271153301</v>
+        <v>0.0003713926271153745</v>
       </c>
       <c r="H13" t="n">
         <v>8</v>
@@ -3026,7 +3026,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001716239216839277</v>
+        <v>0.0001716239216839166</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.159233054340186e-05</v>
+        <v>-7.159233054339076e-05</v>
       </c>
       <c r="H16" t="n">
         <v>50</v>
@@ -3100,7 +3100,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>8.792114628443093e-05</v>
+        <v>8.792114628441983e-05</v>
       </c>
       <c r="H17" t="n">
         <v>15</v>
@@ -3137,7 +3137,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.105894637469355e-06</v>
+        <v>-5.10589463744715e-06</v>
       </c>
       <c r="H18" t="n">
         <v>38</v>
@@ -3174,7 +3174,7 @@
         <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001321039942656199</v>
+        <v>0.000132103994265631</v>
       </c>
       <c r="H19" t="n">
         <v>12</v>
@@ -3248,7 +3248,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>4.073934206418883e-05</v>
+        <v>4.073934206416663e-05</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4275278758199269</v>
+        <v>0.4275278758199268</v>
       </c>
       <c r="D2" t="n">
         <v>0.03550831053475043</v>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1547372651050634</v>
+        <v>0.1547372651050635</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007585522874415529</v>
+        <v>0.007585522874415515</v>
       </c>
     </row>
     <row r="4">
@@ -4784,7 +4784,7 @@
         <v>0.08337686689426374</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006168871607691502</v>
+        <v>0.006168871607691524</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02625494934165764</v>
+        <v>0.02625494934165765</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003888841631173515</v>
+        <v>0.003888841631173509</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01662492513450207</v>
+        <v>0.01662492513450205</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002830197896181445</v>
+        <v>0.002830197896181418</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001183796798163073</v>
+        <v>0.001183796798163061</v>
       </c>
       <c r="D7" t="n">
-        <v>9.264444868287794e-05</v>
+        <v>9.264444868288706e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0009065309642399915</v>
+        <v>0.0009065309642396138</v>
       </c>
       <c r="D8" t="n">
-        <v>8.551896153054946e-06</v>
+        <v>8.551896152560557e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003713926271153301</v>
+        <v>0.0003713926271153745</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001100944661529354</v>
+        <v>0.0001100944661529108</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001997195509044092</v>
+        <v>0.0001997195509044203</v>
       </c>
       <c r="D10" t="n">
-        <v>6.949015172659392e-05</v>
+        <v>6.949015172658809e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0001716239216839277</v>
+        <v>0.0001716239216839166</v>
       </c>
       <c r="D11" t="n">
-        <v>6.954159173446452e-05</v>
+        <v>6.954159173444464e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.000151267789462084</v>
+        <v>0.0001512677894620507</v>
       </c>
       <c r="D12" t="n">
-        <v>6.712967861880868e-05</v>
+        <v>6.712967861880446e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0001321039942656199</v>
+        <v>0.000132103994265631</v>
       </c>
       <c r="D13" t="n">
-        <v>2.584794060076915e-05</v>
+        <v>2.584794060076993e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4944,7 +4944,7 @@
         <v>0.0001214139411114035</v>
       </c>
       <c r="D14" t="n">
-        <v>4.654010032356979e-05</v>
+        <v>4.654010032362521e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4960,7 +4960,7 @@
         <v>0.0001071084214119389</v>
       </c>
       <c r="D15" t="n">
-        <v>8.690073980559234e-05</v>
+        <v>8.690073980561625e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.792114628443093e-05</v>
+        <v>8.792114628441983e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>5.947570701509682e-05</v>
+        <v>5.947570701508156e-05</v>
       </c>
     </row>
     <row r="17">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.458258715732467e-05</v>
+        <v>6.458258715731357e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>5.005957946790429e-05</v>
+        <v>5.005957946789628e-05</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.641385675950738e-05</v>
+        <v>5.641385675948518e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>2.228212941223416e-05</v>
+        <v>2.228212941223275e-05</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.255398592509785e-05</v>
+        <v>4.255398592508675e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>3.306726163051698e-05</v>
+        <v>3.306726163052123e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.174844017821311e-05</v>
+        <v>4.174844017820201e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>6.216704953096202e-05</v>
+        <v>6.21670495309607e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.073934206418883e-05</v>
+        <v>4.073934206416663e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>3.180255036780966e-05</v>
+        <v>3.180255036783024e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.731557529442874e-05</v>
+        <v>2.731557529441764e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>7.713035803174252e-05</v>
+        <v>7.713035803176242e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.521327939198903e-05</v>
+        <v>2.521327939195572e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>1.167913747057947e-05</v>
+        <v>1.167913747059034e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.916612153399777e-05</v>
+        <v>1.916612153397557e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.702656900939287e-05</v>
+        <v>1.702656900939434e-05</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.7556905478322e-05</v>
+        <v>1.75569054783109e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>4.201143414976832e-05</v>
+        <v>4.201143414977489e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.612708750226011e-05</v>
+        <v>1.612708750228231e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.383780085513268e-05</v>
+        <v>1.383780085515209e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.540573459712373e-06</v>
+        <v>6.540573459734578e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>1.210792919676313e-05</v>
+        <v>1.210792919679283e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.263717936794144e-06</v>
+        <v>6.263717936783042e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>2.661511124307446e-05</v>
+        <v>2.661511124306268e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5200,7 +5200,7 @@
         <v>4.903678078282958e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0001315005443876463</v>
+        <v>0.0001315005443876507</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.495879729875639e-06</v>
+        <v>3.495879729864537e-06</v>
       </c>
       <c r="D31" t="n">
-        <v>5.816398148777523e-07</v>
+        <v>5.816398148942419e-07</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.40641085841975e-06</v>
+        <v>3.406410858430853e-06</v>
       </c>
       <c r="D32" t="n">
-        <v>6.861140601515437e-05</v>
+        <v>6.861140601516018e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.333098037632375e-06</v>
+        <v>2.33309803761017e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>1.344812316134969e-05</v>
+        <v>1.34481231613268e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.726373676852915e-07</v>
+        <v>7.726373676963938e-07</v>
       </c>
       <c r="D34" t="n">
-        <v>6.249980597893795e-07</v>
+        <v>6.249980597747904e-07</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.102212534354052e-07</v>
+        <v>1.10221253424303e-07</v>
       </c>
       <c r="D35" t="n">
-        <v>1.252178067890837e-07</v>
+        <v>1.252178067716491e-07</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-9.162387754613199e-07</v>
+        <v>-9.162387754724222e-07</v>
       </c>
       <c r="D36" t="n">
-        <v>4.830560856431495e-05</v>
+        <v>4.830560856431567e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-4.703411712991823e-06</v>
+        <v>-4.703411713002925e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005463410241920008</v>
+        <v>0.000546341024192002</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-5.105894637469355e-06</v>
+        <v>-5.10589463744715e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>3.495626077877415e-05</v>
+        <v>3.495626077876469e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5360,7 +5360,7 @@
         <v>-6.05583248360908e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>1.460938618062169e-05</v>
+        <v>1.460938618062955e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-6.182965407941499e-06</v>
+        <v>-6.182965407930397e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>3.076844158505298e-05</v>
+        <v>3.076844158508651e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-6.67839771288925e-06</v>
+        <v>-6.678397712900352e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>9.07070924700926e-06</v>
+        <v>9.070709247008393e-06</v>
       </c>
     </row>
     <row r="43">
@@ -5408,7 +5408,7 @@
         <v>-2.240409385209086e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>3.110442438468803e-05</v>
+        <v>3.110442438469597e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5424,7 +5424,7 @@
         <v>-2.314953044951773e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00012310960812805</v>
+        <v>0.0001231096081280563</v>
       </c>
     </row>
     <row r="45">
@@ -5456,7 +5456,7 @@
         <v>-3.15504134551281e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>2.435233876713221e-05</v>
+        <v>2.435233876711132e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-3.208803637063662e-05</v>
+        <v>-3.208803637064772e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>1.553855684654054e-05</v>
+        <v>1.553855684654045e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-3.738914359018297e-05</v>
+        <v>-3.738914359020517e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>5.200121220848164e-05</v>
+        <v>5.200121220846929e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-3.951582136071386e-05</v>
+        <v>-3.951582136070275e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>3.375271597848838e-05</v>
+        <v>3.37527159784978e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5.748719285413318e-05</v>
+        <v>-5.748719285409986e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>3.706251298449458e-05</v>
+        <v>3.706251298446691e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-7.159233054340186e-05</v>
+        <v>-7.159233054339076e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0006041521753791865</v>
+        <v>0.0006041521753791926</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-8.670828243894091e-05</v>
+        <v>-8.67082824389187e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>4.386469448239552e-05</v>
+        <v>4.386469448237873e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5568,7 +5568,7 @@
         <v>-0.0001153350793199892</v>
       </c>
       <c r="D53" t="n">
-        <v>6.87529426097149e-05</v>
+        <v>6.875294260969742e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0002221778104696814</v>
+        <v>-0.0002221778104696925</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003531514623099235</v>
+        <v>0.0003531514623099167</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:54:30 UTC</t>
+          <t>2026-06-15 07:11:10 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4977888743490059</v>
+        <v>0.479002827428072</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3555639308574666</v>
+        <v>0.3708154388070739</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4275278758199268</v>
+        <v>0.4151684769240047</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.212438164413909</v>
+        <v>1.214214548351573</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1705570914101155</v>
+        <v>0.156106518976033</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2190170715818167</v>
+        <v>0.2171298895431281</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547372651050635</v>
+        <v>0.1452153833480583</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.231562346339471</v>
+        <v>1.230827167303108</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1493154822576961</v>
+        <v>0.1550704807012017</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1945990500210734</v>
+        <v>0.2138932899822522</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08337686689426374</v>
+        <v>0.088669051891718</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.071602712577556</v>
+        <v>1.067892686625295</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09109327576136467</v>
+        <v>0.08551606937745387</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1704639022676688</v>
+        <v>0.1554086179779583</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02625494934165765</v>
+        <v>0.02320092263992006</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6647508870541099</v>
+        <v>0.6646724278380272</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.07266127677126222</v>
+        <v>0.1058781797457002</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009783522296471749</v>
+        <v>0.007965469251124511</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01662492513450205</v>
+        <v>0.03472139380998875</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.550538439464701</v>
+        <v>0.5457839952037666</v>
       </c>
       <c r="J6" t="n">
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0007103842065014464</v>
+        <v>0.0007658894802093276</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01008863850085699</v>
+        <v>0.01110020662490868</v>
       </c>
       <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001224674681760484</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0009065309642396138</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.6663908335330178</v>
+        <v>0.6982133532024903</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001106154337122481</v>
+        <v>0.0008026042183470292</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01507350619875696</v>
+        <v>0.001461027214969927</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001183796798163061</v>
+        <v>0.0001132409813681789</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3335482345837661</v>
+        <v>0.4883554073292515</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0006782722832782091</v>
+        <v>0.0004499887887125859</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00107945562607117</v>
+        <v>0.002104069512245189</v>
       </c>
       <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.641555722113335e-05</v>
+      </c>
+      <c r="H9" t="n">
         <v>15</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0001071084214119389</v>
-      </c>
-      <c r="H9" t="n">
-        <v>14</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.4648439152564756</v>
+        <v>0.254449059903076</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0004998411828986698</v>
+        <v>0.0005538084323941195</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001375017038606483</v>
+        <v>0.0003921316205577167</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001512677894620507</v>
+        <v>0.000386734951151535</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2547847995899231</v>
+        <v>0.2090796911647348</v>
       </c>
       <c r="J10" t="n">
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003127567702813812</v>
+        <v>0.0007552535896017913</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001910325373208544</v>
+        <v>0.001724987166789213</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001997195509044203</v>
+        <v>1.95459259154207e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2587939072850545</v>
+        <v>0.2445897889469877</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0005909537916020339</v>
+        <v>0.0006599948468637758</v>
       </c>
       <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.001189236023866339</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.493349073656725e-05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2388977550151199</v>
+      </c>
+      <c r="J12" t="n">
         <v>12</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.001058674853744491</v>
-      </c>
-      <c r="F12" t="n">
-        <v>17</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.458258715731357e-05</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.2408108237229087</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
       <c r="K12" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="13">
@@ -904,32 +904,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0005375576450263882</v>
+        <v>0.0002346047832836143</v>
       </c>
       <c r="D13" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.002423009528338022</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.776381560408273e-05</v>
+      </c>
+      <c r="H13" t="n">
         <v>14</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.0004710658840022318</v>
-      </c>
-      <c r="F13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0003713926271153745</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.2102993797330091</v>
+        <v>0.5971940052420313</v>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
         <v>15.5</v>
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0002653077650617428</v>
+        <v>0.000819571623694239</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001670788762225316</v>
+        <v>0.001147447577271913</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001214139411114035</v>
+        <v>8.294305775450317e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5913076670343078</v>
+        <v>0.1128833862155965</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="15">
@@ -978,32 +978,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0002802875274942336</v>
+        <v>0.003841308591179958</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001330236486653077</v>
+        <v>0.002066237702520325</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001716239216839166</v>
+        <v>-0.0002374245944075759</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2552694439026277</v>
+        <v>0.7957843210604252</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>16.25</v>
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002701697807286757</v>
+        <v>0.0003921208109701725</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002646968175849742</v>
+        <v>0.0006658543047210953</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.159233054339076e-05</v>
+        <v>0.0001145028742273069</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8068634900832006</v>
+        <v>0.128004666543299</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0007793803402373105</v>
+        <v>0.0004827296461692438</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001065731735818191</v>
+        <v>0.0003293996298317123</v>
       </c>
       <c r="F17" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.577100925052593e-05</v>
+      </c>
+      <c r="H17" t="n">
         <v>16</v>
       </c>
-      <c r="G17" t="n">
-        <v>8.792114628441983e-05</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.1142378946588831</v>
+        <v>0.1978806624188503</v>
       </c>
       <c r="J17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>17.75</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005057072382968386</v>
+        <v>0.001233913518759386</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001182958538978182</v>
+        <v>0.001272840268085012</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.10589463744715e-06</v>
+        <v>3.470811547484631e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2429740107274019</v>
+        <v>0.09019047787179169</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K18" t="n">
-        <v>20.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="19">
@@ -1130,31 +1130,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004523097060686619</v>
+        <v>0.0004349541834486765</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0007324938894881081</v>
+        <v>0.0005908886295479543</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000132103994265631</v>
+        <v>0.0001061095124867406</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1077071466686097</v>
+        <v>0.1109000822803394</v>
       </c>
       <c r="J19" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>21.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004078805259264197</v>
+        <v>0.0004201002537335781</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0004516600996286941</v>
+        <v>0.0002957327832152873</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>8.593794349395222e-05</v>
+        <v>3.640806285143405e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1301270971527879</v>
+        <v>0.1541083634048221</v>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>21.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="21">
@@ -1200,32 +1200,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.000403395323502312</v>
+        <v>5.507254521737946e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0004206830033535337</v>
+        <v>0.0008943155502233942</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>4.073934206416663e-05</v>
+        <v>5.668589636222965e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1471659955571996</v>
+        <v>0.179419606724633</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
         <v>23</v>
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003690440611496681</v>
+        <v>0.0002603813432706558</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0002893802531270894</v>
+        <v>0.0002700299580722579</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>2.731557529441764e-05</v>
+        <v>0.0001190846683090108</v>
       </c>
       <c r="H22" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1957813546346203</v>
+        <v>0.1257174204872564</v>
       </c>
       <c r="J22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K22" t="n">
-        <v>23.75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004043506940899511</v>
+        <v>0.0004514912917013022</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002980767494984981</v>
+        <v>0.0002907332313330439</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>1.75569054783109e-05</v>
+        <v>-1.37911551978398e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I23" t="n">
-        <v>0.14754127066016</v>
+        <v>0.1579773684353802</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K23" t="n">
-        <v>24.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001208727117400267</v>
+        <v>0.0003306362148198881</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0008763349563827641</v>
+        <v>0.0004634979776089925</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.703411713002925e-06</v>
+        <v>3.4899099556851e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08944913025642398</v>
+        <v>0.1012321550566364</v>
       </c>
       <c r="J24" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K24" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003215492859344674</v>
+        <v>0.0003165778647685665</v>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0003054777829877038</v>
+        <v>0.0002559530322263791</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>4.255398592508675e-05</v>
+        <v>6.864221674716121e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1107850262028252</v>
+        <v>0.1157586112848028</v>
       </c>
       <c r="J25" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>26.25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003165551200612789</v>
+        <v>4.765300527810781e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0002417902342040286</v>
+        <v>0.0007847765641236794</v>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>4.174844017820201e-05</v>
+        <v>2.086065535663595e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1471304004695173</v>
+        <v>0.1985218637648338</v>
       </c>
       <c r="J26" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
-        <v>27.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.397080698261438e-05</v>
+        <v>0.0003803717109066179</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0008689963662404777</v>
+        <v>0.0002586722132948113</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>2.521327939195572e-05</v>
+        <v>-2.401259645712361e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1902758747175912</v>
+        <v>0.1463444515688344</v>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.690559978830481e-05</v>
+        <v>0.0003255631359984801</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0007659739879395197</v>
+        <v>0.0002644991210552066</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>1.612708750228231e-05</v>
+        <v>-5.473914662283974e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1711370859094126</v>
+        <v>0.2003431368120432</v>
       </c>
       <c r="J28" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>28.25</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002604295756068635</v>
+        <v>4.81417526374781e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0002712595222667998</v>
+        <v>0.001316217371036625</v>
       </c>
       <c r="F29" t="n">
+        <v>12</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-9.532754855268166e-07</v>
+      </c>
+      <c r="H29" t="n">
         <v>33</v>
       </c>
-      <c r="G29" t="n">
-        <v>5.641385675948518e-05</v>
-      </c>
-      <c r="H29" t="n">
-        <v>18</v>
-      </c>
       <c r="I29" t="n">
-        <v>0.1299078641209057</v>
+        <v>0.1270876349829884</v>
       </c>
       <c r="J29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>28.5</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003420062886621227</v>
+        <v>0.0003263166708085113</v>
       </c>
       <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0003296549198025265</v>
+      </c>
+      <c r="F30" t="n">
         <v>23</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.0001883828094131394</v>
-      </c>
-      <c r="F30" t="n">
-        <v>43</v>
-      </c>
       <c r="G30" t="n">
-        <v>4.903678078282958e-06</v>
+        <v>5.897804915833138e-06</v>
       </c>
       <c r="H30" t="n">
         <v>29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1479960569991445</v>
+        <v>0.08227123552180649</v>
       </c>
       <c r="J30" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K30" t="n">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0003048981208460142</v>
+        <v>0.0006713817408349152</v>
       </c>
       <c r="D31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.000266665932164506</v>
+      </c>
+      <c r="F31" t="n">
+        <v>28</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.0001146724911101238</v>
+      </c>
+      <c r="H31" t="n">
+        <v>44</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1013475265185595</v>
+      </c>
+      <c r="J31" t="n">
+        <v>32</v>
+      </c>
+      <c r="K31" t="n">
         <v>29</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.0003543421399181286</v>
-      </c>
-      <c r="F31" t="n">
-        <v>26</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-3.951582136070275e-05</v>
-      </c>
-      <c r="H31" t="n">
-        <v>48</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.2134376731829786</v>
-      </c>
-      <c r="J31" t="n">
-        <v>16</v>
-      </c>
-      <c r="K31" t="n">
-        <v>29.75</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0005657610149501117</v>
+        <v>0.0003127336073616019</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0002582400865463695</v>
+        <v>0.0002267020745110839</v>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.314953044951773e-05</v>
+        <v>-5.725481025053991e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09673555695449876</v>
+        <v>0.199104616219703</v>
       </c>
       <c r="J32" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>32.25</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0003213782488106037</v>
+        <v>0.0005245434802480583</v>
       </c>
       <c r="D33" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0002432338739456334</v>
+        <v>0.0002333882366519568</v>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G33" t="n">
-        <v>-8.67082824389187e-05</v>
+        <v>-0.0001693918106480341</v>
       </c>
       <c r="H33" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1958019766982275</v>
+        <v>0.1131160250941958</v>
       </c>
       <c r="J33" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>32.5</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.505301077455776e-05</v>
+        <v>0.0003314617241769402</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001399623245753354</v>
+        <v>0.0002575738410540276</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.05583248360908e-06</v>
+        <v>-1.992766598154505e-05</v>
       </c>
       <c r="H34" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1214339320950062</v>
+        <v>0.09845236262286194</v>
       </c>
       <c r="J34" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0002654677369844531</v>
+        <v>0.0002839607771757138</v>
       </c>
       <c r="D35" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0003021859458919988</v>
+        <v>0.0001681276977475154</v>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>6.263717936783042e-06</v>
+        <v>-3.298314087567533e-05</v>
       </c>
       <c r="H35" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I35" t="n">
-        <v>0.087624953920451</v>
+        <v>0.1314012452942006</v>
       </c>
       <c r="J35" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>33</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0002341925729293735</v>
+        <v>7.845175888786344e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0002022542739255145</v>
+        <v>0.0003866395757596791</v>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
-        <v>-9.162387754724222e-07</v>
+        <v>1.469885477373145e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I36" t="n">
-        <v>0.16122192641236</v>
+        <v>0.02422029185884722</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>34.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002751731629187985</v>
+        <v>0.0002849999135802555</v>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0003326441258727966</v>
+        <v>0.0001509610263934775</v>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>-3.15504134551281e-05</v>
+        <v>-1.376256657787955e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1029656032469943</v>
+        <v>0.1205093625624927</v>
       </c>
       <c r="J37" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K37" t="n">
-        <v>35</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0003221144683825916</v>
+        <v>0.000269819388515531</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0002404243134378276</v>
+        <v>0.0002527575403065533</v>
       </c>
       <c r="F38" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.92481468815442e-05</v>
+        <v>1.977355755543586e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1026725904342158</v>
+        <v>0.02226437970643325</v>
       </c>
       <c r="J38" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K38" t="n">
-        <v>35.75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.876224140878438e-05</v>
+        <v>0.0002185384107880062</v>
       </c>
       <c r="D39" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0004722700057947649</v>
+        <v>0.0001486877091022238</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>3.495879729864537e-06</v>
+        <v>3.825811388710188e-05</v>
       </c>
       <c r="H39" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>0.03428089609839091</v>
+        <v>0.08183413992755595</v>
       </c>
       <c r="J39" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K39" t="n">
-        <v>36</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0004632163977099433</v>
+        <v>0.000181564445292913</v>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002240733036846782</v>
+        <v>8.619195589405681e-05</v>
       </c>
       <c r="F40" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0002221778104696925</v>
+        <v>3.877498871663887e-05</v>
       </c>
       <c r="H40" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1062313428240609</v>
+        <v>0.07665119805792608</v>
       </c>
       <c r="J40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K40" t="n">
-        <v>36</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002681110978138219</v>
+        <v>0.0002254269015934438</v>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002907647771068084</v>
+        <v>0.0002010497293285353</v>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.240409385209086e-05</v>
+        <v>9.296446570461469e-06</v>
       </c>
       <c r="H41" t="n">
+        <v>28</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.02348779014183311</v>
+      </c>
+      <c r="J41" t="n">
         <v>42</v>
       </c>
-      <c r="I41" t="n">
-        <v>0.03341579694077312</v>
-      </c>
-      <c r="J41" t="n">
-        <v>48</v>
-      </c>
       <c r="K41" t="n">
-        <v>38.25</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0002448766988373972</v>
+        <v>0.0002091552013541006</v>
       </c>
       <c r="D42" t="n">
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0002077091998718574</v>
+        <v>0.0001066543420614364</v>
       </c>
       <c r="F42" t="n">
         <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.738914359020517e-05</v>
+        <v>-7.867949670369301e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1220322635174351</v>
+        <v>0.1132120060624557</v>
       </c>
       <c r="J42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>38.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0002095847207526698</v>
+        <v>0.0002472730179358964</v>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0001555529762327496</v>
+        <v>0.0002177273615987803</v>
       </c>
       <c r="F43" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G43" t="n">
-        <v>3.406410858430853e-06</v>
+        <v>-7.955627674814947e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08510757614392039</v>
+        <v>0.08654473467831325</v>
       </c>
       <c r="J43" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>39.75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0002553428017997986</v>
+        <v>0.0001822711714317765</v>
       </c>
       <c r="D44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0002092501790068323</v>
+        <v>9.666994566442012e-05</v>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>-2.014887607815208e-06</v>
+        <v>-1.085444705649641e-05</v>
       </c>
       <c r="H44" t="n">
         <v>36</v>
       </c>
       <c r="I44" t="n">
-        <v>0.02686938527320182</v>
+        <v>0.07421889375992929</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>40.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
@@ -2088,32 +2088,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0001901943927653888</v>
+        <v>4.582974446636209e-06</v>
       </c>
       <c r="D45" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001580952325513216</v>
+        <v>6.721828422630137e-05</v>
       </c>
       <c r="F45" t="n">
         <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>-3.208803637064772e-05</v>
+        <v>-1.112074870857072e-07</v>
       </c>
       <c r="H45" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1131622911198775</v>
+        <v>0.0185581043306744</v>
       </c>
       <c r="J45" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K45" t="n">
         <v>41</v>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0001366122827683942</v>
+        <v>2.765950821275766e-06</v>
       </c>
       <c r="D46" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E46" t="n">
-        <v>9.854451162539894e-05</v>
+        <v>1.967618852711355e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>6.540573459734578e-06</v>
+        <v>5.023328003561645e-07</v>
       </c>
       <c r="H46" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07784304879969328</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>45</v>
@@ -2162,294 +2162,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0002205826903911296</v>
+        <v>7.945004319825028e-06</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E47" t="n">
-        <v>0.000222129825404503</v>
+        <v>9.184471826045516e-06</v>
       </c>
       <c r="F47" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>-5.748719285409986e-05</v>
+        <v>-1.23170674979356e-06</v>
       </c>
       <c r="H47" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.08788530601202416</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K47" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>7.506688267847946e-05</v>
-      </c>
-      <c r="D48" t="n">
-        <v>47</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.0001034278042927943</v>
-      </c>
-      <c r="F48" t="n">
-        <v>48</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1.916612153397557e-05</v>
-      </c>
-      <c r="H48" t="n">
-        <v>24</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.02907315417629119</v>
-      </c>
-      <c r="J48" t="n">
-        <v>49</v>
-      </c>
-      <c r="K48" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>filtercake_moisture</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0001974076638096041</v>
-      </c>
-      <c r="D49" t="n">
-        <v>41</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.0001254575048111429</v>
-      </c>
-      <c r="F49" t="n">
-        <v>46</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.0001153350793199892</v>
-      </c>
-      <c r="H49" t="n">
-        <v>52</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.1065366655791227</v>
-      </c>
-      <c r="J49" t="n">
-        <v>35</v>
-      </c>
-      <c r="K49" t="n">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>6.965077812365236e-05</v>
-      </c>
-      <c r="D50" t="n">
-        <v>49</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.0001115110041910677</v>
-      </c>
-      <c r="F50" t="n">
-        <v>47</v>
-      </c>
-      <c r="G50" t="n">
-        <v>2.33309803761017e-06</v>
-      </c>
-      <c r="H50" t="n">
-        <v>32</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.06408156581287239</v>
-      </c>
-      <c r="J50" t="n">
-        <v>46</v>
-      </c>
-      <c r="K50" t="n">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0001796341241109861</v>
-      </c>
-      <c r="D51" t="n">
-        <v>43</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.0001013191853664384</v>
-      </c>
-      <c r="F51" t="n">
-        <v>49</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-6.182965407930397e-06</v>
-      </c>
-      <c r="H51" t="n">
-        <v>40</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.08188351724165344</v>
-      </c>
-      <c r="J51" t="n">
-        <v>44</v>
-      </c>
-      <c r="K51" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>5.432341154503717e-06</v>
-      </c>
-      <c r="D52" t="n">
-        <v>53</v>
-      </c>
-      <c r="E52" t="n">
-        <v>5.725891521908949e-05</v>
-      </c>
-      <c r="F52" t="n">
-        <v>51</v>
-      </c>
-      <c r="G52" t="n">
-        <v>7.726373676963938e-07</v>
-      </c>
-      <c r="H52" t="n">
-        <v>33</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.005891922780134173</v>
-      </c>
-      <c r="J52" t="n">
-        <v>51</v>
-      </c>
-      <c r="K52" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1.136232410642219e-05</v>
-      </c>
-      <c r="D53" t="n">
-        <v>51</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1.890476486443773e-05</v>
-      </c>
-      <c r="F53" t="n">
-        <v>53</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.10221253424303e-07</v>
-      </c>
-      <c r="H53" t="n">
-        <v>34</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>52</v>
-      </c>
-      <c r="K53" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>8.698675467773773e-06</v>
-      </c>
-      <c r="D54" t="n">
-        <v>52</v>
-      </c>
-      <c r="E54" t="n">
-        <v>1.942895088559494e-05</v>
-      </c>
-      <c r="F54" t="n">
-        <v>52</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-6.678397712900352e-06</v>
-      </c>
-      <c r="H54" t="n">
-        <v>41</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>52</v>
-      </c>
-      <c r="K54" t="n">
-        <v>49.25</v>
+        <v>42.25</v>
       </c>
     </row>
   </sheetData>
@@ -2533,25 +2274,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4977888743490059</v>
+        <v>0.479002827428072</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3555639308574666</v>
+        <v>0.3708154388070739</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4275278758199268</v>
+        <v>0.4151684769240047</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.212438164413909</v>
+        <v>1.214214548351573</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -2570,25 +2311,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1705570914101155</v>
+        <v>0.156106518976033</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2190170715818167</v>
+        <v>0.2171298895431281</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547372651050635</v>
+        <v>0.1452153833480583</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.231562346339471</v>
+        <v>1.230827167303108</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -2607,25 +2348,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1493154822576961</v>
+        <v>0.1550704807012017</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1945990500210734</v>
+        <v>0.2138932899822522</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08337686689426374</v>
+        <v>0.088669051891718</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.071602712577556</v>
+        <v>1.067892686625295</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -2644,31 +2385,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09109327576136467</v>
+        <v>0.08551606937745387</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1704639022676688</v>
+        <v>0.1554086179779583</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02625494934165765</v>
+        <v>0.02320092263992006</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6647508870541099</v>
+        <v>0.6646724278380272</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2681,31 +2422,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.07266127677126222</v>
+        <v>0.1058781797457002</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009783522296471749</v>
+        <v>0.007965469251124511</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01662492513450205</v>
+        <v>0.03472139380998875</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.550538439464701</v>
+        <v>0.5457839952037666</v>
       </c>
       <c r="J6" t="n">
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -2718,31 +2459,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0007103842065014464</v>
+        <v>0.0007658894802093276</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01008863850085699</v>
+        <v>0.01110020662490868</v>
       </c>
       <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001224674681760484</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0009065309642396138</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.6663908335330178</v>
+        <v>0.6982133532024903</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -2751,35 +2492,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001106154337122481</v>
+        <v>0.0008026042183470292</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01507350619875696</v>
+        <v>0.001461027214969927</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001183796798163061</v>
+        <v>0.0001132409813681789</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3335482345837661</v>
+        <v>0.4883554073292515</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -2788,35 +2529,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0006782722832782091</v>
+        <v>0.0004499887887125859</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00107945562607117</v>
+        <v>0.002104069512245189</v>
       </c>
       <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.641555722113335e-05</v>
+      </c>
+      <c r="H9" t="n">
         <v>15</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0001071084214119389</v>
-      </c>
-      <c r="H9" t="n">
-        <v>14</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.4648439152564756</v>
+        <v>0.254449059903076</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="10">
@@ -2825,35 +2566,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0004998411828986698</v>
+        <v>0.0005538084323941195</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001375017038606483</v>
+        <v>0.0003921316205577167</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001512677894620507</v>
+        <v>0.000386734951151535</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2547847995899231</v>
+        <v>0.2090796911647348</v>
       </c>
       <c r="J10" t="n">
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2603,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003127567702813812</v>
+        <v>0.0007552535896017913</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001910325373208544</v>
+        <v>0.001724987166789213</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001997195509044203</v>
+        <v>1.95459259154207e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2587939072850545</v>
+        <v>0.2445897889469877</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2640,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0005909537916020339</v>
+        <v>0.0006599948468637758</v>
       </c>
       <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.001189236023866339</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.493349073656725e-05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2388977550151199</v>
+      </c>
+      <c r="J12" t="n">
         <v>12</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.001058674853744491</v>
-      </c>
-      <c r="F12" t="n">
-        <v>17</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.458258715731357e-05</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.2408108237229087</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
       <c r="K12" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="13">
@@ -2936,32 +2677,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0005375576450263882</v>
+        <v>0.0002346047832836143</v>
       </c>
       <c r="D13" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.002423009528338022</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.776381560408273e-05</v>
+      </c>
+      <c r="H13" t="n">
         <v>14</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.0004710658840022318</v>
-      </c>
-      <c r="F13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0003713926271153745</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.2102993797330091</v>
+        <v>0.5971940052420313</v>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
         <v>15.5</v>
@@ -2973,35 +2714,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0002653077650617428</v>
+        <v>0.000819571623694239</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001670788762225316</v>
+        <v>0.001147447577271913</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001214139411114035</v>
+        <v>8.294305775450317e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5913076670343078</v>
+        <v>0.1128833862155965</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="15">
@@ -3010,32 +2751,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0002802875274942336</v>
+        <v>0.003841308591179958</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001330236486653077</v>
+        <v>0.002066237702520325</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001716239216839166</v>
+        <v>-0.0002374245944075759</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2552694439026277</v>
+        <v>0.7957843210604252</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>16.25</v>
@@ -3047,35 +2788,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002701697807286757</v>
+        <v>0.0003921208109701725</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002646968175849742</v>
+        <v>0.0006658543047210953</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.159233054339076e-05</v>
+        <v>0.0001145028742273069</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8068634900832006</v>
+        <v>0.128004666543299</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +2825,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0007793803402373105</v>
+        <v>0.0004827296461692438</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001065731735818191</v>
+        <v>0.0003293996298317123</v>
       </c>
       <c r="F17" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.577100925052593e-05</v>
+      </c>
+      <c r="H17" t="n">
         <v>16</v>
       </c>
-      <c r="G17" t="n">
-        <v>8.792114628441983e-05</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.1142378946588831</v>
+        <v>0.1978806624188503</v>
       </c>
       <c r="J17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>17.75</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +2862,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005057072382968386</v>
+        <v>0.001233913518759386</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001182958538978182</v>
+        <v>0.001272840268085012</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.10589463744715e-06</v>
+        <v>3.470811547484631e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2429740107274019</v>
+        <v>0.09019047787179169</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K18" t="n">
-        <v>20.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="19">
@@ -3162,31 +2903,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004523097060686619</v>
+        <v>0.0004349541834486765</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0007324938894881081</v>
+        <v>0.0005908886295479543</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000132103994265631</v>
+        <v>0.0001061095124867406</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1077071466686097</v>
+        <v>0.1109000822803394</v>
       </c>
       <c r="J19" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>21.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +2936,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004078805259264197</v>
+        <v>0.0004201002537335781</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0004516600996286941</v>
+        <v>0.0002957327832152873</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>8.593794349395222e-05</v>
+        <v>3.640806285143405e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1301270971527879</v>
+        <v>0.1541083634048221</v>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>21.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="21">
@@ -3232,32 +2973,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.000403395323502312</v>
+        <v>5.507254521737946e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0004206830033535337</v>
+        <v>0.0008943155502233942</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>4.073934206416663e-05</v>
+        <v>5.668589636222965e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1471659955571996</v>
+        <v>0.179419606724633</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
         <v>23</v>
@@ -3274,7 +3015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,7 +3045,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4977888743490059</v>
+        <v>0.479002827428072</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3058,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1705570914101155</v>
+        <v>0.156106518976033</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3071,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1493154822576961</v>
+        <v>0.1550704807012017</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3080,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09109327576136467</v>
+        <v>0.1058781797457002</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3093,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.07266127677126222</v>
+        <v>0.08551606937745387</v>
       </c>
     </row>
     <row r="7">
@@ -3369,7 +3110,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002701697807286757</v>
+        <v>0.003841308591179958</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3123,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001208727117400267</v>
+        <v>0.001233913518759386</v>
       </c>
     </row>
     <row r="9">
@@ -3391,11 +3132,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001106154337122481</v>
+        <v>0.000819571623694239</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3145,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0007793803402373105</v>
+        <v>0.0008026042183470292</v>
       </c>
     </row>
     <row r="11">
@@ -3421,7 +3162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0007103842065014464</v>
+        <v>0.0007658894802093276</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3171,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0006782722832782091</v>
+        <v>0.0007552535896017913</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3184,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0005909537916020339</v>
+        <v>0.0006713817408349152</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3197,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0005657610149501117</v>
+        <v>0.0006599948468637758</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3214,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005375576450263882</v>
+        <v>0.0005538084323941195</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3223,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005057072382968386</v>
+        <v>0.0005245434802480583</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3236,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0004998411828986698</v>
+        <v>0.0004827296461692438</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3249,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0004632163977099433</v>
+        <v>0.0004514912917013022</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3262,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004523097060686619</v>
+        <v>0.0004499887887125859</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3275,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004078805259264197</v>
+        <v>0.0004349541834486765</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3288,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004043506940899511</v>
+        <v>0.0004201002537335781</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3301,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.000403395323502312</v>
+        <v>0.0003921208109701725</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3314,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003690440611496681</v>
+        <v>0.0003803717109066179</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3327,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003420062886621227</v>
+        <v>0.0003314617241769402</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3340,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003221144683825916</v>
+        <v>0.0003306362148198881</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3353,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003215492859344674</v>
+        <v>0.0003263166708085113</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3366,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003213782488106037</v>
+        <v>0.0003255631359984801</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3379,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003165551200612789</v>
+        <v>0.0003165778647685665</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3392,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0003127567702813812</v>
+        <v>0.0003127336073616019</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3405,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003048981208460142</v>
+        <v>0.0002849999135802555</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3418,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002802875274942336</v>
+        <v>0.0002839607771757138</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3431,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002751731629187985</v>
+        <v>0.000269819388515531</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3444,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002681110978138219</v>
+        <v>0.0002603813432706558</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3457,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0002654677369844531</v>
+        <v>0.0002472730179358964</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3474,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0002653077650617428</v>
+        <v>0.0002346047832836143</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3483,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0002604295756068635</v>
+        <v>0.0002254269015934438</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3496,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002553428017997986</v>
+        <v>0.0002185384107880062</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3509,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0002448766988373972</v>
+        <v>0.0002091552013541006</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3522,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0002341925729293735</v>
+        <v>0.0001822711714317765</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3535,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0002205826903911296</v>
+        <v>0.000181564445292913</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3548,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002095847207526698</v>
+        <v>7.845175888786344e-05</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3561,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0001974076638096041</v>
+        <v>5.507254521737946e-05</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3574,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0001901943927653888</v>
+        <v>4.81417526374781e-05</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3587,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0001796341241109861</v>
+        <v>4.765300527810781e-05</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3600,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0001366122827683942</v>
+        <v>7.945004319825028e-06</v>
       </c>
     </row>
     <row r="46">
@@ -3872,11 +3613,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.876224140878438e-05</v>
+        <v>4.582974446636209e-06</v>
       </c>
     </row>
     <row r="47">
@@ -3885,102 +3626,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7.690559978830481e-05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>7.506688267847946e-05</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>7.397080698261438e-05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>6.965077812365236e-05</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>work_period</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>6.505301077455776e-05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1.136232410642219e-05</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>8.698675467773773e-06</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>5.432341154503717e-06</v>
+        <v>2.765950821275766e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3994,7 +3644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,7 +3674,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3555639308574666</v>
+        <v>0.3708154388070739</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +3687,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2190170715818167</v>
+        <v>0.2171298895431281</v>
       </c>
     </row>
     <row r="4">
@@ -4050,7 +3700,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1945990500210734</v>
+        <v>0.2138932899822522</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +3713,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1704639022676688</v>
+        <v>0.1554086179779583</v>
       </c>
     </row>
     <row r="6">
@@ -4072,11 +3722,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01507350619875696</v>
+        <v>0.01110020662490868</v>
       </c>
     </row>
     <row r="7">
@@ -4085,11 +3735,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01008863850085699</v>
+        <v>0.007965469251124511</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +3748,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009783522296471749</v>
+        <v>0.002423009528338022</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +3761,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002646968175849742</v>
+        <v>0.002104069512245189</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +3774,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001910325373208544</v>
+        <v>0.002066237702520325</v>
       </c>
     </row>
     <row r="11">
@@ -4137,11 +3787,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001670788762225316</v>
+        <v>0.001724987166789213</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +3800,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001399623245753354</v>
+        <v>0.001461027214969927</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +3813,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001375017038606483</v>
+        <v>0.001316217371036625</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +3826,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001330236486653077</v>
+        <v>0.001272840268085012</v>
       </c>
     </row>
     <row r="15">
@@ -4193,7 +3843,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001182958538978182</v>
+        <v>0.001189236023866339</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +3852,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00107945562607117</v>
+        <v>0.001147447577271913</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +3865,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001065731735818191</v>
+        <v>0.0008943155502233942</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +3878,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001058674853744491</v>
+        <v>0.0007847765641236794</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +3891,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0008763349563827641</v>
+        <v>0.0006658543047210953</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +3904,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0008689963662404777</v>
+        <v>0.0005908886295479543</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +3917,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0007659739879395197</v>
+        <v>0.0004634979776089925</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +3930,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0007324938894881081</v>
+        <v>0.0003921316205577167</v>
       </c>
     </row>
     <row r="23">
@@ -4297,7 +3947,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004722700057947649</v>
+        <v>0.0003866395757596791</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +3956,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004710658840022318</v>
+        <v>0.0003296549198025265</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +3969,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004516600996286941</v>
+        <v>0.0003293996298317123</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +3982,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0004206830033535337</v>
+        <v>0.0002957327832152873</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +3995,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003543421399181286</v>
+        <v>0.0002907332313330439</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +4008,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003326441258727966</v>
+        <v>0.0002700299580722579</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +4021,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0003054777829877038</v>
+        <v>0.000266665932164506</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4034,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003021859458919988</v>
+        <v>0.0002644991210552066</v>
       </c>
     </row>
     <row r="31">
@@ -4401,7 +4051,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002980767494984981</v>
+        <v>0.0002586722132948113</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4060,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002907647771068084</v>
+        <v>0.0002575738410540276</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4073,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002893802531270894</v>
+        <v>0.0002559530322263791</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4086,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0002712595222667998</v>
+        <v>0.0002527575403065533</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4099,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0002582400865463695</v>
+        <v>0.0002333882366519568</v>
       </c>
     </row>
     <row r="36">
@@ -4466,7 +4116,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0002432338739456334</v>
+        <v>0.0002267020745110839</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4125,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002417902342040286</v>
+        <v>0.0002177273615987803</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4138,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0002404243134378276</v>
+        <v>0.0002010497293285353</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4151,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0002240733036846782</v>
+        <v>0.0001681276977475154</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4164,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.000222129825404503</v>
+        <v>0.0001509610263934775</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4177,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002092501790068323</v>
+        <v>0.0001486877091022238</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4190,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0002077091998718574</v>
+        <v>0.0001066543420614364</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4203,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0002022542739255145</v>
+        <v>9.666994566442012e-05</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4216,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0001883828094131394</v>
+        <v>8.619195589405681e-05</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4229,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0001580952325513216</v>
+        <v>6.721828422630137e-05</v>
       </c>
     </row>
     <row r="46">
@@ -4592,11 +4242,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0001555529762327496</v>
+        <v>1.967618852711355e-05</v>
       </c>
     </row>
     <row r="47">
@@ -4605,102 +4255,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0001254575048111429</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0001115110041910677</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0001034278042927943</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0001013191853664384</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>9.854451162539894e-05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>5.725891521908949e-05</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1.942895088559494e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1.890476486443773e-05</v>
+        <v>9.184471826045516e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4749,10 +4308,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4275278758199268</v>
+        <v>0.4151684769240047</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03550831053475043</v>
+        <v>0.03585740306874218</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4324,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1547372651050635</v>
+        <v>0.1452153833480583</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007585522874415515</v>
+        <v>0.007893559155186981</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4340,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08337686689426374</v>
+        <v>0.088669051891718</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006168871607691524</v>
+        <v>0.006418180945404459</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4352,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02625494934165765</v>
+        <v>0.03472139380998875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003888841631173509</v>
+        <v>0.004857797986097962</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4368,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01662492513450205</v>
+        <v>0.02320092263992006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002830197896181418</v>
+        <v>0.003386018282960633</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4384,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001183796798163061</v>
+        <v>0.001224674681760484</v>
       </c>
       <c r="D7" t="n">
-        <v>9.264444868288706e-05</v>
+        <v>7.172409575399142e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4400,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0009065309642396138</v>
+        <v>0.000386734951151535</v>
       </c>
       <c r="D8" t="n">
-        <v>8.551896152560557e-06</v>
+        <v>0.0001047161780032434</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4416,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003713926271153745</v>
+        <v>0.0001190846683090108</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001100944661529108</v>
+        <v>3.523323039944314e-05</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4432,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001997195509044203</v>
+        <v>0.0001145028742273069</v>
       </c>
       <c r="D10" t="n">
-        <v>6.949015172658809e-05</v>
+        <v>5.411114243543691e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4448,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0001716239216839166</v>
+        <v>0.0001132409813681789</v>
       </c>
       <c r="D11" t="n">
-        <v>6.954159173444464e-05</v>
+        <v>9.124886024204294e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4464,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0001512677894620507</v>
+        <v>0.0001061095124867406</v>
       </c>
       <c r="D12" t="n">
-        <v>6.712967861880446e-05</v>
+        <v>2.240972448756145e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4480,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.000132103994265631</v>
+        <v>8.294305775450317e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>2.584794060076993e-05</v>
+        <v>6.510810811704055e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4496,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0001214139411114035</v>
+        <v>6.864221674716121e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>4.654010032362521e-05</v>
+        <v>3.449762040931623e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4512,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0001071084214119389</v>
+        <v>6.776381560408273e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>8.690073980561625e-05</v>
+        <v>4.82139979298405e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4528,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.792114628441983e-05</v>
+        <v>6.641555722113335e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>5.947570701508156e-05</v>
+        <v>7.870459201753235e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4544,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.593794349395222e-05</v>
+        <v>6.577100925052593e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>5.649686260959632e-05</v>
+        <v>8.231106213275129e-05</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +4560,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.458258715731357e-05</v>
+        <v>5.668589636222965e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>5.005957946789628e-05</v>
+        <v>1.198434451167347e-05</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +4576,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.641385675948518e-05</v>
+        <v>3.877498871663887e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>2.228212941223275e-05</v>
+        <v>8.729649372100562e-06</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +4592,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.255398592508675e-05</v>
+        <v>3.825811388710188e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>3.306726163052123e-05</v>
+        <v>4.129479947288042e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +4612,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.174844017820201e-05</v>
+        <v>3.640806285143405e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>6.21670495309607e-05</v>
+        <v>7.696999015808194e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +4624,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.073934206416663e-05</v>
+        <v>3.4899099556851e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>3.180255036783024e-05</v>
+        <v>2.865660719759947e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +4640,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.731557529441764e-05</v>
+        <v>3.470811547484631e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>7.713035803176242e-05</v>
+        <v>0.0005975802484130515</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +4656,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.521327939195572e-05</v>
+        <v>2.493349073656725e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>1.167913747059034e-05</v>
+        <v>4.218239431177304e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +4672,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.916612153397557e-05</v>
+        <v>2.086065535663595e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.702656900939434e-05</v>
+        <v>1.075062352602821e-05</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +4688,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.75569054783109e-05</v>
+        <v>1.977355755543586e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>4.201143414977489e-05</v>
+        <v>1.733902140411539e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +4704,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.612708750228231e-05</v>
+        <v>1.95459259154207e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.383780085515209e-05</v>
+        <v>6.546704857291255e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +4720,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.540573459734578e-06</v>
+        <v>1.469885477373145e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>1.210792919679283e-05</v>
+        <v>5.183685194202562e-07</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +4736,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.263717936783042e-06</v>
+        <v>9.296446570461469e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>2.661511124306268e-05</v>
+        <v>2.054224886737263e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +4752,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.903678078282958e-06</v>
+        <v>5.897804915833138e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0001315005443876507</v>
+        <v>2.151435860366258e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +4768,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.495879729864537e-06</v>
+        <v>5.023328003561645e-07</v>
       </c>
       <c r="D31" t="n">
-        <v>5.816398148942419e-07</v>
+        <v>1.06016980499951e-06</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +4784,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.406410858430853e-06</v>
+        <v>-1.112074870857072e-07</v>
       </c>
       <c r="D32" t="n">
-        <v>6.861140601516018e-05</v>
+        <v>8.027611327202384e-07</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +4800,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.33309803761017e-06</v>
+        <v>-1.37911551978398e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.34481231613268e-05</v>
+        <v>6.497295969079401e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +4816,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.726373676963938e-07</v>
+        <v>-9.532754855268166e-07</v>
       </c>
       <c r="D34" t="n">
-        <v>6.249980597747904e-07</v>
+        <v>1.986051368787528e-05</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +4832,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.10221253424303e-07</v>
+        <v>-1.23170674979356e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>1.252178067716491e-07</v>
+        <v>2.740569868528188e-06</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +4848,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-9.162387754724222e-07</v>
+        <v>-2.401259645712361e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>4.830560856431567e-05</v>
+        <v>5.258298484720497e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +4864,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-2.014887607815208e-06</v>
+        <v>-1.085444705649641e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>1.324658498492881e-05</v>
+        <v>2.383813053813461e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +4880,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-4.703411713002925e-06</v>
+        <v>-1.376256657787955e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.000546341024192002</v>
+        <v>2.057263625478612e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +4896,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-5.10589463744715e-06</v>
+        <v>-1.992766598154505e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>3.495626077876469e-05</v>
+        <v>4.096201357540879e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +4912,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-6.05583248360908e-06</v>
+        <v>-3.298314087567533e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>1.460938618062955e-05</v>
+        <v>7.337010872462637e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +4928,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-6.182965407930397e-06</v>
+        <v>-5.473914662283974e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>3.076844158508651e-05</v>
+        <v>5.123210380942341e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +4944,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-6.678397712900352e-06</v>
+        <v>-5.725481025053991e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>9.070709247008393e-06</v>
+        <v>4.706985318580351e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +4960,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-2.240409385209086e-05</v>
+        <v>-7.867949670369301e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>3.110442438469597e-05</v>
+        <v>6.093680350789598e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +4976,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-2.314953044951773e-05</v>
+        <v>-7.955627674814947e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001231096081280563</v>
+        <v>3.875278440792544e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +4992,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.92481468815442e-05</v>
+        <v>-0.0001146724911101238</v>
       </c>
       <c r="D45" t="n">
-        <v>4.659280836759468e-05</v>
+        <v>0.000132097102009706</v>
       </c>
     </row>
     <row r="46">
@@ -5449,14 +5008,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.15504134551281e-05</v>
+        <v>-0.0001693918106480341</v>
       </c>
       <c r="D46" t="n">
-        <v>2.435233876711132e-05</v>
+        <v>0.0003384858451474934</v>
       </c>
     </row>
     <row r="47">
@@ -5465,126 +5024,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-3.208803637064772e-05</v>
+        <v>-0.0002374245944075759</v>
       </c>
       <c r="D47" t="n">
-        <v>1.553855684654045e-05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-3.738914359020517e-05</v>
-      </c>
-      <c r="D48" t="n">
-        <v>5.200121220846929e-05</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>wastewater_r1_q</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-3.951582136070275e-05</v>
-      </c>
-      <c r="D49" t="n">
-        <v>3.37527159784978e-05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>standard_liquor_brix</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-5.748719285409986e-05</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3.706251298446691e-05</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>work_day</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-7.159233054339076e-05</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.0006041521753791926</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiling_r1_q</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-8.67082824389187e-05</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4.386469448237873e-05</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>filtercake_moisture</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0001153350793199892</v>
-      </c>
-      <c r="D53" t="n">
-        <v>6.875294260969742e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>filtercake_sugar</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.0002221778104696925</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.0003531514623099167</v>
+        <v>0.0005903266323297765</v>
       </c>
     </row>
   </sheetData>
@@ -5598,7 +5045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5628,7 +5075,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.231562346339471</v>
+        <v>1.230827167303108</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5088,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.212438164413909</v>
+        <v>1.214214548351573</v>
       </c>
     </row>
     <row r="4">
@@ -5654,7 +5101,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.071602712577556</v>
+        <v>1.067892686625295</v>
       </c>
     </row>
     <row r="5">
@@ -5667,7 +5114,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8068634900832006</v>
+        <v>0.7957843210604252</v>
       </c>
     </row>
     <row r="6">
@@ -5680,7 +5127,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6663908335330178</v>
+        <v>0.6982133532024903</v>
       </c>
     </row>
     <row r="7">
@@ -5693,7 +5140,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6647508870541099</v>
+        <v>0.6646724278380272</v>
       </c>
     </row>
     <row r="8">
@@ -5706,7 +5153,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5913076670343078</v>
+        <v>0.5971940052420313</v>
       </c>
     </row>
     <row r="9">
@@ -5719,7 +5166,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.550538439464701</v>
+        <v>0.5457839952037666</v>
       </c>
     </row>
     <row r="10">
@@ -5732,7 +5179,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4648439152564756</v>
+        <v>0.4883554073292515</v>
       </c>
     </row>
     <row r="11">
@@ -5741,11 +5188,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3335482345837661</v>
+        <v>0.254449059903076</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5201,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2587939072850545</v>
+        <v>0.2445897889469877</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5214,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2552694439026277</v>
+        <v>0.2388977550151199</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5227,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2547847995899231</v>
+        <v>0.2090796911647348</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5240,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2429740107274019</v>
+        <v>0.2003431368120432</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5253,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2408108237229087</v>
+        <v>0.199104616219703</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5266,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2134376731829786</v>
+        <v>0.1985218637648338</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5279,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.2102993797330091</v>
+        <v>0.1978806624188503</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5292,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1958019766982275</v>
+        <v>0.179419606724633</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5305,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1957813546346203</v>
+        <v>0.1579773684353802</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5318,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1902758747175912</v>
+        <v>0.1541083634048221</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5331,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1711370859094126</v>
+        <v>0.1463444515688344</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5344,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.16122192641236</v>
+        <v>0.1314012452942006</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5357,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1479960569991445</v>
+        <v>0.128004666543299</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5370,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.14754127066016</v>
+        <v>0.1270876349829884</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5383,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1471659955571996</v>
+        <v>0.1257174204872564</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5396,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1471304004695173</v>
+        <v>0.1205093625624927</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5409,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1301270971527879</v>
+        <v>0.1157586112848028</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5422,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1299078641209057</v>
+        <v>0.1132120060624557</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5435,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1220322635174351</v>
+        <v>0.1131160250941958</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5448,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1214339320950062</v>
+        <v>0.1128833862155965</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +5461,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1142378946588831</v>
+        <v>0.1109000822803394</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +5474,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1131622911198775</v>
+        <v>0.1013475265185595</v>
       </c>
     </row>
     <row r="34">
@@ -6044,7 +5491,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1107850262028252</v>
+        <v>0.1012321550566364</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +5500,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1077071466686097</v>
+        <v>0.09845236262286194</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +5513,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1065366655791227</v>
+        <v>0.09019047787179169</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +5526,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1062313428240609</v>
+        <v>0.08654473467831325</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +5539,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1029656032469943</v>
+        <v>0.08227123552180649</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +5552,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1026725904342158</v>
+        <v>0.08183413992755595</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +5565,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.09673555695449876</v>
+        <v>0.07665119805792608</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +5578,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.08944913025642398</v>
+        <v>0.07421889375992929</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +5591,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.08788530601202416</v>
+        <v>0.02422029185884722</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +5604,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.087624953920451</v>
+        <v>0.02348779014183311</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +5617,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.08510757614392039</v>
+        <v>0.02226437970643325</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +5630,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.08188351724165344</v>
+        <v>0.0185581043306744</v>
       </c>
     </row>
     <row r="46">
@@ -6196,114 +5643,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.07784304879969328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.06408156581287239</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.03428089609839091</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiling_r2_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.03341579694077312</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.02907315417629119</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>wastewater_r2_pol</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.02686938527320182</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.005891922780134173</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6379,10 +5735,10 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6391,7 +5747,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:11:10 UTC</t>
+          <t>2026-06-16 11:45:44 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4151684769240047</v>
+        <v>0.4151684769240049</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1452153833480583</v>
+        <v>0.1452153833480585</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.088669051891718</v>
+        <v>0.08866905189171811</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02320092263992006</v>
+        <v>0.02320092263992017</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03472139380998875</v>
+        <v>0.03472139380998884</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -698,7 +698,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001224674681760484</v>
+        <v>0.001224674681799011</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001132409813681789</v>
+        <v>0.0001132409813683011</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.641555722113335e-05</v>
+        <v>6.641555722122216e-05</v>
       </c>
       <c r="H9" t="n">
         <v>15</v>
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000386734951151535</v>
+        <v>0.0003867349511516682</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95459259154207e-05</v>
+        <v>1.954592591554283e-05</v>
       </c>
       <c r="H11" t="n">
         <v>26</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.493349073656725e-05</v>
+        <v>2.493349073668938e-05</v>
       </c>
       <c r="H12" t="n">
         <v>23</v>
@@ -920,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.776381560408273e-05</v>
+        <v>6.776381560418266e-05</v>
       </c>
       <c r="H13" t="n">
         <v>14</v>
@@ -957,7 +957,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>8.294305775450317e-05</v>
+        <v>8.29430577546142e-05</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -994,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0002374245944075759</v>
+        <v>-0.0002374245944074649</v>
       </c>
       <c r="H15" t="n">
         <v>46</v>
@@ -1031,7 +1031,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001145028742273069</v>
+        <v>0.0001145028742274179</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
@@ -1068,7 +1068,7 @@
         <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>6.577100925052593e-05</v>
+        <v>6.577100925065915e-05</v>
       </c>
       <c r="H17" t="n">
         <v>16</v>
@@ -1105,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>3.470811547484631e-05</v>
+        <v>3.470811547494624e-05</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -1142,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001061095124867406</v>
+        <v>0.0001061095124868405</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>3.640806285143405e-05</v>
+        <v>3.640806285152287e-05</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -1216,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>5.668589636222965e-05</v>
+        <v>5.668589636235177e-05</v>
       </c>
       <c r="H21" t="n">
         <v>17</v>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001190846683090108</v>
+        <v>0.0001190846683090885</v>
       </c>
       <c r="H22" t="n">
         <v>8</v>
@@ -1290,7 +1290,7 @@
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.37911551978398e-07</v>
+        <v>-1.379115518784779e-07</v>
       </c>
       <c r="H23" t="n">
         <v>32</v>
@@ -1327,7 +1327,7 @@
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4899099556851e-05</v>
+        <v>3.489909955696202e-05</v>
       </c>
       <c r="H24" t="n">
         <v>21</v>
@@ -1364,7 +1364,7 @@
         <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>6.864221674716121e-05</v>
+        <v>6.864221674729443e-05</v>
       </c>
       <c r="H25" t="n">
         <v>13</v>
@@ -1401,7 +1401,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>2.086065535663595e-05</v>
+        <v>2.086065535674697e-05</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1438,7 +1438,7 @@
         <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.401259645712361e-06</v>
+        <v>-2.401259645579134e-06</v>
       </c>
       <c r="H27" t="n">
         <v>35</v>
@@ -1475,7 +1475,7 @@
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>-5.473914662283974e-05</v>
+        <v>-5.473914662270652e-05</v>
       </c>
       <c r="H28" t="n">
         <v>40</v>
@@ -1512,7 +1512,7 @@
         <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.532754855268166e-07</v>
+        <v>-9.532754854268965e-07</v>
       </c>
       <c r="H29" t="n">
         <v>33</v>
@@ -1549,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>5.897804915833138e-06</v>
+        <v>5.897804915933058e-06</v>
       </c>
       <c r="H30" t="n">
         <v>29</v>
@@ -1586,7 +1586,7 @@
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0001146724911101238</v>
+        <v>-0.000114672491110035</v>
       </c>
       <c r="H31" t="n">
         <v>44</v>
@@ -1623,7 +1623,7 @@
         <v>35</v>
       </c>
       <c r="G32" t="n">
-        <v>-5.725481025053991e-05</v>
+        <v>-5.725481025039558e-05</v>
       </c>
       <c r="H32" t="n">
         <v>41</v>
@@ -1660,7 +1660,7 @@
         <v>34</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0001693918106480341</v>
+        <v>-0.000169391810647912</v>
       </c>
       <c r="H33" t="n">
         <v>45</v>
@@ -1697,7 +1697,7 @@
         <v>31</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.992766598154505e-05</v>
+        <v>-1.992766598145623e-05</v>
       </c>
       <c r="H34" t="n">
         <v>38</v>
@@ -1734,7 +1734,7 @@
         <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>-3.298314087567533e-05</v>
+        <v>-3.298314087556431e-05</v>
       </c>
       <c r="H35" t="n">
         <v>39</v>
@@ -1771,7 +1771,7 @@
         <v>22</v>
       </c>
       <c r="G36" t="n">
-        <v>1.469885477373145e-05</v>
+        <v>1.469885477386468e-05</v>
       </c>
       <c r="H36" t="n">
         <v>27</v>
@@ -1808,7 +1808,7 @@
         <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.376256657787955e-05</v>
+        <v>-1.376256657777963e-05</v>
       </c>
       <c r="H37" t="n">
         <v>37</v>
@@ -1845,7 +1845,7 @@
         <v>33</v>
       </c>
       <c r="G38" t="n">
-        <v>1.977355755543586e-05</v>
+        <v>1.977355755554688e-05</v>
       </c>
       <c r="H38" t="n">
         <v>25</v>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>3.825811388710188e-05</v>
+        <v>3.82581138872351e-05</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -1919,7 +1919,7 @@
         <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>3.877498871663887e-05</v>
+        <v>3.877498871677209e-05</v>
       </c>
       <c r="H40" t="n">
         <v>18</v>
@@ -1956,7 +1956,7 @@
         <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>9.296446570461469e-06</v>
+        <v>9.296446570583594e-06</v>
       </c>
       <c r="H41" t="n">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>-7.867949670369301e-05</v>
+        <v>-7.867949670359309e-05</v>
       </c>
       <c r="H42" t="n">
         <v>42</v>
@@ -2030,7 +2030,7 @@
         <v>36</v>
       </c>
       <c r="G43" t="n">
-        <v>-7.955627674814947e-05</v>
+        <v>-7.955627674804955e-05</v>
       </c>
       <c r="H43" t="n">
         <v>43</v>
@@ -2067,7 +2067,7 @@
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.085444705649641e-05</v>
+        <v>-1.085444705638538e-05</v>
       </c>
       <c r="H44" t="n">
         <v>36</v>
@@ -2104,7 +2104,7 @@
         <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.112074870857072e-07</v>
+        <v>-1.112074869635826e-07</v>
       </c>
       <c r="H45" t="n">
         <v>31</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>5.023328003561645e-07</v>
+        <v>5.023328004671868e-07</v>
       </c>
       <c r="H46" t="n">
         <v>30</v>
@@ -2178,7 +2178,7 @@
         <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.23170674979356e-06</v>
+        <v>-1.231706749671435e-06</v>
       </c>
       <c r="H47" t="n">
         <v>34</v>
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4151684769240047</v>
+        <v>0.4151684769240049</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1452153833480583</v>
+        <v>0.1452153833480585</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2360,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.088669051891718</v>
+        <v>0.08866905189171811</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02320092263992006</v>
+        <v>0.02320092263992017</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03472139380998875</v>
+        <v>0.03472139380998884</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -2471,7 +2471,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001224674681760484</v>
+        <v>0.001224674681799011</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2508,7 +2508,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001132409813681789</v>
+        <v>0.0001132409813683011</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -2545,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.641555722113335e-05</v>
+        <v>6.641555722122216e-05</v>
       </c>
       <c r="H9" t="n">
         <v>15</v>
@@ -2582,7 +2582,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000386734951151535</v>
+        <v>0.0003867349511516682</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -2619,7 +2619,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95459259154207e-05</v>
+        <v>1.954592591554283e-05</v>
       </c>
       <c r="H11" t="n">
         <v>26</v>
@@ -2656,7 +2656,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.493349073656725e-05</v>
+        <v>2.493349073668938e-05</v>
       </c>
       <c r="H12" t="n">
         <v>23</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.776381560408273e-05</v>
+        <v>6.776381560418266e-05</v>
       </c>
       <c r="H13" t="n">
         <v>14</v>
@@ -2730,7 +2730,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>8.294305775450317e-05</v>
+        <v>8.29430577546142e-05</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -2767,7 +2767,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0002374245944075759</v>
+        <v>-0.0002374245944074649</v>
       </c>
       <c r="H15" t="n">
         <v>46</v>
@@ -2804,7 +2804,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001145028742273069</v>
+        <v>0.0001145028742274179</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>6.577100925052593e-05</v>
+        <v>6.577100925065915e-05</v>
       </c>
       <c r="H17" t="n">
         <v>16</v>
@@ -2878,7 +2878,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>3.470811547484631e-05</v>
+        <v>3.470811547494624e-05</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -2915,7 +2915,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001061095124867406</v>
+        <v>0.0001061095124868405</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -2952,7 +2952,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>3.640806285143405e-05</v>
+        <v>3.640806285152287e-05</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -2989,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>5.668589636222965e-05</v>
+        <v>5.668589636235177e-05</v>
       </c>
       <c r="H21" t="n">
         <v>17</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4151684769240047</v>
+        <v>0.4151684769240049</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03585740306874218</v>
+        <v>0.03585740306874215</v>
       </c>
     </row>
     <row r="3">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1452153833480583</v>
+        <v>0.1452153833480585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007893559155186981</v>
+        <v>0.007893559155186962</v>
       </c>
     </row>
     <row r="4">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.088669051891718</v>
+        <v>0.08866905189171811</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006418180945404459</v>
+        <v>0.006418180945404426</v>
       </c>
     </row>
     <row r="5">
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03472139380998875</v>
+        <v>0.03472139380998884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004857797986097962</v>
+        <v>0.004857797986097995</v>
       </c>
     </row>
     <row r="6">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02320092263992006</v>
+        <v>0.02320092263992017</v>
       </c>
       <c r="D6" t="n">
         <v>0.003386018282960633</v>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001224674681760484</v>
+        <v>0.001224674681799011</v>
       </c>
       <c r="D7" t="n">
-        <v>7.172409575399142e-06</v>
+        <v>7.172409575789004e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.000386734951151535</v>
+        <v>0.0003867349511516682</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001047161780032434</v>
+        <v>0.0001047161780032659</v>
       </c>
     </row>
     <row r="9">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0001190846683090108</v>
+        <v>0.0001190846683090885</v>
       </c>
       <c r="D9" t="n">
-        <v>3.523323039944314e-05</v>
+        <v>3.52332303994778e-05</v>
       </c>
     </row>
     <row r="10">
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001145028742273069</v>
+        <v>0.0001145028742274179</v>
       </c>
       <c r="D10" t="n">
         <v>5.411114243543691e-05</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0001132409813681789</v>
+        <v>0.0001132409813683011</v>
       </c>
       <c r="D11" t="n">
-        <v>9.124886024204294e-05</v>
+        <v>9.124886024203394e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0001061095124867406</v>
+        <v>0.0001061095124868405</v>
       </c>
       <c r="D12" t="n">
-        <v>2.240972448756145e-05</v>
+        <v>2.24097244875441e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.294305775450317e-05</v>
+        <v>8.29430577546142e-05</v>
       </c>
       <c r="D13" t="n">
         <v>6.510810811704055e-05</v>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.864221674716121e-05</v>
+        <v>6.864221674729443e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>3.449762040931623e-05</v>
+        <v>3.449762040930817e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.776381560408273e-05</v>
+        <v>6.776381560418266e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.82139979298405e-05</v>
+        <v>4.821399792983768e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.641555722113335e-05</v>
+        <v>6.641555722122216e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>7.870459201753235e-05</v>
+        <v>7.870459201753825e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.577100925052593e-05</v>
+        <v>6.577100925065915e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>8.231106213275129e-05</v>
+        <v>8.231106213274462e-05</v>
       </c>
     </row>
     <row r="18">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.668589636222965e-05</v>
+        <v>5.668589636235177e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>1.198434451167347e-05</v>
+        <v>1.198434451167938e-05</v>
       </c>
     </row>
     <row r="19">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.877498871663887e-05</v>
+        <v>3.877498871677209e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>8.729649372100562e-06</v>
+        <v>8.729649372118166e-06</v>
       </c>
     </row>
     <row r="20">
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.825811388710188e-05</v>
+        <v>3.82581138872351e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>4.129479947288042e-05</v>
+        <v>4.129479947290707e-05</v>
       </c>
     </row>
     <row r="21">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.640806285143405e-05</v>
+        <v>3.640806285152287e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>7.696999015808194e-05</v>
+        <v>7.696999015808648e-05</v>
       </c>
     </row>
     <row r="22">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.4899099556851e-05</v>
+        <v>3.489909955696202e-05</v>
       </c>
       <c r="D22" t="n">
         <v>2.865660719759947e-05</v>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.470811547484631e-05</v>
+        <v>3.470811547494624e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0005975802484130515</v>
+        <v>0.0005975802484130701</v>
       </c>
     </row>
     <row r="24">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.493349073656725e-05</v>
+        <v>2.493349073668938e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>4.218239431177304e-05</v>
+        <v>4.218239431178164e-05</v>
       </c>
     </row>
     <row r="25">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.086065535663595e-05</v>
+        <v>2.086065535674697e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.075062352602821e-05</v>
+        <v>1.075062352605771e-05</v>
       </c>
     </row>
     <row r="26">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.977355755543586e-05</v>
+        <v>1.977355755554688e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>1.733902140411539e-05</v>
+        <v>1.733902140411977e-05</v>
       </c>
     </row>
     <row r="27">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.95459259154207e-05</v>
+        <v>1.954592591554283e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>6.546704857291255e-05</v>
+        <v>6.546704857291021e-05</v>
       </c>
     </row>
     <row r="28">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.469885477373145e-05</v>
+        <v>1.469885477386468e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>5.183685194202562e-07</v>
+        <v>5.183685194247337e-07</v>
       </c>
     </row>
     <row r="29">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9.296446570461469e-06</v>
+        <v>9.296446570583594e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>2.054224886737263e-05</v>
+        <v>2.054224886736475e-05</v>
       </c>
     </row>
     <row r="30">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.897804915833138e-06</v>
+        <v>5.897804915933058e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>2.151435860366258e-05</v>
+        <v>2.151435860366567e-05</v>
       </c>
     </row>
     <row r="31">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.023328003561645e-07</v>
+        <v>5.023328004671868e-07</v>
       </c>
       <c r="D31" t="n">
-        <v>1.06016980499951e-06</v>
+        <v>1.060169804981944e-06</v>
       </c>
     </row>
     <row r="32">
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1.112074870857072e-07</v>
+        <v>-1.112074869635826e-07</v>
       </c>
       <c r="D32" t="n">
-        <v>8.027611327202384e-07</v>
+        <v>8.027611327254037e-07</v>
       </c>
     </row>
     <row r="33">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1.37911551978398e-07</v>
+        <v>-1.379115518784779e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>6.497295969079401e-05</v>
+        <v>6.497295969080344e-05</v>
       </c>
     </row>
     <row r="34">
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-9.532754855268166e-07</v>
+        <v>-9.532754854268965e-07</v>
       </c>
       <c r="D34" t="n">
-        <v>1.986051368787528e-05</v>
+        <v>1.986051368786649e-05</v>
       </c>
     </row>
     <row r="35">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1.23170674979356e-06</v>
+        <v>-1.231706749671435e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>2.740569868528188e-06</v>
+        <v>2.740569868491958e-06</v>
       </c>
     </row>
     <row r="36">
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-2.401259645712361e-06</v>
+        <v>-2.401259645579134e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>5.258298484720497e-05</v>
+        <v>5.258298484722797e-05</v>
       </c>
     </row>
     <row r="37">
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1.085444705649641e-05</v>
+        <v>-1.085444705638538e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>2.383813053813461e-05</v>
+        <v>2.383813053813047e-05</v>
       </c>
     </row>
     <row r="38">
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1.376256657787955e-05</v>
+        <v>-1.376256657777963e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>2.057263625478612e-05</v>
+        <v>2.057263625478888e-05</v>
       </c>
     </row>
     <row r="39">
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1.992766598154505e-05</v>
+        <v>-1.992766598145623e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>4.096201357540879e-05</v>
+        <v>4.096201357540938e-05</v>
       </c>
     </row>
     <row r="40">
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-3.298314087567533e-05</v>
+        <v>-3.298314087556431e-05</v>
       </c>
       <c r="D40" t="n">
         <v>7.337010872462637e-05</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-5.473914662283974e-05</v>
+        <v>-5.473914662270652e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>5.123210380942341e-05</v>
+        <v>5.123210380941628e-05</v>
       </c>
     </row>
     <row r="42">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.725481025053991e-05</v>
+        <v>-5.725481025039558e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>4.706985318580351e-05</v>
+        <v>4.706985318580334e-05</v>
       </c>
     </row>
     <row r="43">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-7.867949670369301e-05</v>
+        <v>-7.867949670359309e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>6.093680350789598e-05</v>
+        <v>6.093680350785984e-05</v>
       </c>
     </row>
     <row r="44">
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-7.955627674814947e-05</v>
+        <v>-7.955627674804955e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>3.875278440792544e-05</v>
+        <v>3.875278440791153e-05</v>
       </c>
     </row>
     <row r="45">
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0001146724911101238</v>
+        <v>-0.000114672491110035</v>
       </c>
       <c r="D45" t="n">
-        <v>0.000132097102009706</v>
+        <v>0.0001320971020097435</v>
       </c>
     </row>
     <row r="46">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0001693918106480341</v>
+        <v>-0.000169391810647912</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003384858451474934</v>
+        <v>0.0003384858451474698</v>
       </c>
     </row>
     <row r="47">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.0002374245944075759</v>
+        <v>-0.0002374245944074649</v>
       </c>
       <c r="D47" t="n">
         <v>0.0005903266323297765</v>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:45:44 UTC</t>
+          <t>2026-06-16 14:03:54 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4151684769240049</v>
+        <v>0.4151684769240047</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1452153833480585</v>
+        <v>0.1452153833480583</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08866905189171811</v>
+        <v>0.08866905189171798</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02320092263992017</v>
+        <v>0.02320092263992006</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03472139380998884</v>
+        <v>0.03472139380998871</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -698,7 +698,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001224674681799011</v>
+        <v>0.001224674681760728</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001132409813683011</v>
+        <v>0.0001132409813682012</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.641555722122216e-05</v>
+        <v>6.641555722112225e-05</v>
       </c>
       <c r="H9" t="n">
         <v>15</v>
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003867349511516682</v>
+        <v>0.0003867349511515683</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>1.954592591554283e-05</v>
+        <v>1.95459259154096e-05</v>
       </c>
       <c r="H11" t="n">
         <v>26</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.493349073668938e-05</v>
+        <v>2.493349073655615e-05</v>
       </c>
       <c r="H12" t="n">
         <v>23</v>
@@ -920,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.776381560418266e-05</v>
+        <v>6.776381560408273e-05</v>
       </c>
       <c r="H13" t="n">
         <v>14</v>
@@ -957,7 +957,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>8.29430577546142e-05</v>
+        <v>8.294305775450317e-05</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -994,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0002374245944074649</v>
+        <v>-0.0002374245944075426</v>
       </c>
       <c r="H15" t="n">
         <v>46</v>
@@ -1031,7 +1031,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001145028742274179</v>
+        <v>0.0001145028742273069</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
@@ -1068,7 +1068,7 @@
         <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>6.577100925065915e-05</v>
+        <v>6.577100925051483e-05</v>
       </c>
       <c r="H17" t="n">
         <v>16</v>
@@ -1105,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>3.470811547494624e-05</v>
+        <v>3.470811547485741e-05</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -1142,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001061095124868405</v>
+        <v>0.0001061095124867517</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>3.640806285152287e-05</v>
+        <v>3.640806285141185e-05</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -1216,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>5.668589636235177e-05</v>
+        <v>5.668589636222965e-05</v>
       </c>
       <c r="H21" t="n">
         <v>17</v>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001190846683090885</v>
+        <v>0.0001190846683089997</v>
       </c>
       <c r="H22" t="n">
         <v>8</v>
@@ -1290,7 +1290,7 @@
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.379115518784779e-07</v>
+        <v>-1.379115519895002e-07</v>
       </c>
       <c r="H23" t="n">
         <v>32</v>
@@ -1327,7 +1327,7 @@
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>3.489909955696202e-05</v>
+        <v>3.48990995568621e-05</v>
       </c>
       <c r="H24" t="n">
         <v>21</v>
@@ -1364,7 +1364,7 @@
         <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>6.864221674729443e-05</v>
+        <v>6.86422167471723e-05</v>
       </c>
       <c r="H25" t="n">
         <v>13</v>
@@ -1401,7 +1401,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>2.086065535674697e-05</v>
+        <v>2.086065535663595e-05</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1438,7 +1438,7 @@
         <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.401259645579134e-06</v>
+        <v>-2.401259645712361e-06</v>
       </c>
       <c r="H27" t="n">
         <v>35</v>
@@ -1475,7 +1475,7 @@
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>-5.473914662270652e-05</v>
+        <v>-5.473914662282864e-05</v>
       </c>
       <c r="H28" t="n">
         <v>40</v>
@@ -1512,7 +1512,7 @@
         <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.532754854268965e-07</v>
+        <v>-9.532754855379188e-07</v>
       </c>
       <c r="H29" t="n">
         <v>33</v>
@@ -1549,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>5.897804915933058e-06</v>
+        <v>5.897804915833138e-06</v>
       </c>
       <c r="H30" t="n">
         <v>29</v>
@@ -1586,7 +1586,7 @@
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.000114672491110035</v>
+        <v>-0.0001146724911101238</v>
       </c>
       <c r="H31" t="n">
         <v>44</v>
@@ -1623,7 +1623,7 @@
         <v>35</v>
       </c>
       <c r="G32" t="n">
-        <v>-5.725481025039558e-05</v>
+        <v>-5.725481025050661e-05</v>
       </c>
       <c r="H32" t="n">
         <v>41</v>
@@ -1660,7 +1660,7 @@
         <v>34</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.000169391810647912</v>
+        <v>-0.0001693918106480341</v>
       </c>
       <c r="H33" t="n">
         <v>45</v>
@@ -1697,7 +1697,7 @@
         <v>31</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.992766598145623e-05</v>
+        <v>-1.992766598155615e-05</v>
       </c>
       <c r="H34" t="n">
         <v>38</v>
@@ -1734,7 +1734,7 @@
         <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>-3.298314087556431e-05</v>
+        <v>-3.298314087568643e-05</v>
       </c>
       <c r="H35" t="n">
         <v>39</v>
@@ -1771,7 +1771,7 @@
         <v>22</v>
       </c>
       <c r="G36" t="n">
-        <v>1.469885477386468e-05</v>
+        <v>1.469885477374255e-05</v>
       </c>
       <c r="H36" t="n">
         <v>27</v>
@@ -1808,7 +1808,7 @@
         <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.376256657777963e-05</v>
+        <v>-1.376256657786845e-05</v>
       </c>
       <c r="H37" t="n">
         <v>37</v>
@@ -1845,7 +1845,7 @@
         <v>33</v>
       </c>
       <c r="G38" t="n">
-        <v>1.977355755554688e-05</v>
+        <v>1.977355755543586e-05</v>
       </c>
       <c r="H38" t="n">
         <v>25</v>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>3.82581138872351e-05</v>
+        <v>3.825811388710188e-05</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -1919,7 +1919,7 @@
         <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>3.877498871677209e-05</v>
+        <v>3.877498871664997e-05</v>
       </c>
       <c r="H40" t="n">
         <v>18</v>
@@ -1956,7 +1956,7 @@
         <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>9.296446570583594e-06</v>
+        <v>9.296446570472572e-06</v>
       </c>
       <c r="H41" t="n">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>-7.867949670359309e-05</v>
+        <v>-7.867949670368191e-05</v>
       </c>
       <c r="H42" t="n">
         <v>42</v>
@@ -2030,7 +2030,7 @@
         <v>36</v>
       </c>
       <c r="G43" t="n">
-        <v>-7.955627674804955e-05</v>
+        <v>-7.955627674813837e-05</v>
       </c>
       <c r="H43" t="n">
         <v>43</v>
@@ -2067,7 +2067,7 @@
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.085444705638538e-05</v>
+        <v>-1.085444705648531e-05</v>
       </c>
       <c r="H44" t="n">
         <v>36</v>
@@ -2104,7 +2104,7 @@
         <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.112074869635826e-07</v>
+        <v>-1.112074870635027e-07</v>
       </c>
       <c r="H45" t="n">
         <v>31</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>5.023328004671868e-07</v>
+        <v>5.023328003450622e-07</v>
       </c>
       <c r="H46" t="n">
         <v>30</v>
@@ -2178,7 +2178,7 @@
         <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.231706749671435e-06</v>
+        <v>-1.231706749782458e-06</v>
       </c>
       <c r="H47" t="n">
         <v>34</v>
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4151684769240049</v>
+        <v>0.4151684769240047</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1452153833480585</v>
+        <v>0.1452153833480583</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2360,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08866905189171811</v>
+        <v>0.08866905189171798</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02320092263992017</v>
+        <v>0.02320092263992006</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03472139380998884</v>
+        <v>0.03472139380998871</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -2471,7 +2471,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001224674681799011</v>
+        <v>0.001224674681760728</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2508,7 +2508,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001132409813683011</v>
+        <v>0.0001132409813682012</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -2545,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.641555722122216e-05</v>
+        <v>6.641555722112225e-05</v>
       </c>
       <c r="H9" t="n">
         <v>15</v>
@@ -2582,7 +2582,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003867349511516682</v>
+        <v>0.0003867349511515683</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -2619,7 +2619,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>1.954592591554283e-05</v>
+        <v>1.95459259154096e-05</v>
       </c>
       <c r="H11" t="n">
         <v>26</v>
@@ -2656,7 +2656,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.493349073668938e-05</v>
+        <v>2.493349073655615e-05</v>
       </c>
       <c r="H12" t="n">
         <v>23</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.776381560418266e-05</v>
+        <v>6.776381560408273e-05</v>
       </c>
       <c r="H13" t="n">
         <v>14</v>
@@ -2730,7 +2730,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>8.29430577546142e-05</v>
+        <v>8.294305775450317e-05</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -2767,7 +2767,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0002374245944074649</v>
+        <v>-0.0002374245944075426</v>
       </c>
       <c r="H15" t="n">
         <v>46</v>
@@ -2804,7 +2804,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001145028742274179</v>
+        <v>0.0001145028742273069</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>6.577100925065915e-05</v>
+        <v>6.577100925051483e-05</v>
       </c>
       <c r="H17" t="n">
         <v>16</v>
@@ -2878,7 +2878,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>3.470811547494624e-05</v>
+        <v>3.470811547485741e-05</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -2915,7 +2915,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001061095124868405</v>
+        <v>0.0001061095124867517</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -2952,7 +2952,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>3.640806285152287e-05</v>
+        <v>3.640806285141185e-05</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -2989,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>5.668589636235177e-05</v>
+        <v>5.668589636222965e-05</v>
       </c>
       <c r="H21" t="n">
         <v>17</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4151684769240049</v>
+        <v>0.4151684769240047</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03585740306874215</v>
+        <v>0.03585740306874217</v>
       </c>
     </row>
     <row r="3">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1452153833480585</v>
+        <v>0.1452153833480583</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007893559155186962</v>
+        <v>0.00789355915518695</v>
       </c>
     </row>
     <row r="4">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08866905189171811</v>
+        <v>0.08866905189171798</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006418180945404426</v>
+        <v>0.006418180945404469</v>
       </c>
     </row>
     <row r="5">
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03472139380998884</v>
+        <v>0.03472139380998871</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004857797986097995</v>
+        <v>0.004857797986097984</v>
       </c>
     </row>
     <row r="6">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02320092263992017</v>
+        <v>0.02320092263992006</v>
       </c>
       <c r="D6" t="n">
         <v>0.003386018282960633</v>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001224674681799011</v>
+        <v>0.001224674681760728</v>
       </c>
       <c r="D7" t="n">
-        <v>7.172409575789004e-06</v>
+        <v>7.172409575468379e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0003867349511516682</v>
+        <v>0.0003867349511515683</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001047161780032659</v>
+        <v>0.000104716178003271</v>
       </c>
     </row>
     <row r="9">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0001190846683090885</v>
+        <v>0.0001190846683089997</v>
       </c>
       <c r="D9" t="n">
-        <v>3.52332303994778e-05</v>
+        <v>3.52332303994458e-05</v>
       </c>
     </row>
     <row r="10">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001145028742274179</v>
+        <v>0.0001145028742273069</v>
       </c>
       <c r="D10" t="n">
-        <v>5.411114243543691e-05</v>
+        <v>5.411114243545376e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0001132409813683011</v>
+        <v>0.0001132409813682012</v>
       </c>
       <c r="D11" t="n">
-        <v>9.124886024203394e-05</v>
+        <v>9.124886024205887e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0001061095124868405</v>
+        <v>0.0001061095124867517</v>
       </c>
       <c r="D12" t="n">
-        <v>2.24097244875441e-05</v>
+        <v>2.240972448756349e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.29430577546142e-05</v>
+        <v>8.294305775450317e-05</v>
       </c>
       <c r="D13" t="n">
         <v>6.510810811704055e-05</v>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.864221674729443e-05</v>
+        <v>6.86422167471723e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>3.449762040930817e-05</v>
+        <v>3.449762040931654e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.776381560418266e-05</v>
+        <v>6.776381560408273e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.821399792983768e-05</v>
+        <v>4.821399792982933e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.641555722122216e-05</v>
+        <v>6.641555722112225e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>7.870459201753825e-05</v>
+        <v>7.870459201753994e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.577100925065915e-05</v>
+        <v>6.577100925051483e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>8.231106213274462e-05</v>
+        <v>8.231106213275732e-05</v>
       </c>
     </row>
     <row r="18">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.668589636235177e-05</v>
+        <v>5.668589636222965e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>1.198434451167938e-05</v>
+        <v>1.198434451168686e-05</v>
       </c>
     </row>
     <row r="19">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.877498871677209e-05</v>
+        <v>3.877498871664997e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>8.729649372118166e-06</v>
+        <v>8.729649372123523e-06</v>
       </c>
     </row>
     <row r="20">
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.82581138872351e-05</v>
+        <v>3.825811388710188e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>4.129479947290707e-05</v>
+        <v>4.129479947288042e-05</v>
       </c>
     </row>
     <row r="21">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.640806285152287e-05</v>
+        <v>3.640806285141185e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>7.696999015808648e-05</v>
+        <v>7.696999015808772e-05</v>
       </c>
     </row>
     <row r="22">
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.489909955696202e-05</v>
+        <v>3.48990995568621e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>2.865660719759947e-05</v>
+        <v>2.865660719761766e-05</v>
       </c>
     </row>
     <row r="23">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.470811547494624e-05</v>
+        <v>3.470811547485741e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0005975802484130701</v>
+        <v>0.0005975802484130679</v>
       </c>
     </row>
     <row r="24">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.493349073668938e-05</v>
+        <v>2.493349073655615e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>4.218239431178164e-05</v>
+        <v>4.21823943117968e-05</v>
       </c>
     </row>
     <row r="25">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.086065535674697e-05</v>
+        <v>2.086065535663595e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.075062352605771e-05</v>
+        <v>1.07506235260568e-05</v>
       </c>
     </row>
     <row r="26">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.977355755554688e-05</v>
+        <v>1.977355755543586e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>1.733902140411977e-05</v>
+        <v>1.733902140411907e-05</v>
       </c>
     </row>
     <row r="27">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.954592591554283e-05</v>
+        <v>1.95459259154096e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>6.546704857291021e-05</v>
+        <v>6.546704857289839e-05</v>
       </c>
     </row>
     <row r="28">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.469885477386468e-05</v>
+        <v>1.469885477374255e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>5.183685194247337e-07</v>
+        <v>5.183685194479902e-07</v>
       </c>
     </row>
     <row r="29">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9.296446570583594e-06</v>
+        <v>9.296446570472572e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>2.054224886736475e-05</v>
+        <v>2.054224886737346e-05</v>
       </c>
     </row>
     <row r="30">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.897804915933058e-06</v>
+        <v>5.897804915833138e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>2.151435860366567e-05</v>
+        <v>2.1514358603652e-05</v>
       </c>
     </row>
     <row r="31">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.023328004671868e-07</v>
+        <v>5.023328003450622e-07</v>
       </c>
       <c r="D31" t="n">
-        <v>1.060169804981944e-06</v>
+        <v>1.06016980500865e-06</v>
       </c>
     </row>
     <row r="32">
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1.112074869635826e-07</v>
+        <v>-1.112074870635027e-07</v>
       </c>
       <c r="D32" t="n">
-        <v>8.027611327254037e-07</v>
+        <v>8.027611327375691e-07</v>
       </c>
     </row>
     <row r="33">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1.379115518784779e-07</v>
+        <v>-1.379115519895002e-07</v>
       </c>
       <c r="D33" t="n">
         <v>6.497295969080344e-05</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-9.532754854268965e-07</v>
+        <v>-9.532754855379188e-07</v>
       </c>
       <c r="D34" t="n">
-        <v>1.986051368786649e-05</v>
+        <v>1.98605136878915e-05</v>
       </c>
     </row>
     <row r="35">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1.231706749671435e-06</v>
+        <v>-1.231706749782458e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>2.740569868491958e-06</v>
+        <v>2.740569868528807e-06</v>
       </c>
     </row>
     <row r="36">
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-2.401259645579134e-06</v>
+        <v>-2.401259645712361e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>5.258298484722797e-05</v>
+        <v>5.25829848472249e-05</v>
       </c>
     </row>
     <row r="37">
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1.085444705638538e-05</v>
+        <v>-1.085444705648531e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>2.383813053813047e-05</v>
+        <v>2.383813053811377e-05</v>
       </c>
     </row>
     <row r="38">
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1.376256657777963e-05</v>
+        <v>-1.376256657786845e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>2.057263625478888e-05</v>
+        <v>2.057263625477628e-05</v>
       </c>
     </row>
     <row r="39">
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1.992766598145623e-05</v>
+        <v>-1.992766598155615e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>4.096201357540938e-05</v>
+        <v>4.096201357540273e-05</v>
       </c>
     </row>
     <row r="40">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-3.298314087556431e-05</v>
+        <v>-3.298314087568643e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>7.337010872462637e-05</v>
+        <v>7.337010872463543e-05</v>
       </c>
     </row>
     <row r="41">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-5.473914662270652e-05</v>
+        <v>-5.473914662282864e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>5.123210380941628e-05</v>
+        <v>5.123210380945012e-05</v>
       </c>
     </row>
     <row r="42">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.725481025039558e-05</v>
+        <v>-5.725481025050661e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>4.706985318580334e-05</v>
+        <v>4.706985318581556e-05</v>
       </c>
     </row>
     <row r="43">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-7.867949670359309e-05</v>
+        <v>-7.867949670368191e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>6.093680350785984e-05</v>
+        <v>6.093680350786929e-05</v>
       </c>
     </row>
     <row r="44">
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-7.955627674804955e-05</v>
+        <v>-7.955627674813837e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>3.875278440791153e-05</v>
+        <v>3.875278440792212e-05</v>
       </c>
     </row>
     <row r="45">
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.000114672491110035</v>
+        <v>-0.0001146724911101238</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0001320971020097435</v>
+        <v>0.0001320971020097207</v>
       </c>
     </row>
     <row r="46">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.000169391810647912</v>
+        <v>-0.0001693918106480341</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003384858451474698</v>
+        <v>0.0003384858451474988</v>
       </c>
     </row>
     <row r="47">
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.0002374245944074649</v>
+        <v>-0.0002374245944075426</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0005903266323297765</v>
+        <v>0.0005903266323297701</v>
       </c>
     </row>
   </sheetData>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:03:54 UTC</t>
+          <t>2026-06-16 15:14:03 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394592</v>
+        <v>0.0818519196639458</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888977</v>
+        <v>0.0768119112588896</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996418</v>
+        <v>0.1562167422996417</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968109</v>
+        <v>0.1428123658968107</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06888948248264246</v>
+        <v>0.0688894824826424</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737097</v>
+        <v>0.02844175294737089</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394592</v>
+        <v>0.0818519196639458</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888977</v>
+        <v>0.0768119112588896</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996418</v>
+        <v>0.1562167422996417</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968109</v>
+        <v>0.1428123658968107</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06888948248264246</v>
+        <v>0.0688894824826424</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737097</v>
+        <v>0.02844175294737089</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1562167422996418</v>
+        <v>0.1562167422996417</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03347985025613801</v>
+        <v>0.03347985025613799</v>
       </c>
     </row>
     <row r="3">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1428123658968109</v>
+        <v>0.1428123658968107</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0470955501769421</v>
+        <v>0.04709555017694214</v>
       </c>
     </row>
     <row r="4">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08185191966394592</v>
+        <v>0.0818519196639458</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03023935897827631</v>
+        <v>0.03023935897827635</v>
       </c>
     </row>
     <row r="5">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07681191125888977</v>
+        <v>0.0768119112588896</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03415374733627249</v>
+        <v>0.0341537473362725</v>
       </c>
     </row>
     <row r="6">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.06888948248264246</v>
+        <v>0.0688894824826424</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0327956112039283</v>
+        <v>0.03279561120392827</v>
       </c>
     </row>
     <row r="7">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02844175294737097</v>
+        <v>0.02844175294737089</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01932516567551015</v>
+        <v>0.01932516567551016</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:30:28 UTC</t>
+          <t>2026-06-16 15:41:43 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0818519196639458</v>
+        <v>0.08185191966394589</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0768119112588896</v>
+        <v>0.07681191125888978</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996417</v>
+        <v>0.1562167422996418</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968107</v>
+        <v>0.1428123658968109</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0688894824826424</v>
+        <v>0.06888948248264247</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737089</v>
+        <v>0.02844175294737087</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0818519196639458</v>
+        <v>0.08185191966394589</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0768119112588896</v>
+        <v>0.07681191125888978</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996417</v>
+        <v>0.1562167422996418</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968107</v>
+        <v>0.1428123658968109</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0688894824826424</v>
+        <v>0.06888948248264247</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737089</v>
+        <v>0.02844175294737087</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1562167422996417</v>
+        <v>0.1562167422996418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03347985025613799</v>
+        <v>0.03347985025613793</v>
       </c>
     </row>
     <row r="3">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1428123658968107</v>
+        <v>0.1428123658968109</v>
       </c>
       <c r="D3" t="n">
         <v>0.04709555017694214</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0818519196639458</v>
+        <v>0.08185191966394589</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03023935897827635</v>
+        <v>0.03023935897827634</v>
       </c>
     </row>
     <row r="5">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0768119112588896</v>
+        <v>0.07681191125888978</v>
       </c>
       <c r="D5" t="n">
         <v>0.0341537473362725</v>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0688894824826424</v>
+        <v>0.06888948248264247</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03279561120392827</v>
+        <v>0.0327956112039283</v>
       </c>
     </row>
     <row r="7">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02844175294737089</v>
+        <v>0.02844175294737087</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01932516567551016</v>
+        <v>0.01932516567551021</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:41:43 UTC</t>
+          <t>2026-06-16 16:27:53 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394589</v>
+        <v>0.08185191966394577</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888978</v>
+        <v>0.07681191125888968</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996418</v>
+        <v>0.1562167422996417</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968109</v>
+        <v>0.1428123658968107</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06888948248264247</v>
+        <v>0.0688894824826424</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737087</v>
+        <v>0.0284417529473708</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394589</v>
+        <v>0.08185191966394577</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888978</v>
+        <v>0.07681191125888968</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996418</v>
+        <v>0.1562167422996417</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968109</v>
+        <v>0.1428123658968107</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06888948248264247</v>
+        <v>0.0688894824826424</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737087</v>
+        <v>0.0284417529473708</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1562167422996418</v>
+        <v>0.1562167422996417</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03347985025613793</v>
+        <v>0.03347985025613795</v>
       </c>
     </row>
     <row r="3">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1428123658968109</v>
+        <v>0.1428123658968107</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04709555017694214</v>
+        <v>0.04709555017694213</v>
       </c>
     </row>
     <row r="4">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08185191966394589</v>
+        <v>0.08185191966394577</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03023935897827634</v>
+        <v>0.03023935897827633</v>
       </c>
     </row>
     <row r="5">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07681191125888978</v>
+        <v>0.07681191125888968</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0341537473362725</v>
+        <v>0.03415374733627251</v>
       </c>
     </row>
     <row r="6">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.06888948248264247</v>
+        <v>0.0688894824826424</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0327956112039283</v>
+        <v>0.03279561120392831</v>
       </c>
     </row>
     <row r="7">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02844175294737087</v>
+        <v>0.0284417529473708</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01932516567551021</v>
+        <v>0.01932516567551018</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-16 16:27:53 UTC</t>
+          <t>2026-06-16 17:02:36 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394577</v>
+        <v>0.08185191966394571</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888968</v>
+        <v>0.07681191125888956</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996417</v>
+        <v>0.1562167422996416</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0688894824826424</v>
+        <v>0.06888948248264228</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0284417529473708</v>
+        <v>0.02844175294737075</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394577</v>
+        <v>0.08185191966394571</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888968</v>
+        <v>0.07681191125888956</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996417</v>
+        <v>0.1562167422996416</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0688894824826424</v>
+        <v>0.06888948248264228</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0284417529473708</v>
+        <v>0.02844175294737075</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1562167422996417</v>
+        <v>0.1562167422996416</v>
       </c>
       <c r="D2" t="n">
         <v>0.03347985025613795</v>
@@ -1289,7 +1289,7 @@
         <v>0.1428123658968107</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04709555017694213</v>
+        <v>0.04709555017694211</v>
       </c>
     </row>
     <row r="4">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08185191966394577</v>
+        <v>0.08185191966394571</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03023935897827633</v>
+        <v>0.03023935897827636</v>
       </c>
     </row>
     <row r="5">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07681191125888968</v>
+        <v>0.07681191125888956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03415374733627251</v>
+        <v>0.03415374733627247</v>
       </c>
     </row>
     <row r="6">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0688894824826424</v>
+        <v>0.06888948248264228</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03279561120392831</v>
+        <v>0.03279561120392832</v>
       </c>
     </row>
     <row r="7">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0284417529473708</v>
+        <v>0.02844175294737075</v>
       </c>
       <c r="D7" t="n">
         <v>0.01932516567551018</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:02:36 UTC</t>
+          <t>2026-06-16 17:20:47 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394571</v>
+        <v>0.08185191966394589</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888956</v>
+        <v>0.07681191125888977</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996416</v>
+        <v>0.1562167422996418</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968107</v>
+        <v>0.1428123658968109</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06888948248264228</v>
+        <v>0.0688894824826425</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737075</v>
+        <v>0.028441752947371</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394571</v>
+        <v>0.08185191966394589</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888956</v>
+        <v>0.07681191125888977</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1562167422996416</v>
+        <v>0.1562167422996418</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1428123658968107</v>
+        <v>0.1428123658968109</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06888948248264228</v>
+        <v>0.0688894824826425</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02844175294737075</v>
+        <v>0.028441752947371</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1562167422996416</v>
+        <v>0.1562167422996418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03347985025613795</v>
+        <v>0.03347985025613796</v>
       </c>
     </row>
     <row r="3">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1428123658968107</v>
+        <v>0.1428123658968109</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04709555017694211</v>
+        <v>0.04709555017694209</v>
       </c>
     </row>
     <row r="4">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08185191966394571</v>
+        <v>0.08185191966394589</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03023935897827636</v>
+        <v>0.03023935897827637</v>
       </c>
     </row>
     <row r="5">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07681191125888956</v>
+        <v>0.07681191125888977</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03415374733627247</v>
+        <v>0.03415374733627249</v>
       </c>
     </row>
     <row r="6">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.06888948248264228</v>
+        <v>0.0688894824826425</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03279561120392832</v>
+        <v>0.03279561120392829</v>
       </c>
     </row>
     <row r="7">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02844175294737075</v>
+        <v>0.028441752947371</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01932516567551018</v>
+        <v>0.01932516567551017</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:20:47 UTC</t>
+          <t>2026-06-16 18:08:36 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394589</v>
+        <v>0.08185191966394592</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888977</v>
+        <v>0.07681191125888978</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0688894824826425</v>
+        <v>0.06888948248264251</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.028441752947371</v>
+        <v>0.02844175294737098</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08185191966394589</v>
+        <v>0.08185191966394592</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07681191125888977</v>
+        <v>0.07681191125888978</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0688894824826425</v>
+        <v>0.06888948248264251</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.028441752947371</v>
+        <v>0.02844175294737098</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1289,7 +1289,7 @@
         <v>0.1428123658968109</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04709555017694209</v>
+        <v>0.04709555017694212</v>
       </c>
     </row>
     <row r="4">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08185191966394589</v>
+        <v>0.08185191966394592</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03023935897827637</v>
+        <v>0.03023935897827633</v>
       </c>
     </row>
     <row r="5">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07681191125888977</v>
+        <v>0.07681191125888978</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03415374733627249</v>
+        <v>0.03415374733627252</v>
       </c>
     </row>
     <row r="6">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0688894824826425</v>
+        <v>0.06888948248264251</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03279561120392829</v>
+        <v>0.03279561120392828</v>
       </c>
     </row>
     <row r="7">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.028441752947371</v>
+        <v>0.02844175294737098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01932516567551017</v>
+        <v>0.01932516567551022</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:08:36 UTC</t>
+          <t>2026-06-16 19:00:51 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_total_points.xlsx
+++ b/NN/reports/feature_importance_white_total_points.xlsx
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547372651050634</v>
+        <v>0.1547372651050635</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08337686689426374</v>
+        <v>0.08337686689426375</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02625494934165764</v>
+        <v>0.02625494934165763</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01662492513450207</v>
+        <v>0.01662492513450209</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009065309642399915</v>
+        <v>0.0009065309642397356</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001071084214119389</v>
+        <v>0.0001071084214119167</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -809,7 +809,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000151267789462084</v>
+        <v>0.0001512677894620951</v>
       </c>
       <c r="H10" t="n">
         <v>11</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001997195509044092</v>
+        <v>0.0001997195509044203</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>6.458258715732467e-05</v>
+        <v>6.458258715733579e-05</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -920,7 +920,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003713926271153301</v>
+        <v>0.0003713926271153412</v>
       </c>
       <c r="H13" t="n">
         <v>8</v>
@@ -957,7 +957,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001214139411114035</v>
+        <v>0.0001214139411113924</v>
       </c>
       <c r="H14" t="n">
         <v>13</v>
@@ -1031,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.159233054340186e-05</v>
+        <v>-7.159233054339076e-05</v>
       </c>
       <c r="H16" t="n">
         <v>50</v>
@@ -1068,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>8.792114628443093e-05</v>
+        <v>8.792114628441983e-05</v>
       </c>
       <c r="H17" t="n">
         <v>15</v>
@@ -1105,7 +1105,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.105894637469355e-06</v>
+        <v>-5.105894637458253e-06</v>
       </c>
       <c r="H18" t="n">
         <v>38</v>
@@ -1216,7 +1216,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>4.073934206418883e-05</v>
+        <v>4.073934206415553e-05</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>2.731557529442874e-05</v>
+        <v>2.731557529445094e-05</v>
       </c>
       <c r="H22" t="n">
         <v>22</v>
@@ -1290,7 +1290,7 @@
         <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7556905478322e-05</v>
+        <v>1.75569054783109e-05</v>
       </c>
       <c r="H23" t="n">
         <v>25</v>
@@ -1475,7 +1475,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>1.612708750226011e-05</v>
+        <v>1.612708750227121e-05</v>
       </c>
       <c r="H28" t="n">
         <v>26</v>
@@ -1586,7 +1586,7 @@
         <v>26</v>
       </c>
       <c r="G31" t="n">
-        <v>-3.951582136071386e-05</v>
+        <v>-3.951582136069165e-05</v>
       </c>
       <c r="H31" t="n">
         <v>48</v>
@@ -1623,7 +1623,7 @@
         <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.314953044951773e-05</v>
+        <v>-2.314953044952883e-05</v>
       </c>
       <c r="H32" t="n">
         <v>43</v>
@@ -1660,7 +1660,7 @@
         <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>-8.670828243894091e-05</v>
+        <v>-8.670828243892981e-05</v>
       </c>
       <c r="H33" t="n">
         <v>51</v>
@@ -1697,7 +1697,7 @@
         <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.05583248360908e-06</v>
+        <v>-6.055832483620183e-06</v>
       </c>
       <c r="H34" t="n">
         <v>39</v>
@@ -1734,7 +1734,7 @@
         <v>29</v>
       </c>
       <c r="G35" t="n">
-        <v>6.263717936794144e-06</v>
+        <v>6.263717936783042e-06</v>
       </c>
       <c r="H35" t="n">
         <v>28</v>
@@ -1771,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="G36" t="n">
-        <v>-9.162387754613199e-07</v>
+        <v>-9.162387754724222e-07</v>
       </c>
       <c r="H36" t="n">
         <v>35</v>
@@ -1808,7 +1808,7 @@
         <v>27</v>
       </c>
       <c r="G37" t="n">
-        <v>-3.15504134551281e-05</v>
+        <v>-3.155041345509479e-05</v>
       </c>
       <c r="H37" t="n">
         <v>45</v>
@@ -1845,7 +1845,7 @@
         <v>37</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.92481468815442e-05</v>
+        <v>-2.92481468815553e-05</v>
       </c>
       <c r="H38" t="n">
         <v>44</v>
@@ -1882,7 +1882,7 @@
         <v>22</v>
       </c>
       <c r="G39" t="n">
-        <v>3.495879729875639e-06</v>
+        <v>3.495879729897844e-06</v>
       </c>
       <c r="H39" t="n">
         <v>30</v>
@@ -1919,7 +1919,7 @@
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0002221778104696814</v>
+        <v>-0.0002221778104696925</v>
       </c>
       <c r="H40" t="n">
         <v>53</v>
@@ -1993,7 +1993,7 @@
         <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.738914359018297e-05</v>
+        <v>-3.738914359020517e-05</v>
       </c>
       <c r="H42" t="n">
         <v>47</v>
@@ -2067,7 +2067,7 @@
         <v>40</v>
       </c>
       <c r="G44" t="n">
-        <v>-2.014887607815208e-06</v>
+        <v>-2.014887607804106e-06</v>
       </c>
       <c r="H44" t="n">
         <v>36</v>
@@ -2141,7 +2141,7 @@
         <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>6.540573459712373e-06</v>
+        <v>6.54057345974568e-06</v>
       </c>
       <c r="H46" t="n">
         <v>27</v>
@@ -2178,7 +2178,7 @@
         <v>39</v>
       </c>
       <c r="G47" t="n">
-        <v>-5.748719285413318e-05</v>
+        <v>-5.748719285412207e-05</v>
       </c>
       <c r="H47" t="n">
         <v>49</v>
@@ -2252,7 +2252,7 @@
         <v>46</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0001153350793199892</v>
+        <v>-0.0001153350793200003</v>
       </c>
       <c r="H49" t="n">
         <v>52</v>
@@ -2326,7 +2326,7 @@
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-6.182965407941499e-06</v>
+        <v>-6.182965407930397e-06</v>
       </c>
       <c r="H51" t="n">
         <v>40</v>
@@ -2363,7 +2363,7 @@
         <v>51</v>
       </c>
       <c r="G52" t="n">
-        <v>7.726373676852915e-07</v>
+        <v>7.726373676963938e-07</v>
       </c>
       <c r="H52" t="n">
         <v>33</v>
@@ -2400,7 +2400,7 @@
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>1.102212534354052e-07</v>
+        <v>1.102212534020985e-07</v>
       </c>
       <c r="H53" t="n">
         <v>34</v>
@@ -2437,7 +2437,7 @@
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>-6.67839771288925e-06</v>
+        <v>-6.678397712878148e-06</v>
       </c>
       <c r="H54" t="n">
         <v>41</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547372651050634</v>
+        <v>0.1547372651050635</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08337686689426374</v>
+        <v>0.08337686689426375</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02625494934165764</v>
+        <v>0.02625494934165763</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01662492513450207</v>
+        <v>0.01662492513450209</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009065309642399915</v>
+        <v>0.0009065309642397356</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2804,7 +2804,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001071084214119389</v>
+        <v>0.0001071084214119167</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -2841,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000151267789462084</v>
+        <v>0.0001512677894620951</v>
       </c>
       <c r="H10" t="n">
         <v>11</v>
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001997195509044092</v>
+        <v>0.0001997195509044203</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -2915,7 +2915,7 @@
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>6.458258715732467e-05</v>
+        <v>6.458258715733579e-05</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -2952,7 +2952,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003713926271153301</v>
+        <v>0.0003713926271153412</v>
       </c>
       <c r="H13" t="n">
         <v>8</v>
@@ -2989,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001214139411114035</v>
+        <v>0.0001214139411113924</v>
       </c>
       <c r="H14" t="n">
         <v>13</v>
@@ -3063,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.159233054340186e-05</v>
+        <v>-7.159233054339076e-05</v>
       </c>
       <c r="H16" t="n">
         <v>50</v>
@@ -3100,7 +3100,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>8.792114628443093e-05</v>
+        <v>8.792114628441983e-05</v>
       </c>
       <c r="H17" t="n">
         <v>15</v>
@@ -3137,7 +3137,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.105894637469355e-06</v>
+        <v>-5.105894637458253e-06</v>
       </c>
       <c r="H18" t="n">
         <v>38</v>
@@ -3248,7 +3248,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>4.073934206418883e-05</v>
+        <v>4.073934206415553e-05</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -4752,7 +4752,7 @@
         <v>0.4275278758199269</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03550831053475043</v>
+        <v>0.03550831053475044</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1547372651050634</v>
+        <v>0.1547372651050635</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007585522874415529</v>
+        <v>0.00758552287441553</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08337686689426374</v>
+        <v>0.08337686689426375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006168871607691502</v>
+        <v>0.006168871607691515</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02625494934165764</v>
+        <v>0.02625494934165763</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003888841631173515</v>
+        <v>0.003888841631173528</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01662492513450207</v>
+        <v>0.01662492513450209</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002830197896181445</v>
+        <v>0.002830197896181399</v>
       </c>
     </row>
     <row r="7">
@@ -4832,7 +4832,7 @@
         <v>0.001183796798163073</v>
       </c>
       <c r="D7" t="n">
-        <v>9.264444868287794e-05</v>
+        <v>9.264444868287196e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0009065309642399915</v>
+        <v>0.0009065309642397356</v>
       </c>
       <c r="D8" t="n">
-        <v>8.551896153054946e-06</v>
+        <v>8.551896152880928e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003713926271153301</v>
+        <v>0.0003713926271153412</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001100944661529354</v>
+        <v>0.0001100944661529278</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001997195509044092</v>
+        <v>0.0001997195509044203</v>
       </c>
       <c r="D10" t="n">
-        <v>6.949015172659392e-05</v>
+        <v>6.949015172658795e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.000151267789462084</v>
+        <v>0.0001512677894620951</v>
       </c>
       <c r="D12" t="n">
-        <v>6.712967861880868e-05</v>
+        <v>6.712967861878739e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4928,7 +4928,7 @@
         <v>0.0001321039942656199</v>
       </c>
       <c r="D13" t="n">
-        <v>2.584794060076915e-05</v>
+        <v>2.584794060078515e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0001214139411114035</v>
+        <v>0.0001214139411113924</v>
       </c>
       <c r="D14" t="n">
-        <v>4.654010032356979e-05</v>
+        <v>4.654010032360957e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0001071084214119389</v>
+        <v>0.0001071084214119167</v>
       </c>
       <c r="D15" t="n">
-        <v>8.690073980559234e-05</v>
+        <v>8.690073980560859e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.792114628443093e-05</v>
+        <v>8.792114628441983e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>5.947570701509682e-05</v>
+        <v>5.947570701509089e-05</v>
       </c>
     </row>
     <row r="17">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.458258715732467e-05</v>
+        <v>6.458258715733579e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>5.005957946790429e-05</v>
+        <v>5.005957946790255e-05</v>
       </c>
     </row>
     <row r="19">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.073934206418883e-05</v>
+        <v>4.073934206415553e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>3.180255036780966e-05</v>
+        <v>3.180255036781274e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.731557529442874e-05</v>
+        <v>2.731557529445094e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>7.713035803174252e-05</v>
+        <v>7.713035803170732e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5120,7 +5120,7 @@
         <v>1.916612153399777e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>1.702656900939287e-05</v>
+        <v>1.702656900936875e-05</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.7556905478322e-05</v>
+        <v>1.75569054783109e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>4.201143414976832e-05</v>
+        <v>4.201143414976464e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.612708750226011e-05</v>
+        <v>1.612708750227121e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.383780085513268e-05</v>
+        <v>1.383780085514585e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.540573459712373e-06</v>
+        <v>6.54057345974568e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>1.210792919676313e-05</v>
+        <v>1.210792919677046e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.263717936794144e-06</v>
+        <v>6.263717936783042e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>2.661511124307446e-05</v>
+        <v>2.661511124306268e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5200,7 +5200,7 @@
         <v>4.903678078282958e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0001315005443876463</v>
+        <v>0.0001315005443876451</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.495879729875639e-06</v>
+        <v>3.495879729897844e-06</v>
       </c>
       <c r="D31" t="n">
-        <v>5.816398148777523e-07</v>
+        <v>5.81639814890867e-07</v>
       </c>
     </row>
     <row r="32">
@@ -5232,7 +5232,7 @@
         <v>3.40641085841975e-06</v>
       </c>
       <c r="D32" t="n">
-        <v>6.861140601515437e-05</v>
+        <v>6.861140601517543e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5248,7 +5248,7 @@
         <v>2.333098037632375e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>1.344812316134969e-05</v>
+        <v>1.344812316134239e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.726373676852915e-07</v>
+        <v>7.726373676963938e-07</v>
       </c>
       <c r="D34" t="n">
-        <v>6.249980597893795e-07</v>
+        <v>6.249980597747904e-07</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.102212534354052e-07</v>
+        <v>1.102212534020985e-07</v>
       </c>
       <c r="D35" t="n">
-        <v>1.252178067890837e-07</v>
+        <v>1.252178067876901e-07</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-9.162387754613199e-07</v>
+        <v>-9.162387754724222e-07</v>
       </c>
       <c r="D36" t="n">
-        <v>4.830560856431495e-05</v>
+        <v>4.830560856433452e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-2.014887607815208e-06</v>
+        <v>-2.014887607804106e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>1.324658498492881e-05</v>
+        <v>1.324658498491808e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5328,7 +5328,7 @@
         <v>-4.703411712991823e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005463410241920008</v>
+        <v>0.0005463410241920093</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-5.105894637469355e-06</v>
+        <v>-5.105894637458253e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>3.495626077877415e-05</v>
+        <v>3.495626077880426e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-6.05583248360908e-06</v>
+        <v>-6.055832483620183e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>1.460938618062169e-05</v>
+        <v>1.460938618063769e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-6.182965407941499e-06</v>
+        <v>-6.182965407930397e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>3.076844158505298e-05</v>
+        <v>3.07684415850609e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-6.67839771288925e-06</v>
+        <v>-6.678397712878148e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>9.07070924700926e-06</v>
+        <v>9.070709247001052e-06</v>
       </c>
     </row>
     <row r="43">
@@ -5408,7 +5408,7 @@
         <v>-2.240409385209086e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>3.110442438468803e-05</v>
+        <v>3.110442438470023e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-2.314953044951773e-05</v>
+        <v>-2.314953044952883e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00012310960812805</v>
+        <v>0.0001231096081280672</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.92481468815442e-05</v>
+        <v>-2.92481468815553e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>4.659280836759468e-05</v>
+        <v>4.659280836759686e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.15504134551281e-05</v>
+        <v>-3.155041345509479e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>2.435233876713221e-05</v>
+        <v>2.435233876710837e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-3.738914359018297e-05</v>
+        <v>-3.738914359020517e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>5.200121220848164e-05</v>
+        <v>5.200121220846929e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-3.951582136071386e-05</v>
+        <v>-3.951582136069165e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>3.375271597848838e-05</v>
+        <v>3.375271597849002e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5.748719285413318e-05</v>
+        <v>-5.748719285412207e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>3.706251298449458e-05</v>
+        <v>3.70625129844483e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-7.159233054340186e-05</v>
+        <v>-7.159233054339076e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0006041521753791865</v>
+        <v>0.0006041521753791926</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-8.670828243894091e-05</v>
+        <v>-8.670828243892981e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>4.386469448239552e-05</v>
+        <v>4.38646944823842e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001153350793199892</v>
+        <v>-0.0001153350793200003</v>
       </c>
       <c r="D53" t="n">
-        <v>6.87529426097149e-05</v>
+        <v>6.875294260969585e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0002221778104696814</v>
+        <v>-0.0002221778104696925</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003531514623099235</v>
+        <v>0.0003531514623099139</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:54:30 UTC</t>
+          <t>2026-06-16 19:23:09 UTC</t>
         </is>
       </c>
     </row>
